--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA74D84-EDA5-4F53-B516-677C579C5190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B852FA38-DB7D-44DE-9B5B-F57F7940B7AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9317,7 +9317,7 @@
       </c>
       <c r="F407" s="3"/>
     </row>
-    <row r="408" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B408" s="2">
         <f t="shared" si="6"/>
         <v>404</v>
@@ -9333,7 +9333,7 @@
       </c>
       <c r="F408" s="3"/>
     </row>
-    <row r="409" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B409" s="2">
         <f t="shared" si="6"/>
         <v>405</v>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="F409" s="3"/>
     </row>
-    <row r="410" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B410" s="2">
         <f t="shared" si="6"/>
         <v>406</v>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="F410" s="3"/>
     </row>
-    <row r="411" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B411" s="2">
         <f t="shared" si="6"/>
         <v>407</v>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="F411" s="3"/>
     </row>
-    <row r="412" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B412" s="2">
         <f t="shared" si="6"/>
         <v>408</v>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="F412" s="3"/>
     </row>
-    <row r="413" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B413" s="2">
         <f t="shared" si="6"/>
         <v>409</v>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="F413" s="3"/>
     </row>
-    <row r="414" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B414" s="2">
         <f t="shared" si="6"/>
         <v>410</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="F414" s="3"/>
     </row>
-    <row r="415" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B415" s="2">
         <f t="shared" si="6"/>
         <v>411</v>
@@ -9445,7 +9445,7 @@
       </c>
       <c r="F415" s="3"/>
     </row>
-    <row r="416" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B416" s="2">
         <f t="shared" si="6"/>
         <v>412</v>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="F416" s="3"/>
     </row>
-    <row r="417" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B417" s="2">
         <f t="shared" si="6"/>
         <v>413</v>
@@ -9477,7 +9477,7 @@
       </c>
       <c r="F417" s="3"/>
     </row>
-    <row r="418" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B418" s="2">
         <f t="shared" si="6"/>
         <v>414</v>
@@ -9493,7 +9493,7 @@
       </c>
       <c r="F418" s="3"/>
     </row>
-    <row r="419" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B419" s="2">
         <f t="shared" si="6"/>
         <v>415</v>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="F419" s="3"/>
     </row>
-    <row r="420" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B420" s="2">
         <f t="shared" si="6"/>
         <v>416</v>
@@ -9525,7 +9525,7 @@
       </c>
       <c r="F420" s="3"/>
     </row>
-    <row r="421" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B421" s="2">
         <f t="shared" si="6"/>
         <v>417</v>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="F421" s="3"/>
     </row>
-    <row r="422" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B422" s="2">
         <f t="shared" si="6"/>
         <v>418</v>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="F422" s="3"/>
     </row>
-    <row r="423" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B423" s="2">
         <f t="shared" si="6"/>
         <v>419</v>
@@ -9573,7 +9573,7 @@
       </c>
       <c r="F423" s="3"/>
     </row>
-    <row r="424" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B424" s="2">
         <f t="shared" si="6"/>
         <v>420</v>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="F424" s="3"/>
     </row>
-    <row r="425" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B425" s="2">
         <f t="shared" si="6"/>
         <v>421</v>
@@ -9605,7 +9605,7 @@
       </c>
       <c r="F425" s="3"/>
     </row>
-    <row r="426" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B426" s="2">
         <f t="shared" si="6"/>
         <v>422</v>
@@ -9621,7 +9621,7 @@
       </c>
       <c r="F426" s="3"/>
     </row>
-    <row r="427" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B427" s="2">
         <f t="shared" si="6"/>
         <v>423</v>
@@ -9637,7 +9637,7 @@
       </c>
       <c r="F427" s="3"/>
     </row>
-    <row r="428" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B428" s="2">
         <f t="shared" si="6"/>
         <v>424</v>
@@ -9653,7 +9653,7 @@
       </c>
       <c r="F428" s="3"/>
     </row>
-    <row r="429" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B429" s="2">
         <f t="shared" si="6"/>
         <v>425</v>
@@ -9669,7 +9669,7 @@
       </c>
       <c r="F429" s="3"/>
     </row>
-    <row r="430" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B430" s="2">
         <f t="shared" si="6"/>
         <v>426</v>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="F430" s="3"/>
     </row>
-    <row r="431" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B431" s="2">
         <f t="shared" si="6"/>
         <v>427</v>
@@ -9701,7 +9701,7 @@
       </c>
       <c r="F431" s="3"/>
     </row>
-    <row r="432" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B432" s="2">
         <f t="shared" si="6"/>
         <v>428</v>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="F432" s="3"/>
     </row>
-    <row r="433" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B433" s="2">
         <f t="shared" si="6"/>
         <v>429</v>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="F433" s="3"/>
     </row>
-    <row r="434" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B434" s="2">
         <f t="shared" si="6"/>
         <v>430</v>
@@ -9749,7 +9749,7 @@
       </c>
       <c r="F434" s="3"/>
     </row>
-    <row r="435" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B435" s="2">
         <f t="shared" si="6"/>
         <v>431</v>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="F435" s="3"/>
     </row>
-    <row r="436" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B436" s="2">
         <f t="shared" si="6"/>
         <v>432</v>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="F436" s="3"/>
     </row>
-    <row r="437" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B437" s="2">
         <f t="shared" si="6"/>
         <v>433</v>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="F437" s="3"/>
     </row>
-    <row r="438" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B438" s="2">
         <f t="shared" si="6"/>
         <v>434</v>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="F438" s="3"/>
     </row>
-    <row r="439" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B439" s="2">
         <f t="shared" si="6"/>
         <v>435</v>
@@ -9829,7 +9829,7 @@
       </c>
       <c r="F439" s="3"/>
     </row>
-    <row r="440" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B440" s="2">
         <f t="shared" si="6"/>
         <v>436</v>
@@ -9845,7 +9845,7 @@
       </c>
       <c r="F440" s="3"/>
     </row>
-    <row r="441" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B441" s="2">
         <f t="shared" si="6"/>
         <v>437</v>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="F441" s="3"/>
     </row>
-    <row r="442" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B442" s="2">
         <f t="shared" si="6"/>
         <v>438</v>
@@ -11685,7 +11685,7 @@
       </c>
       <c r="F555" s="3"/>
     </row>
-    <row r="556" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="556" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B556" s="2">
         <f t="shared" si="8"/>
         <v>552</v>
@@ -12443,7 +12443,41 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="SANA CASH AND CARRY IQBAL AVENUE CANAL ROAD"/>
+        <filter val="JALAL SONS  (COLLEGE ROAD) 02"/>
+        <filter val="Jalal sons  (Izmair Town) 01"/>
+        <filter val="Jalal sons (Askari 10 F sector ) 01"/>
+        <filter val="JALAL SONS (ASKARI 11 B BLOCK) 02"/>
+        <filter val="JALAL SONS (AYUBIA) 02"/>
+        <filter val="JALAL SONS (Bahira Orchard) 01"/>
+        <filter val="Jalal Sons (Bahria Town)  01"/>
+        <filter val="JALAL SONS (C BLOCK MODEL TOWN) 02"/>
+        <filter val="JALAL SONS (DHA C BLOCK,PHASE 6) 02"/>
+        <filter val="JALAL SONS (DHA PH IV) 02"/>
+        <filter val="JALAL SONS (DHA PH V) 02"/>
+        <filter val="JALAL SONS (DHA Y BLOCK) 02"/>
+        <filter val="JALAL SONS (EME) 02"/>
+        <filter val="JALAL SONS (FAISAL TOWN) 02"/>
+        <filter val="Jalal Sons (H Block) 01"/>
+        <filter val="JALAL SONS (HUSSAIN CHOWK GULBERG III) 02"/>
+        <filter val="JALAL SONS (IQBAL TOWN) 02"/>
+        <filter val="Jalal Sons (J.T Shadewal) 01"/>
+        <filter val="JALAL SONS (JOHER TOWN) 02"/>
+        <filter val="Jalal Sons (Lake City) 01"/>
+        <filter val="Jalal sons (Main Market) 01"/>
+        <filter val="JALAL SONS (MODEL TOWN LINK ROAD) 02"/>
+        <filter val="Jalal Sons (PAF Market) 01 main Market"/>
+        <filter val="JALAL SONS (PARAGON CITY) 02"/>
+        <filter val="JALAL SONS (PH VI) 02"/>
+        <filter val="JALAL SONS (PHASE 8 EX PARK VIEW) 02"/>
+        <filter val="JALAL SONS (REVAZ GARDEN) 02"/>
+        <filter val="JALAL SONS (SHADMAN) 02"/>
+        <filter val="JALAL SONS (SHAUKAT KHANUM) 02"/>
+        <filter val="JALAL SONS (STATE LIFE) 02"/>
+        <filter val="JALAL SONS (TALWAR CHOWK) 02"/>
+        <filter val="JALAL SONS (VALENCIA TOWN) 02"/>
+        <filter val="JALAL SONS (WAPDA TOWN) 02"/>
+        <filter val="JALAL SONS (XX) 02"/>
+        <filter val="Jalal Sons Askari X (01)"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B852FA38-DB7D-44DE-9B5B-F57F7940B7AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{809C59B2-7AD5-43ED-AF36-CCB22A300CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="807">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="806">
   <si>
     <t>Sr#</t>
   </si>
@@ -496,9 +496,6 @@
   </si>
   <si>
     <t>BAHADUR CASH &amp; CARRY STORE (ISLAMPURA)</t>
-  </si>
-  <si>
-    <t>77191132</t>
   </si>
   <si>
     <t>BASHIR SONS (NAWAB TOWN)</t>
@@ -4475,7 +4472,7 @@
         <v>101</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>90</v>
@@ -4717,8 +4714,8 @@
       <c r="C120" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D120" s="2" t="s">
-        <v>156</v>
+      <c r="D120" s="2">
+        <v>77191132</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>5</v>
@@ -4731,13 +4728,13 @@
         <v>117</v>
       </c>
       <c r="C121" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D121" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D121" s="2" t="s">
-        <v>158</v>
-      </c>
       <c r="E121" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F121" s="3"/>
     </row>
@@ -4747,7 +4744,7 @@
         <v>118</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>5</v>
@@ -4763,10 +4760,10 @@
         <v>119</v>
       </c>
       <c r="C123" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D123" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>5</v>
@@ -4779,10 +4776,10 @@
         <v>120</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>5</v>
@@ -4795,10 +4792,10 @@
         <v>121</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>5</v>
@@ -4811,10 +4808,10 @@
         <v>122</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>5</v>
@@ -4827,10 +4824,10 @@
         <v>123</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>5</v>
@@ -4843,10 +4840,10 @@
         <v>124</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>5</v>
@@ -4859,10 +4856,10 @@
         <v>125</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>5</v>
@@ -4875,10 +4872,10 @@
         <v>126</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>5</v>
@@ -4891,10 +4888,10 @@
         <v>127</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>5</v>
@@ -4907,10 +4904,10 @@
         <v>128</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>5</v>
@@ -4923,10 +4920,10 @@
         <v>129</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>5</v>
@@ -4939,10 +4936,10 @@
         <v>130</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>5</v>
@@ -4955,7 +4952,7 @@
         <v>131</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>5</v>
@@ -4971,10 +4968,10 @@
         <v>132</v>
       </c>
       <c r="C136" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D136" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>175</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>5</v>
@@ -4987,10 +4984,10 @@
         <v>133</v>
       </c>
       <c r="C137" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D137" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>5</v>
@@ -5003,10 +5000,10 @@
         <v>134</v>
       </c>
       <c r="C138" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D138" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>5</v>
@@ -5019,10 +5016,10 @@
         <v>135</v>
       </c>
       <c r="C139" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D139" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>5</v>
@@ -5035,10 +5032,10 @@
         <v>136</v>
       </c>
       <c r="C140" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D140" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="D140" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>5</v>
@@ -5051,10 +5048,10 @@
         <v>137</v>
       </c>
       <c r="C141" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D141" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="D141" s="2" t="s">
-        <v>185</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>5</v>
@@ -5067,10 +5064,10 @@
         <v>138</v>
       </c>
       <c r="C142" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D142" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="D142" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>5</v>
@@ -5083,10 +5080,10 @@
         <v>139</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>5</v>
@@ -5099,10 +5096,10 @@
         <v>140</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>5</v>
@@ -5115,10 +5112,10 @@
         <v>141</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>5</v>
@@ -5131,10 +5128,10 @@
         <v>142</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>5</v>
@@ -5147,10 +5144,10 @@
         <v>143</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>5</v>
@@ -5163,10 +5160,10 @@
         <v>144</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>5</v>
@@ -5179,10 +5176,10 @@
         <v>145</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>5</v>
@@ -5195,10 +5192,10 @@
         <v>146</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>5</v>
@@ -5211,10 +5208,10 @@
         <v>147</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>5</v>
@@ -5227,10 +5224,10 @@
         <v>148</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>5</v>
@@ -5243,10 +5240,10 @@
         <v>149</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>5</v>
@@ -5259,10 +5256,10 @@
         <v>150</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>5</v>
@@ -5275,10 +5272,10 @@
         <v>151</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>5</v>
@@ -5291,10 +5288,10 @@
         <v>152</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>5</v>
@@ -5307,10 +5304,10 @@
         <v>153</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>5</v>
@@ -5323,10 +5320,10 @@
         <v>154</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>5</v>
@@ -5339,10 +5336,10 @@
         <v>155</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>5</v>
@@ -5355,10 +5352,10 @@
         <v>156</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>5</v>
@@ -5371,10 +5368,10 @@
         <v>157</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>5</v>
@@ -5387,10 +5384,10 @@
         <v>158</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>5</v>
@@ -5403,10 +5400,10 @@
         <v>159</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>5</v>
@@ -5419,10 +5416,10 @@
         <v>160</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>5</v>
@@ -5435,10 +5432,10 @@
         <v>161</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>5</v>
@@ -5451,10 +5448,10 @@
         <v>162</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>5</v>
@@ -5467,10 +5464,10 @@
         <v>163</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>5</v>
@@ -5483,10 +5480,10 @@
         <v>164</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>5</v>
@@ -5499,10 +5496,10 @@
         <v>165</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>5</v>
@@ -5515,10 +5512,10 @@
         <v>166</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>5</v>
@@ -5531,10 +5528,10 @@
         <v>167</v>
       </c>
       <c r="C171" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D171" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="D171" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>5</v>
@@ -5547,10 +5544,10 @@
         <v>168</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>5</v>
@@ -5563,10 +5560,10 @@
         <v>169</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>5</v>
@@ -5579,10 +5576,10 @@
         <v>170</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>5</v>
@@ -5595,10 +5592,10 @@
         <v>171</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>5</v>
@@ -5611,10 +5608,10 @@
         <v>172</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>5</v>
@@ -5627,10 +5624,10 @@
         <v>173</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>5</v>
@@ -5643,10 +5640,10 @@
         <v>174</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>5</v>
@@ -5659,10 +5656,10 @@
         <v>175</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>5</v>
@@ -5675,10 +5672,10 @@
         <v>176</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>5</v>
@@ -5691,10 +5688,10 @@
         <v>177</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>5</v>
@@ -5707,10 +5704,10 @@
         <v>178</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>5</v>
@@ -5723,10 +5720,10 @@
         <v>179</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>5</v>
@@ -5739,10 +5736,10 @@
         <v>180</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>5</v>
@@ -5755,10 +5752,10 @@
         <v>181</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>5</v>
@@ -5771,10 +5768,10 @@
         <v>182</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>5</v>
@@ -5787,10 +5784,10 @@
         <v>183</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>5</v>
@@ -5803,13 +5800,13 @@
         <v>184</v>
       </c>
       <c r="C188" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D188" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="D188" s="2" t="s">
-        <v>235</v>
-      </c>
       <c r="E188" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F188" s="3"/>
     </row>
@@ -5819,10 +5816,10 @@
         <v>185</v>
       </c>
       <c r="C189" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D189" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="D189" s="2" t="s">
-        <v>237</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>5</v>
@@ -5835,10 +5832,10 @@
         <v>186</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>5</v>
@@ -5851,10 +5848,10 @@
         <v>187</v>
       </c>
       <c r="C191" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D191" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="D191" s="2" t="s">
-        <v>240</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>5</v>
@@ -5867,10 +5864,10 @@
         <v>188</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>5</v>
@@ -5883,10 +5880,10 @@
         <v>189</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>5</v>
@@ -5899,10 +5896,10 @@
         <v>190</v>
       </c>
       <c r="C194" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D194" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="D194" s="2" t="s">
-        <v>244</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>5</v>
@@ -5915,10 +5912,10 @@
         <v>191</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E195" s="1" t="s">
         <v>5</v>
@@ -5931,10 +5928,10 @@
         <v>192</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>5</v>
@@ -5947,10 +5944,10 @@
         <v>193</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E197" s="1" t="s">
         <v>5</v>
@@ -5963,10 +5960,10 @@
         <v>194</v>
       </c>
       <c r="C198" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D198" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="D198" s="2" t="s">
-        <v>249</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>5</v>
@@ -5979,10 +5976,10 @@
         <v>195</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>5</v>
@@ -5995,10 +5992,10 @@
         <v>196</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>5</v>
@@ -6011,10 +6008,10 @@
         <v>197</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>5</v>
@@ -6027,10 +6024,10 @@
         <v>198</v>
       </c>
       <c r="C202" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D202" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="D202" s="2" t="s">
-        <v>254</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>5</v>
@@ -6043,10 +6040,10 @@
         <v>199</v>
       </c>
       <c r="C203" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D203" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="D203" s="2" t="s">
-        <v>256</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>5</v>
@@ -6059,10 +6056,10 @@
         <v>200</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>5</v>
@@ -6075,10 +6072,10 @@
         <v>201</v>
       </c>
       <c r="C205" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D205" s="2" t="s">
         <v>258</v>
-      </c>
-      <c r="D205" s="2" t="s">
-        <v>259</v>
       </c>
       <c r="E205" s="1" t="s">
         <v>5</v>
@@ -6091,10 +6088,10 @@
         <v>202</v>
       </c>
       <c r="C206" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D206" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="D206" s="2" t="s">
-        <v>261</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>5</v>
@@ -6107,10 +6104,10 @@
         <v>203</v>
       </c>
       <c r="C207" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D207" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="D207" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>5</v>
@@ -6123,10 +6120,10 @@
         <v>204</v>
       </c>
       <c r="C208" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D208" s="2" t="s">
         <v>264</v>
-      </c>
-      <c r="D208" s="2" t="s">
-        <v>265</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>5</v>
@@ -6139,13 +6136,13 @@
         <v>205</v>
       </c>
       <c r="C209" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E209" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="D209" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E209" s="1" t="s">
-        <v>267</v>
       </c>
       <c r="F209" s="3"/>
     </row>
@@ -6155,10 +6152,10 @@
         <v>206</v>
       </c>
       <c r="C210" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D210" s="2" t="s">
         <v>268</v>
-      </c>
-      <c r="D210" s="2" t="s">
-        <v>269</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>5</v>
@@ -6171,10 +6168,10 @@
         <v>207</v>
       </c>
       <c r="C211" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D211" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="D211" s="2" t="s">
-        <v>271</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>5</v>
@@ -6187,10 +6184,10 @@
         <v>208</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>5</v>
@@ -6203,10 +6200,10 @@
         <v>209</v>
       </c>
       <c r="C213" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D213" s="2" t="s">
         <v>273</v>
-      </c>
-      <c r="D213" s="2" t="s">
-        <v>274</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>5</v>
@@ -6219,10 +6216,10 @@
         <v>210</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>5</v>
@@ -6235,10 +6232,10 @@
         <v>211</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E215" s="1" t="s">
         <v>5</v>
@@ -6251,10 +6248,10 @@
         <v>212</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>5</v>
@@ -6267,10 +6264,10 @@
         <v>213</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>5</v>
@@ -6283,10 +6280,10 @@
         <v>214</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E218" s="1" t="s">
         <v>5</v>
@@ -6299,10 +6296,10 @@
         <v>215</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>5</v>
@@ -6315,10 +6312,10 @@
         <v>216</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>5</v>
@@ -6331,10 +6328,10 @@
         <v>217</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>5</v>
@@ -6347,10 +6344,10 @@
         <v>218</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>5</v>
@@ -6363,10 +6360,10 @@
         <v>219</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>5</v>
@@ -6379,10 +6376,10 @@
         <v>220</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>5</v>
@@ -6395,10 +6392,10 @@
         <v>221</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>5</v>
@@ -6411,10 +6408,10 @@
         <v>222</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>5</v>
@@ -6427,10 +6424,10 @@
         <v>223</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>5</v>
@@ -6443,10 +6440,10 @@
         <v>224</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>5</v>
@@ -6459,10 +6456,10 @@
         <v>225</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>5</v>
@@ -6475,10 +6472,10 @@
         <v>226</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>5</v>
@@ -6491,10 +6488,10 @@
         <v>227</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>5</v>
@@ -6507,10 +6504,10 @@
         <v>228</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>5</v>
@@ -6523,10 +6520,10 @@
         <v>229</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>5</v>
@@ -6539,10 +6536,10 @@
         <v>230</v>
       </c>
       <c r="C234" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D234" s="2" t="s">
         <v>295</v>
-      </c>
-      <c r="D234" s="2" t="s">
-        <v>296</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>5</v>
@@ -6555,10 +6552,10 @@
         <v>231</v>
       </c>
       <c r="C235" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D235" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="D235" s="2" t="s">
-        <v>298</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>5</v>
@@ -6571,10 +6568,10 @@
         <v>232</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>5</v>
@@ -6587,10 +6584,10 @@
         <v>233</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>5</v>
@@ -6603,10 +6600,10 @@
         <v>234</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>5</v>
@@ -6619,10 +6616,10 @@
         <v>235</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>5</v>
@@ -6635,10 +6632,10 @@
         <v>236</v>
       </c>
       <c r="C240" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="D240" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="D240" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="E240" s="1" t="s">
         <v>5</v>
@@ -6651,10 +6648,10 @@
         <v>237</v>
       </c>
       <c r="C241" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D241" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="D241" s="2" t="s">
-        <v>306</v>
       </c>
       <c r="E241" s="1" t="s">
         <v>5</v>
@@ -6667,10 +6664,10 @@
         <v>238</v>
       </c>
       <c r="C242" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D242" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="D242" s="2" t="s">
-        <v>308</v>
       </c>
       <c r="E242" s="1" t="s">
         <v>5</v>
@@ -6683,10 +6680,10 @@
         <v>239</v>
       </c>
       <c r="C243" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D243" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="D243" s="2" t="s">
-        <v>310</v>
       </c>
       <c r="E243" s="1" t="s">
         <v>5</v>
@@ -6699,7 +6696,7 @@
         <v>240</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>5</v>
@@ -6715,10 +6712,10 @@
         <v>241</v>
       </c>
       <c r="C245" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="D245" s="2" t="s">
         <v>312</v>
-      </c>
-      <c r="D245" s="2" t="s">
-        <v>313</v>
       </c>
       <c r="E245" s="1" t="s">
         <v>5</v>
@@ -6731,10 +6728,10 @@
         <v>242</v>
       </c>
       <c r="C246" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D246" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="D246" s="2" t="s">
-        <v>315</v>
       </c>
       <c r="E246" s="1" t="s">
         <v>5</v>
@@ -6747,10 +6744,10 @@
         <v>243</v>
       </c>
       <c r="C247" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D247" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="D247" s="2" t="s">
-        <v>317</v>
       </c>
       <c r="E247" s="1" t="s">
         <v>5</v>
@@ -6763,10 +6760,10 @@
         <v>244</v>
       </c>
       <c r="C248" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D248" s="2" t="s">
         <v>318</v>
-      </c>
-      <c r="D248" s="2" t="s">
-        <v>319</v>
       </c>
       <c r="E248" s="1" t="s">
         <v>5</v>
@@ -6779,10 +6776,10 @@
         <v>245</v>
       </c>
       <c r="C249" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="D249" s="2" t="s">
         <v>320</v>
-      </c>
-      <c r="D249" s="2" t="s">
-        <v>321</v>
       </c>
       <c r="E249" s="1" t="s">
         <v>5</v>
@@ -6795,10 +6792,10 @@
         <v>246</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>5</v>
@@ -6811,10 +6808,10 @@
         <v>247</v>
       </c>
       <c r="C251" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="D251" s="2" t="s">
         <v>323</v>
-      </c>
-      <c r="D251" s="2" t="s">
-        <v>324</v>
       </c>
       <c r="E251" s="1" t="s">
         <v>5</v>
@@ -6827,10 +6824,10 @@
         <v>248</v>
       </c>
       <c r="C252" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D252" s="2" t="s">
         <v>325</v>
-      </c>
-      <c r="D252" s="2" t="s">
-        <v>326</v>
       </c>
       <c r="E252" s="1" t="s">
         <v>5</v>
@@ -6843,10 +6840,10 @@
         <v>249</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E253" s="1" t="s">
         <v>5</v>
@@ -6859,10 +6856,10 @@
         <v>250</v>
       </c>
       <c r="C254" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="D254" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="D254" s="2" t="s">
-        <v>328</v>
       </c>
       <c r="E254" s="1" t="s">
         <v>5</v>
@@ -6875,10 +6872,10 @@
         <v>251</v>
       </c>
       <c r="C255" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="D255" s="2" t="s">
         <v>329</v>
-      </c>
-      <c r="D255" s="2" t="s">
-        <v>330</v>
       </c>
       <c r="E255" s="1" t="s">
         <v>5</v>
@@ -6891,10 +6888,10 @@
         <v>252</v>
       </c>
       <c r="C256" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="D256" s="2" t="s">
         <v>331</v>
-      </c>
-      <c r="D256" s="2" t="s">
-        <v>332</v>
       </c>
       <c r="E256" s="2">
         <v>5440099376763</v>
@@ -6907,10 +6904,10 @@
         <v>253</v>
       </c>
       <c r="C257" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D257" s="2" t="s">
         <v>333</v>
-      </c>
-      <c r="D257" s="2" t="s">
-        <v>334</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>5</v>
@@ -6923,10 +6920,10 @@
         <v>254</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E258" s="1" t="s">
         <v>5</v>
@@ -6939,10 +6936,10 @@
         <v>255</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E259" s="1" t="s">
         <v>5</v>
@@ -6955,10 +6952,10 @@
         <v>256</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E260" s="1" t="s">
         <v>5</v>
@@ -6971,10 +6968,10 @@
         <v>257</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E261" s="1" t="s">
         <v>5</v>
@@ -6987,10 +6984,10 @@
         <v>258</v>
       </c>
       <c r="C262" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D262" s="2" t="s">
         <v>338</v>
-      </c>
-      <c r="D262" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="E262" s="1" t="s">
         <v>5</v>
@@ -7003,10 +7000,10 @@
         <v>259</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E263" s="1" t="s">
         <v>5</v>
@@ -7019,10 +7016,10 @@
         <v>260</v>
       </c>
       <c r="C264" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D264" s="2" t="s">
         <v>341</v>
-      </c>
-      <c r="D264" s="2" t="s">
-        <v>342</v>
       </c>
       <c r="E264" s="1" t="s">
         <v>5</v>
@@ -7035,10 +7032,10 @@
         <v>261</v>
       </c>
       <c r="C265" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D265" s="2" t="s">
         <v>343</v>
-      </c>
-      <c r="D265" s="2" t="s">
-        <v>344</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>5</v>
@@ -7051,10 +7048,10 @@
         <v>262</v>
       </c>
       <c r="C266" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D266" s="2" t="s">
         <v>345</v>
-      </c>
-      <c r="D266" s="2" t="s">
-        <v>346</v>
       </c>
       <c r="E266" s="2" t="s">
         <v>5</v>
@@ -7067,13 +7064,13 @@
         <v>263</v>
       </c>
       <c r="C267" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D267" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E267" s="2" t="s">
         <v>347</v>
-      </c>
-      <c r="D267" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E267" s="2" t="s">
-        <v>348</v>
       </c>
       <c r="F267" s="3"/>
     </row>
@@ -7083,10 +7080,10 @@
         <v>264</v>
       </c>
       <c r="C268" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D268" s="2" t="s">
         <v>349</v>
-      </c>
-      <c r="D268" s="2" t="s">
-        <v>350</v>
       </c>
       <c r="E268" s="2" t="s">
         <v>5</v>
@@ -7099,10 +7096,10 @@
         <v>265</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E269" s="2" t="s">
         <v>5</v>
@@ -7115,10 +7112,10 @@
         <v>266</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E270" s="2" t="s">
         <v>5</v>
@@ -7131,10 +7128,10 @@
         <v>267</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E271" s="2" t="s">
         <v>5</v>
@@ -7147,10 +7144,10 @@
         <v>268</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>5</v>
@@ -7163,10 +7160,10 @@
         <v>269</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E273" s="2" t="s">
         <v>5</v>
@@ -7179,10 +7176,10 @@
         <v>270</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E274" s="2" t="s">
         <v>5</v>
@@ -7195,10 +7192,10 @@
         <v>271</v>
       </c>
       <c r="C275" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="D275" s="2" t="s">
         <v>357</v>
-      </c>
-      <c r="D275" s="2" t="s">
-        <v>358</v>
       </c>
       <c r="E275" s="2" t="s">
         <v>5</v>
@@ -7211,10 +7208,10 @@
         <v>272</v>
       </c>
       <c r="C276" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D276" s="2" t="s">
         <v>359</v>
-      </c>
-      <c r="D276" s="2" t="s">
-        <v>360</v>
       </c>
       <c r="E276" s="2" t="s">
         <v>5</v>
@@ -7227,10 +7224,10 @@
         <v>273</v>
       </c>
       <c r="C277" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="D277" s="2" t="s">
         <v>361</v>
-      </c>
-      <c r="D277" s="2" t="s">
-        <v>362</v>
       </c>
       <c r="E277" s="2" t="s">
         <v>5</v>
@@ -7243,13 +7240,13 @@
         <v>274</v>
       </c>
       <c r="C278" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E278" s="2" t="s">
         <v>363</v>
-      </c>
-      <c r="D278" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E278" s="2" t="s">
-        <v>364</v>
       </c>
       <c r="F278" s="3"/>
     </row>
@@ -7259,10 +7256,10 @@
         <v>275</v>
       </c>
       <c r="C279" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D279" s="2" t="s">
         <v>365</v>
-      </c>
-      <c r="D279" s="2" t="s">
-        <v>366</v>
       </c>
       <c r="E279" s="2" t="s">
         <v>5</v>
@@ -7275,10 +7272,10 @@
         <v>276</v>
       </c>
       <c r="C280" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="D280" s="2" t="s">
         <v>367</v>
-      </c>
-      <c r="D280" s="2" t="s">
-        <v>368</v>
       </c>
       <c r="E280" s="2" t="s">
         <v>5</v>
@@ -7291,10 +7288,10 @@
         <v>277</v>
       </c>
       <c r="C281" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="D281" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="D281" s="2" t="s">
-        <v>370</v>
       </c>
       <c r="E281" s="2" t="s">
         <v>5</v>
@@ -7307,10 +7304,10 @@
         <v>278</v>
       </c>
       <c r="C282" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D282" s="2" t="s">
         <v>371</v>
-      </c>
-      <c r="D282" s="2" t="s">
-        <v>372</v>
       </c>
       <c r="E282" s="2" t="s">
         <v>5</v>
@@ -7323,10 +7320,10 @@
         <v>279</v>
       </c>
       <c r="C283" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="D283" s="2" t="s">
         <v>373</v>
-      </c>
-      <c r="D283" s="2" t="s">
-        <v>374</v>
       </c>
       <c r="E283" s="2" t="s">
         <v>5</v>
@@ -7339,10 +7336,10 @@
         <v>280</v>
       </c>
       <c r="C284" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D284" s="2" t="s">
         <v>375</v>
-      </c>
-      <c r="D284" s="2" t="s">
-        <v>376</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>5</v>
@@ -7355,10 +7352,10 @@
         <v>281</v>
       </c>
       <c r="C285" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="D285" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="D285" s="2" t="s">
-        <v>378</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>5</v>
@@ -7371,10 +7368,10 @@
         <v>282</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E286" s="1" t="s">
         <v>5</v>
@@ -7387,10 +7384,10 @@
         <v>283</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E287" s="1" t="s">
         <v>5</v>
@@ -7403,10 +7400,10 @@
         <v>284</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E288" s="1" t="s">
         <v>5</v>
@@ -7419,10 +7416,10 @@
         <v>285</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E289" s="1" t="s">
         <v>5</v>
@@ -7435,10 +7432,10 @@
         <v>286</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E290" s="1" t="s">
         <v>5</v>
@@ -7451,10 +7448,10 @@
         <v>287</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>5</v>
@@ -7467,10 +7464,10 @@
         <v>288</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>5</v>
@@ -7483,10 +7480,10 @@
         <v>289</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>5</v>
@@ -7499,10 +7496,10 @@
         <v>290</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>5</v>
@@ -7515,10 +7512,10 @@
         <v>291</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>5</v>
@@ -7531,10 +7528,10 @@
         <v>292</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E296" s="1" t="s">
         <v>5</v>
@@ -7547,10 +7544,10 @@
         <v>293</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>5</v>
@@ -7563,10 +7560,10 @@
         <v>294</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>5</v>
@@ -7579,10 +7576,10 @@
         <v>295</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E299" s="1" t="s">
         <v>5</v>
@@ -7595,10 +7592,10 @@
         <v>296</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E300" s="1" t="s">
         <v>5</v>
@@ -7611,10 +7608,10 @@
         <v>297</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E301" s="1" t="s">
         <v>5</v>
@@ -7627,10 +7624,10 @@
         <v>298</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E302" s="1" t="s">
         <v>5</v>
@@ -7643,10 +7640,10 @@
         <v>299</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E303" s="1" t="s">
         <v>5</v>
@@ -7659,10 +7656,10 @@
         <v>300</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E304" s="1" t="s">
         <v>5</v>
@@ -7675,10 +7672,10 @@
         <v>301</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E305" s="1" t="s">
         <v>5</v>
@@ -7691,10 +7688,10 @@
         <v>302</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E306" s="1" t="s">
         <v>5</v>
@@ -7707,10 +7704,10 @@
         <v>303</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E307" s="1" t="s">
         <v>5</v>
@@ -7723,10 +7720,10 @@
         <v>304</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E308" s="1" t="s">
         <v>5</v>
@@ -7739,10 +7736,10 @@
         <v>305</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E309" s="1" t="s">
         <v>5</v>
@@ -7755,10 +7752,10 @@
         <v>306</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E310" s="1" t="s">
         <v>5</v>
@@ -7771,10 +7768,10 @@
         <v>307</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E311" s="1" t="s">
         <v>5</v>
@@ -7787,10 +7784,10 @@
         <v>308</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E312" s="1" t="s">
         <v>5</v>
@@ -7803,10 +7800,10 @@
         <v>309</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E313" s="1" t="s">
         <v>5</v>
@@ -7819,10 +7816,10 @@
         <v>310</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E314" s="1" t="s">
         <v>5</v>
@@ -7835,10 +7832,10 @@
         <v>311</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E315" s="1" t="s">
         <v>5</v>
@@ -7851,10 +7848,10 @@
         <v>312</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E316" s="1" t="s">
         <v>5</v>
@@ -7867,10 +7864,10 @@
         <v>313</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E317" s="1" t="s">
         <v>5</v>
@@ -7883,10 +7880,10 @@
         <v>314</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E318" s="1" t="s">
         <v>5</v>
@@ -7899,10 +7896,10 @@
         <v>315</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E319" s="1" t="s">
         <v>5</v>
@@ -7915,10 +7912,10 @@
         <v>316</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>5</v>
@@ -7931,10 +7928,10 @@
         <v>317</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E321" s="1" t="s">
         <v>5</v>
@@ -7947,10 +7944,10 @@
         <v>318</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E322" s="1" t="s">
         <v>5</v>
@@ -7963,10 +7960,10 @@
         <v>319</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E323" s="1" t="s">
         <v>5</v>
@@ -7979,10 +7976,10 @@
         <v>320</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E324" s="1" t="s">
         <v>5</v>
@@ -7995,10 +7992,10 @@
         <v>321</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E325" s="1" t="s">
         <v>5</v>
@@ -8011,10 +8008,10 @@
         <v>322</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E326" s="1" t="s">
         <v>5</v>
@@ -8027,10 +8024,10 @@
         <v>323</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E327" s="1" t="s">
         <v>5</v>
@@ -8043,10 +8040,10 @@
         <v>324</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>5</v>
@@ -8059,10 +8056,10 @@
         <v>325</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>5</v>
@@ -8075,10 +8072,10 @@
         <v>326</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>5</v>
@@ -8091,10 +8088,10 @@
         <v>327</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E331" s="1" t="s">
         <v>5</v>
@@ -8107,10 +8104,10 @@
         <v>328</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>5</v>
@@ -8123,10 +8120,10 @@
         <v>329</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>5</v>
@@ -8139,10 +8136,10 @@
         <v>330</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E334" s="1" t="s">
         <v>5</v>
@@ -8155,10 +8152,10 @@
         <v>331</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E335" s="1" t="s">
         <v>5</v>
@@ -8171,10 +8168,10 @@
         <v>332</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E336" s="1" t="s">
         <v>5</v>
@@ -8187,10 +8184,10 @@
         <v>333</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E337" s="1" t="s">
         <v>5</v>
@@ -8203,10 +8200,10 @@
         <v>334</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E338" s="1" t="s">
         <v>5</v>
@@ -8219,10 +8216,10 @@
         <v>335</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E339" s="1" t="s">
         <v>5</v>
@@ -8235,10 +8232,10 @@
         <v>336</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E340" s="1" t="s">
         <v>5</v>
@@ -8251,10 +8248,10 @@
         <v>337</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>5</v>
@@ -8267,10 +8264,10 @@
         <v>338</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E342" s="1" t="s">
         <v>5</v>
@@ -8283,10 +8280,10 @@
         <v>339</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E343" s="1" t="s">
         <v>5</v>
@@ -8299,10 +8296,10 @@
         <v>340</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E344" s="1" t="s">
         <v>5</v>
@@ -8315,10 +8312,10 @@
         <v>341</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E345" s="1" t="s">
         <v>5</v>
@@ -8331,10 +8328,10 @@
         <v>342</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E346" s="1" t="s">
         <v>5</v>
@@ -8347,10 +8344,10 @@
         <v>343</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E347" s="1" t="s">
         <v>5</v>
@@ -8363,10 +8360,10 @@
         <v>344</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>5</v>
@@ -8379,10 +8376,10 @@
         <v>345</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E349" s="1" t="s">
         <v>5</v>
@@ -8395,10 +8392,10 @@
         <v>346</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>5</v>
@@ -8411,10 +8408,10 @@
         <v>347</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E351" s="1" t="s">
         <v>5</v>
@@ -8427,10 +8424,10 @@
         <v>348</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E352" s="1" t="s">
         <v>5</v>
@@ -8443,10 +8440,10 @@
         <v>349</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E353" s="1" t="s">
         <v>5</v>
@@ -8459,10 +8456,10 @@
         <v>350</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E354" s="1" t="s">
         <v>5</v>
@@ -8475,10 +8472,10 @@
         <v>351</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E355" s="1" t="s">
         <v>5</v>
@@ -8491,10 +8488,10 @@
         <v>352</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E356" s="1" t="s">
         <v>5</v>
@@ -8507,10 +8504,10 @@
         <v>353</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E357" s="1" t="s">
         <v>5</v>
@@ -8523,10 +8520,10 @@
         <v>354</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E358" s="1" t="s">
         <v>5</v>
@@ -8539,10 +8536,10 @@
         <v>355</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E359" s="1" t="s">
         <v>5</v>
@@ -8555,10 +8552,10 @@
         <v>356</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E360" s="1" t="s">
         <v>5</v>
@@ -8571,10 +8568,10 @@
         <v>357</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E361" s="1" t="s">
         <v>5</v>
@@ -8587,10 +8584,10 @@
         <v>358</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E362" s="1" t="s">
         <v>5</v>
@@ -8603,10 +8600,10 @@
         <v>359</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E363" s="1" t="s">
         <v>5</v>
@@ -8619,10 +8616,10 @@
         <v>360</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E364" s="1" t="s">
         <v>5</v>
@@ -8635,10 +8632,10 @@
         <v>361</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E365" s="1" t="s">
         <v>5</v>
@@ -8651,10 +8648,10 @@
         <v>362</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>5</v>
@@ -8667,10 +8664,10 @@
         <v>363</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E367" s="1" t="s">
         <v>5</v>
@@ -8683,10 +8680,10 @@
         <v>364</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E368" s="1" t="s">
         <v>5</v>
@@ -8699,10 +8696,10 @@
         <v>365</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D369" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E369" s="1" t="s">
         <v>5</v>
@@ -8715,10 +8712,10 @@
         <v>366</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D370" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E370" s="1" t="s">
         <v>5</v>
@@ -8731,10 +8728,10 @@
         <v>367</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E371" s="1" t="s">
         <v>5</v>
@@ -8747,10 +8744,10 @@
         <v>368</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D372" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E372" s="1" t="s">
         <v>5</v>
@@ -8763,10 +8760,10 @@
         <v>369</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E373" s="1" t="s">
         <v>5</v>
@@ -8779,10 +8776,10 @@
         <v>370</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D374" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E374" s="1" t="s">
         <v>5</v>
@@ -8795,10 +8792,10 @@
         <v>371</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E375" s="1" t="s">
         <v>5</v>
@@ -8811,10 +8808,10 @@
         <v>372</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E376" s="1" t="s">
         <v>5</v>
@@ -8827,10 +8824,10 @@
         <v>373</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E377" s="1" t="s">
         <v>5</v>
@@ -8843,10 +8840,10 @@
         <v>374</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D378" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E378" s="1" t="s">
         <v>5</v>
@@ -8859,10 +8856,10 @@
         <v>375</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E379" s="1" t="s">
         <v>5</v>
@@ -8875,10 +8872,10 @@
         <v>376</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D380" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E380" s="1" t="s">
         <v>5</v>
@@ -8891,10 +8888,10 @@
         <v>377</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E381" s="1" t="s">
         <v>5</v>
@@ -8907,10 +8904,10 @@
         <v>378</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D382" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E382" s="1" t="s">
         <v>5</v>
@@ -8923,10 +8920,10 @@
         <v>379</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D383" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E383" s="1" t="s">
         <v>5</v>
@@ -8939,10 +8936,10 @@
         <v>380</v>
       </c>
       <c r="C384" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="D384" s="2" t="s">
         <v>477</v>
-      </c>
-      <c r="D384" s="2" t="s">
-        <v>478</v>
       </c>
       <c r="E384" s="1" t="s">
         <v>5</v>
@@ -8955,10 +8952,10 @@
         <v>381</v>
       </c>
       <c r="C385" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="D385" s="2" t="s">
         <v>479</v>
-      </c>
-      <c r="D385" s="2" t="s">
-        <v>480</v>
       </c>
       <c r="E385" s="1" t="s">
         <v>5</v>
@@ -8971,10 +8968,10 @@
         <v>382</v>
       </c>
       <c r="C386" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="D386" s="2" t="s">
         <v>481</v>
-      </c>
-      <c r="D386" s="2" t="s">
-        <v>482</v>
       </c>
       <c r="E386" s="1" t="s">
         <v>5</v>
@@ -8987,10 +8984,10 @@
         <v>383</v>
       </c>
       <c r="C387" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D387" s="2" t="s">
         <v>483</v>
-      </c>
-      <c r="D387" s="2" t="s">
-        <v>484</v>
       </c>
       <c r="E387" s="1" t="s">
         <v>5</v>
@@ -9003,10 +9000,10 @@
         <v>384</v>
       </c>
       <c r="C388" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="D388" s="2" t="s">
         <v>485</v>
-      </c>
-      <c r="D388" s="2" t="s">
-        <v>486</v>
       </c>
       <c r="E388" s="1" t="s">
         <v>5</v>
@@ -9019,10 +9016,10 @@
         <v>385</v>
       </c>
       <c r="C389" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="D389" s="2" t="s">
         <v>487</v>
-      </c>
-      <c r="D389" s="2" t="s">
-        <v>488</v>
       </c>
       <c r="E389" s="1" t="s">
         <v>5</v>
@@ -9035,10 +9032,10 @@
         <v>386</v>
       </c>
       <c r="C390" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="D390" s="2" t="s">
         <v>489</v>
-      </c>
-      <c r="D390" s="2" t="s">
-        <v>490</v>
       </c>
       <c r="E390" s="1" t="s">
         <v>5</v>
@@ -9051,10 +9048,10 @@
         <v>387</v>
       </c>
       <c r="C391" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D391" s="2" t="s">
         <v>491</v>
-      </c>
-      <c r="D391" s="2" t="s">
-        <v>492</v>
       </c>
       <c r="E391" s="1" t="s">
         <v>5</v>
@@ -9067,10 +9064,10 @@
         <v>388</v>
       </c>
       <c r="C392" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="D392" s="2" t="s">
         <v>493</v>
-      </c>
-      <c r="D392" s="2" t="s">
-        <v>494</v>
       </c>
       <c r="E392" s="1" t="s">
         <v>5</v>
@@ -9083,10 +9080,10 @@
         <v>389</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E393" s="1" t="s">
         <v>5</v>
@@ -9099,10 +9096,10 @@
         <v>390</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E394" s="1" t="s">
         <v>5</v>
@@ -9115,10 +9112,10 @@
         <v>391</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D395" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E395" s="1" t="s">
         <v>5</v>
@@ -9131,10 +9128,10 @@
         <v>392</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E396" s="1" t="s">
         <v>5</v>
@@ -9147,10 +9144,10 @@
         <v>393</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E397" s="2" t="s">
         <v>5</v>
@@ -9163,10 +9160,10 @@
         <v>394</v>
       </c>
       <c r="C398" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D398" s="2" t="s">
         <v>500</v>
-      </c>
-      <c r="D398" s="2" t="s">
-        <v>501</v>
       </c>
       <c r="E398" s="2" t="s">
         <v>5</v>
@@ -9179,13 +9176,13 @@
         <v>395</v>
       </c>
       <c r="C399" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="D399" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E399" s="2" t="s">
         <v>502</v>
-      </c>
-      <c r="D399" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E399" s="2" t="s">
-        <v>503</v>
       </c>
       <c r="F399" s="3"/>
     </row>
@@ -9195,10 +9192,10 @@
         <v>396</v>
       </c>
       <c r="C400" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="D400" s="2" t="s">
         <v>504</v>
-      </c>
-      <c r="D400" s="2" t="s">
-        <v>505</v>
       </c>
       <c r="E400" s="2" t="s">
         <v>5</v>
@@ -9211,10 +9208,10 @@
         <v>397</v>
       </c>
       <c r="C401" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="D401" s="2" t="s">
         <v>506</v>
-      </c>
-      <c r="D401" s="2" t="s">
-        <v>507</v>
       </c>
       <c r="E401" s="2" t="s">
         <v>5</v>
@@ -9227,10 +9224,10 @@
         <v>398</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E402" s="2" t="s">
         <v>5</v>
@@ -9243,10 +9240,10 @@
         <v>399</v>
       </c>
       <c r="C403" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="D403" s="2" t="s">
         <v>509</v>
-      </c>
-      <c r="D403" s="2" t="s">
-        <v>510</v>
       </c>
       <c r="E403" s="2" t="s">
         <v>5</v>
@@ -9259,10 +9256,10 @@
         <v>400</v>
       </c>
       <c r="C404" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="D404" s="2" t="s">
         <v>511</v>
-      </c>
-      <c r="D404" s="2" t="s">
-        <v>512</v>
       </c>
       <c r="E404" s="1" t="s">
         <v>5</v>
@@ -9275,10 +9272,10 @@
         <v>401</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D405" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E405" s="1" t="s">
         <v>5</v>
@@ -9291,10 +9288,10 @@
         <v>402</v>
       </c>
       <c r="C406" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="D406" s="2" t="s">
         <v>514</v>
-      </c>
-      <c r="D406" s="2" t="s">
-        <v>515</v>
       </c>
       <c r="E406" s="1" t="s">
         <v>5</v>
@@ -9307,570 +9304,570 @@
         <v>403</v>
       </c>
       <c r="C407" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="D407" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="D407" s="2" t="s">
-        <v>517</v>
-      </c>
       <c r="E407" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F407" s="3"/>
     </row>
-    <row r="408" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="408" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B408" s="2">
         <f t="shared" si="6"/>
         <v>404</v>
       </c>
       <c r="C408" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="D408" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="D408" s="2" t="s">
-        <v>519</v>
-      </c>
       <c r="E408" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F408" s="3"/>
     </row>
-    <row r="409" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="409" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B409" s="2">
         <f t="shared" si="6"/>
         <v>405</v>
       </c>
       <c r="C409" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="D409" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="D409" s="2" t="s">
-        <v>521</v>
-      </c>
       <c r="E409" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F409" s="3"/>
     </row>
-    <row r="410" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="410" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B410" s="2">
         <f t="shared" si="6"/>
         <v>406</v>
       </c>
       <c r="C410" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D410" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E410" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F410" s="3"/>
     </row>
-    <row r="411" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="411" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B411" s="2">
         <f t="shared" si="6"/>
         <v>407</v>
       </c>
       <c r="C411" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D411" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E411" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F411" s="3"/>
     </row>
-    <row r="412" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="412" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B412" s="2">
         <f t="shared" si="6"/>
         <v>408</v>
       </c>
       <c r="C412" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D412" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E412" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F412" s="3"/>
     </row>
-    <row r="413" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="413" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B413" s="2">
         <f t="shared" si="6"/>
         <v>409</v>
       </c>
       <c r="C413" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D413" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E413" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F413" s="3"/>
     </row>
-    <row r="414" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="414" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B414" s="2">
         <f t="shared" si="6"/>
         <v>410</v>
       </c>
       <c r="C414" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D414" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E414" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F414" s="3"/>
     </row>
-    <row r="415" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B415" s="2">
         <f t="shared" si="6"/>
         <v>411</v>
       </c>
       <c r="C415" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D415" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E415" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F415" s="3"/>
     </row>
-    <row r="416" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B416" s="2">
         <f t="shared" si="6"/>
         <v>412</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D416" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E416" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F416" s="3"/>
     </row>
-    <row r="417" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="417" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B417" s="2">
         <f t="shared" si="6"/>
         <v>413</v>
       </c>
       <c r="C417" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D417" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E417" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F417" s="3"/>
     </row>
-    <row r="418" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="418" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B418" s="2">
         <f t="shared" si="6"/>
         <v>414</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D418" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E418" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F418" s="3"/>
     </row>
-    <row r="419" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="419" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B419" s="2">
         <f t="shared" si="6"/>
         <v>415</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D419" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E419" s="7">
         <v>3277876126916</v>
       </c>
       <c r="F419" s="3"/>
     </row>
-    <row r="420" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="420" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B420" s="2">
         <f t="shared" si="6"/>
         <v>416</v>
       </c>
       <c r="C420" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D420" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E420" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F420" s="3"/>
     </row>
-    <row r="421" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="421" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B421" s="2">
         <f t="shared" si="6"/>
         <v>417</v>
       </c>
       <c r="C421" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D421" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E421" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F421" s="3"/>
     </row>
-    <row r="422" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="422" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B422" s="2">
         <f t="shared" si="6"/>
         <v>418</v>
       </c>
       <c r="C422" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D422" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E422" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F422" s="3"/>
     </row>
-    <row r="423" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="423" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B423" s="2">
         <f t="shared" si="6"/>
         <v>419</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D423" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E423" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F423" s="3"/>
     </row>
-    <row r="424" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="424" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B424" s="2">
         <f t="shared" si="6"/>
         <v>420</v>
       </c>
       <c r="C424" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D424" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E424" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F424" s="3"/>
     </row>
-    <row r="425" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="425" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B425" s="2">
         <f t="shared" si="6"/>
         <v>421</v>
       </c>
       <c r="C425" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D425" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E425" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F425" s="3"/>
     </row>
-    <row r="426" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="426" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B426" s="2">
         <f t="shared" si="6"/>
         <v>422</v>
       </c>
       <c r="C426" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D426" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E426" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F426" s="3"/>
     </row>
-    <row r="427" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="427" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B427" s="2">
         <f t="shared" si="6"/>
         <v>423</v>
       </c>
       <c r="C427" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D427" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E427" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F427" s="3"/>
     </row>
-    <row r="428" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="428" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B428" s="2">
         <f t="shared" si="6"/>
         <v>424</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D428" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E428" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F428" s="3"/>
     </row>
-    <row r="429" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="429" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B429" s="2">
         <f t="shared" si="6"/>
         <v>425</v>
       </c>
       <c r="C429" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E429" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F429" s="3"/>
     </row>
-    <row r="430" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="430" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B430" s="2">
         <f t="shared" si="6"/>
         <v>426</v>
       </c>
       <c r="C430" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D430" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E430" s="7">
         <v>3520255124113</v>
       </c>
       <c r="F430" s="3"/>
     </row>
-    <row r="431" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="431" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B431" s="2">
         <f t="shared" si="6"/>
         <v>427</v>
       </c>
       <c r="C431" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E431" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F431" s="3"/>
     </row>
-    <row r="432" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="432" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B432" s="2">
         <f t="shared" si="6"/>
         <v>428</v>
       </c>
       <c r="C432" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E432" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F432" s="3"/>
     </row>
-    <row r="433" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="433" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B433" s="2">
         <f t="shared" si="6"/>
         <v>429</v>
       </c>
       <c r="C433" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E433" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F433" s="3"/>
     </row>
-    <row r="434" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="434" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B434" s="2">
         <f t="shared" si="6"/>
         <v>430</v>
       </c>
       <c r="C434" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F434" s="3"/>
     </row>
-    <row r="435" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="435" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B435" s="2">
         <f t="shared" si="6"/>
         <v>431</v>
       </c>
       <c r="C435" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F435" s="3"/>
     </row>
-    <row r="436" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="436" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B436" s="2">
         <f t="shared" si="6"/>
         <v>432</v>
       </c>
       <c r="C436" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F436" s="3"/>
     </row>
-    <row r="437" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="437" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B437" s="2">
         <f t="shared" si="6"/>
         <v>433</v>
       </c>
       <c r="C437" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E437" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F437" s="3"/>
     </row>
-    <row r="438" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="438" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B438" s="2">
         <f t="shared" si="6"/>
         <v>434</v>
       </c>
       <c r="C438" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E438" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F438" s="3"/>
     </row>
-    <row r="439" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="439" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B439" s="2">
         <f t="shared" si="6"/>
         <v>435</v>
       </c>
       <c r="C439" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F439" s="3"/>
     </row>
-    <row r="440" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="440" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B440" s="2">
         <f t="shared" si="6"/>
         <v>436</v>
       </c>
       <c r="C440" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F440" s="3"/>
     </row>
-    <row r="441" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="441" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B441" s="2">
         <f t="shared" si="6"/>
         <v>437</v>
       </c>
       <c r="C441" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F441" s="3"/>
     </row>
-    <row r="442" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="442" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B442" s="2">
         <f t="shared" si="6"/>
         <v>438</v>
       </c>
       <c r="C442" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E442" s="1" t="s">
         <v>5</v>
@@ -9883,10 +9880,10 @@
         <v>439</v>
       </c>
       <c r="C443" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="D443" s="2" t="s">
         <v>554</v>
-      </c>
-      <c r="D443" s="2" t="s">
-        <v>555</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>5</v>
@@ -9899,10 +9896,10 @@
         <v>440</v>
       </c>
       <c r="C444" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="D444" s="2" t="s">
         <v>556</v>
-      </c>
-      <c r="D444" s="2" t="s">
-        <v>557</v>
       </c>
       <c r="E444" s="1" t="s">
         <v>5</v>
@@ -9915,10 +9912,10 @@
         <v>441</v>
       </c>
       <c r="C445" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="D445" s="2" t="s">
         <v>558</v>
-      </c>
-      <c r="D445" s="2" t="s">
-        <v>559</v>
       </c>
       <c r="E445" s="1" t="s">
         <v>5</v>
@@ -9931,10 +9928,10 @@
         <v>442</v>
       </c>
       <c r="C446" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D446" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E446" s="1" t="s">
         <v>5</v>
@@ -9947,10 +9944,10 @@
         <v>443</v>
       </c>
       <c r="C447" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E447" s="1" t="s">
         <v>5</v>
@@ -9963,10 +9960,10 @@
         <v>444</v>
       </c>
       <c r="C448" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E448" s="1" t="s">
         <v>5</v>
@@ -9979,10 +9976,10 @@
         <v>445</v>
       </c>
       <c r="C449" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E449" s="1" t="s">
         <v>5</v>
@@ -9995,10 +9992,10 @@
         <v>446</v>
       </c>
       <c r="C450" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E450" s="1" t="s">
         <v>5</v>
@@ -10011,10 +10008,10 @@
         <v>447</v>
       </c>
       <c r="C451" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E451" s="1" t="s">
         <v>5</v>
@@ -10027,10 +10024,10 @@
         <v>448</v>
       </c>
       <c r="C452" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E452" s="1" t="s">
         <v>5</v>
@@ -10043,10 +10040,10 @@
         <v>449</v>
       </c>
       <c r="C453" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>5</v>
@@ -10059,10 +10056,10 @@
         <v>450</v>
       </c>
       <c r="C454" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E454" s="1" t="s">
         <v>5</v>
@@ -10075,10 +10072,10 @@
         <v>451</v>
       </c>
       <c r="C455" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E455" s="1" t="s">
         <v>5</v>
@@ -10091,10 +10088,10 @@
         <v>452</v>
       </c>
       <c r="C456" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E456" s="1" t="s">
         <v>5</v>
@@ -10107,10 +10104,10 @@
         <v>453</v>
       </c>
       <c r="C457" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E457" s="1" t="s">
         <v>5</v>
@@ -10123,10 +10120,10 @@
         <v>454</v>
       </c>
       <c r="C458" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E458" s="1" t="s">
         <v>5</v>
@@ -10139,10 +10136,10 @@
         <v>455</v>
       </c>
       <c r="C459" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E459" s="1" t="s">
         <v>5</v>
@@ -10155,10 +10152,10 @@
         <v>456</v>
       </c>
       <c r="C460" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E460" s="1" t="s">
         <v>5</v>
@@ -10171,10 +10168,10 @@
         <v>457</v>
       </c>
       <c r="C461" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D461" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E461" s="1" t="s">
         <v>5</v>
@@ -10187,10 +10184,10 @@
         <v>458</v>
       </c>
       <c r="C462" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D462" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E462" s="1" t="s">
         <v>5</v>
@@ -10203,10 +10200,10 @@
         <v>459</v>
       </c>
       <c r="C463" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E463" s="1" t="s">
         <v>5</v>
@@ -10219,10 +10216,10 @@
         <v>460</v>
       </c>
       <c r="C464" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="D464" s="2" t="s">
         <v>578</v>
-      </c>
-      <c r="D464" s="2" t="s">
-        <v>579</v>
       </c>
       <c r="E464" s="1" t="s">
         <v>5</v>
@@ -10235,10 +10232,10 @@
         <v>461</v>
       </c>
       <c r="C465" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D465" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E465" s="1" t="s">
         <v>5</v>
@@ -10251,26 +10248,26 @@
         <v>462</v>
       </c>
       <c r="C466" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="D466" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="D466" s="2" t="s">
-        <v>582</v>
-      </c>
       <c r="E466" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F466" s="3"/>
     </row>
-    <row r="467" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B467" s="2">
         <f t="shared" si="7"/>
         <v>463</v>
       </c>
       <c r="C467" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="D467" s="2" t="s">
         <v>583</v>
-      </c>
-      <c r="D467" s="2" t="s">
-        <v>584</v>
       </c>
       <c r="E467" s="1" t="s">
         <v>5</v>
@@ -10283,10 +10280,10 @@
         <v>464</v>
       </c>
       <c r="C468" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="D468" s="2" t="s">
         <v>585</v>
-      </c>
-      <c r="D468" s="2" t="s">
-        <v>586</v>
       </c>
       <c r="E468" s="1" t="s">
         <v>5</v>
@@ -10299,7 +10296,7 @@
         <v>465</v>
       </c>
       <c r="C469" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D469" s="2" t="s">
         <v>114</v>
@@ -10315,10 +10312,10 @@
         <v>466</v>
       </c>
       <c r="C470" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="D470" s="2" t="s">
         <v>588</v>
-      </c>
-      <c r="D470" s="2" t="s">
-        <v>589</v>
       </c>
       <c r="E470" s="1" t="s">
         <v>5</v>
@@ -10331,7 +10328,7 @@
         <v>467</v>
       </c>
       <c r="C471" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D471" s="2" t="s">
         <v>114</v>
@@ -10347,7 +10344,7 @@
         <v>468</v>
       </c>
       <c r="C472" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D472" s="2" t="s">
         <v>114</v>
@@ -10363,10 +10360,10 @@
         <v>469</v>
       </c>
       <c r="C473" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D473" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E473" s="1" t="s">
         <v>5</v>
@@ -10379,10 +10376,10 @@
         <v>470</v>
       </c>
       <c r="C474" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D474" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E474" s="1" t="s">
         <v>5</v>
@@ -10395,10 +10392,10 @@
         <v>471</v>
       </c>
       <c r="C475" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="D475" s="2" t="s">
         <v>594</v>
-      </c>
-      <c r="D475" s="2" t="s">
-        <v>595</v>
       </c>
       <c r="E475" s="1" t="s">
         <v>5</v>
@@ -10411,13 +10408,13 @@
         <v>472</v>
       </c>
       <c r="C476" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="D476" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E476" s="2" t="s">
         <v>596</v>
-      </c>
-      <c r="D476" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E476" s="2" t="s">
-        <v>597</v>
       </c>
       <c r="F476" s="3"/>
     </row>
@@ -10427,10 +10424,10 @@
         <v>473</v>
       </c>
       <c r="C477" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="D477" s="2" t="s">
         <v>598</v>
-      </c>
-      <c r="D477" s="2" t="s">
-        <v>599</v>
       </c>
       <c r="E477" s="1" t="s">
         <v>5</v>
@@ -10443,10 +10440,10 @@
         <v>474</v>
       </c>
       <c r="C478" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D478" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E478" s="1" t="s">
         <v>5</v>
@@ -10459,10 +10456,10 @@
         <v>475</v>
       </c>
       <c r="C479" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D479" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E479" s="1" t="s">
         <v>5</v>
@@ -10475,10 +10472,10 @@
         <v>476</v>
       </c>
       <c r="C480" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D480" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E480" s="1" t="s">
         <v>5</v>
@@ -10491,10 +10488,10 @@
         <v>477</v>
       </c>
       <c r="C481" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D481" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E481" s="1" t="s">
         <v>5</v>
@@ -10507,10 +10504,10 @@
         <v>478</v>
       </c>
       <c r="C482" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D482" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E482" s="1" t="s">
         <v>5</v>
@@ -10523,10 +10520,10 @@
         <v>479</v>
       </c>
       <c r="C483" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D483" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E483" s="1" t="s">
         <v>5</v>
@@ -10539,10 +10536,10 @@
         <v>480</v>
       </c>
       <c r="C484" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D484" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E484" s="1" t="s">
         <v>5</v>
@@ -10555,10 +10552,10 @@
         <v>481</v>
       </c>
       <c r="C485" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D485" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E485" s="1" t="s">
         <v>5</v>
@@ -10571,10 +10568,10 @@
         <v>482</v>
       </c>
       <c r="C486" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D486" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E486" s="1" t="s">
         <v>5</v>
@@ -10587,10 +10584,10 @@
         <v>483</v>
       </c>
       <c r="C487" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D487" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E487" s="1" t="s">
         <v>5</v>
@@ -10603,10 +10600,10 @@
         <v>484</v>
       </c>
       <c r="C488" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D488" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E488" s="1" t="s">
         <v>5</v>
@@ -10619,10 +10616,10 @@
         <v>485</v>
       </c>
       <c r="C489" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D489" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E489" s="1" t="s">
         <v>5</v>
@@ -10635,10 +10632,10 @@
         <v>486</v>
       </c>
       <c r="C490" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D490" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E490" s="1" t="s">
         <v>5</v>
@@ -10651,10 +10648,10 @@
         <v>487</v>
       </c>
       <c r="C491" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D491" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E491" s="1" t="s">
         <v>5</v>
@@ -10667,10 +10664,10 @@
         <v>488</v>
       </c>
       <c r="C492" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D492" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E492" s="1" t="s">
         <v>5</v>
@@ -10683,10 +10680,10 @@
         <v>489</v>
       </c>
       <c r="C493" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D493" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E493" s="1" t="s">
         <v>5</v>
@@ -10699,10 +10696,10 @@
         <v>490</v>
       </c>
       <c r="C494" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D494" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E494" s="1" t="s">
         <v>5</v>
@@ -10715,10 +10712,10 @@
         <v>491</v>
       </c>
       <c r="C495" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D495" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E495" s="1" t="s">
         <v>5</v>
@@ -10731,10 +10728,10 @@
         <v>492</v>
       </c>
       <c r="C496" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="D496" s="2" t="s">
         <v>618</v>
-      </c>
-      <c r="D496" s="2" t="s">
-        <v>619</v>
       </c>
       <c r="E496" s="2" t="s">
         <v>5</v>
@@ -10747,13 +10744,13 @@
         <v>493</v>
       </c>
       <c r="C497" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="D497" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E497" s="2" t="s">
         <v>620</v>
-      </c>
-      <c r="D497" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E497" s="2" t="s">
-        <v>621</v>
       </c>
       <c r="F497" s="3"/>
     </row>
@@ -10763,10 +10760,10 @@
         <v>494</v>
       </c>
       <c r="C498" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="D498" s="2" t="s">
         <v>622</v>
-      </c>
-      <c r="D498" s="2" t="s">
-        <v>623</v>
       </c>
       <c r="E498" s="2" t="s">
         <v>5</v>
@@ -10779,10 +10776,10 @@
         <v>495</v>
       </c>
       <c r="C499" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="D499" s="2" t="s">
         <v>624</v>
-      </c>
-      <c r="D499" s="2" t="s">
-        <v>625</v>
       </c>
       <c r="E499" s="2" t="s">
         <v>5</v>
@@ -10795,13 +10792,13 @@
         <v>496</v>
       </c>
       <c r="C500" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="D500" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E500" s="2" t="s">
         <v>626</v>
-      </c>
-      <c r="D500" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E500" s="2" t="s">
-        <v>627</v>
       </c>
       <c r="F500" s="3"/>
     </row>
@@ -10811,10 +10808,10 @@
         <v>497</v>
       </c>
       <c r="C501" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="D501" s="2" t="s">
         <v>628</v>
-      </c>
-      <c r="D501" s="2" t="s">
-        <v>629</v>
       </c>
       <c r="E501" s="1" t="s">
         <v>5</v>
@@ -10827,10 +10824,10 @@
         <v>498</v>
       </c>
       <c r="C502" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="D502" s="2" t="s">
         <v>630</v>
-      </c>
-      <c r="D502" s="2" t="s">
-        <v>631</v>
       </c>
       <c r="E502" s="1" t="s">
         <v>5</v>
@@ -10843,10 +10840,10 @@
         <v>499</v>
       </c>
       <c r="C503" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="D503" s="2" t="s">
         <v>632</v>
-      </c>
-      <c r="D503" s="2" t="s">
-        <v>633</v>
       </c>
       <c r="E503" s="1" t="s">
         <v>5</v>
@@ -10859,10 +10856,10 @@
         <v>500</v>
       </c>
       <c r="C504" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D504" s="2" t="s">
         <v>634</v>
-      </c>
-      <c r="D504" s="2" t="s">
-        <v>635</v>
       </c>
       <c r="E504" s="1" t="s">
         <v>5</v>
@@ -10875,10 +10872,10 @@
         <v>501</v>
       </c>
       <c r="C505" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="D505" s="2" t="s">
         <v>636</v>
-      </c>
-      <c r="D505" s="2" t="s">
-        <v>637</v>
       </c>
       <c r="E505" s="1" t="s">
         <v>5</v>
@@ -10891,10 +10888,10 @@
         <v>502</v>
       </c>
       <c r="C506" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D506" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E506" s="1" t="s">
         <v>5</v>
@@ -10907,10 +10904,10 @@
         <v>503</v>
       </c>
       <c r="C507" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="D507" s="2" t="s">
         <v>639</v>
-      </c>
-      <c r="D507" s="2" t="s">
-        <v>640</v>
       </c>
       <c r="E507" s="1" t="s">
         <v>5</v>
@@ -10923,10 +10920,10 @@
         <v>504</v>
       </c>
       <c r="C508" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D508" s="2" t="s">
         <v>641</v>
-      </c>
-      <c r="D508" s="2" t="s">
-        <v>642</v>
       </c>
       <c r="E508" s="1" t="s">
         <v>5</v>
@@ -10939,10 +10936,10 @@
         <v>505</v>
       </c>
       <c r="C509" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="D509" s="2" t="s">
         <v>643</v>
-      </c>
-      <c r="D509" s="2" t="s">
-        <v>644</v>
       </c>
       <c r="E509" s="1" t="s">
         <v>5</v>
@@ -10955,10 +10952,10 @@
         <v>506</v>
       </c>
       <c r="C510" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="D510" s="2" t="s">
         <v>645</v>
-      </c>
-      <c r="D510" s="2" t="s">
-        <v>646</v>
       </c>
       <c r="E510" s="1" t="s">
         <v>5</v>
@@ -10971,10 +10968,10 @@
         <v>507</v>
       </c>
       <c r="C511" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D511" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E511" s="1" t="s">
         <v>5</v>
@@ -10987,10 +10984,10 @@
         <v>508</v>
       </c>
       <c r="C512" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="D512" s="2" t="s">
         <v>648</v>
-      </c>
-      <c r="D512" s="2" t="s">
-        <v>649</v>
       </c>
       <c r="E512" s="1" t="s">
         <v>5</v>
@@ -11003,10 +11000,10 @@
         <v>509</v>
       </c>
       <c r="C513" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="D513" s="2" t="s">
         <v>650</v>
-      </c>
-      <c r="D513" s="2" t="s">
-        <v>651</v>
       </c>
       <c r="E513" s="1" t="s">
         <v>5</v>
@@ -11019,10 +11016,10 @@
         <v>510</v>
       </c>
       <c r="C514" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="D514" s="2" t="s">
         <v>652</v>
-      </c>
-      <c r="D514" s="2" t="s">
-        <v>653</v>
       </c>
       <c r="E514" s="1" t="s">
         <v>5</v>
@@ -11035,10 +11032,10 @@
         <v>511</v>
       </c>
       <c r="C515" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D515" s="2" t="s">
         <v>654</v>
-      </c>
-      <c r="D515" s="2" t="s">
-        <v>655</v>
       </c>
       <c r="E515" s="1" t="s">
         <v>5</v>
@@ -11051,13 +11048,13 @@
         <v>512</v>
       </c>
       <c r="C516" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="D516" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E516" s="2" t="s">
         <v>656</v>
-      </c>
-      <c r="D516" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E516" s="2" t="s">
-        <v>657</v>
       </c>
       <c r="F516" s="3"/>
     </row>
@@ -11067,10 +11064,10 @@
         <v>513</v>
       </c>
       <c r="C517" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="D517" s="2" t="s">
         <v>658</v>
-      </c>
-      <c r="D517" s="2" t="s">
-        <v>659</v>
       </c>
       <c r="E517" s="1" t="s">
         <v>5</v>
@@ -11083,10 +11080,10 @@
         <v>514</v>
       </c>
       <c r="C518" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="D518" s="2" t="s">
         <v>660</v>
-      </c>
-      <c r="D518" s="2" t="s">
-        <v>661</v>
       </c>
       <c r="E518" s="1" t="s">
         <v>5</v>
@@ -11099,10 +11096,10 @@
         <v>515</v>
       </c>
       <c r="C519" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="D519" s="2" t="s">
         <v>662</v>
-      </c>
-      <c r="D519" s="2" t="s">
-        <v>663</v>
       </c>
       <c r="E519" s="1" t="s">
         <v>5</v>
@@ -11115,10 +11112,10 @@
         <v>516</v>
       </c>
       <c r="C520" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="D520" s="2" t="s">
         <v>664</v>
-      </c>
-      <c r="D520" s="2" t="s">
-        <v>665</v>
       </c>
       <c r="E520" s="1" t="s">
         <v>5</v>
@@ -11131,10 +11128,10 @@
         <v>517</v>
       </c>
       <c r="C521" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="D521" s="2" t="s">
         <v>666</v>
-      </c>
-      <c r="D521" s="2" t="s">
-        <v>667</v>
       </c>
       <c r="E521" s="1" t="s">
         <v>5</v>
@@ -11147,7 +11144,7 @@
         <v>518</v>
       </c>
       <c r="C522" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D522" s="2" t="s">
         <v>5</v>
@@ -11163,10 +11160,10 @@
         <v>519</v>
       </c>
       <c r="C523" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="D523" s="2" t="s">
         <v>669</v>
-      </c>
-      <c r="D523" s="2" t="s">
-        <v>670</v>
       </c>
       <c r="E523" s="1" t="s">
         <v>5</v>
@@ -11179,10 +11176,10 @@
         <v>520</v>
       </c>
       <c r="C524" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="D524" s="2" t="s">
         <v>671</v>
-      </c>
-      <c r="D524" s="2" t="s">
-        <v>672</v>
       </c>
       <c r="E524" s="1" t="s">
         <v>5</v>
@@ -11195,10 +11192,10 @@
         <v>521</v>
       </c>
       <c r="C525" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="D525" s="2" t="s">
         <v>673</v>
-      </c>
-      <c r="D525" s="2" t="s">
-        <v>674</v>
       </c>
       <c r="E525" s="1" t="s">
         <v>5</v>
@@ -11211,10 +11208,10 @@
         <v>522</v>
       </c>
       <c r="C526" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="D526" s="2" t="s">
         <v>675</v>
-      </c>
-      <c r="D526" s="2" t="s">
-        <v>676</v>
       </c>
       <c r="E526" s="1" t="s">
         <v>5</v>
@@ -11227,10 +11224,10 @@
         <v>523</v>
       </c>
       <c r="C527" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="D527" s="2" t="s">
         <v>677</v>
-      </c>
-      <c r="D527" s="2" t="s">
-        <v>678</v>
       </c>
       <c r="E527" s="1" t="s">
         <v>5</v>
@@ -11243,10 +11240,10 @@
         <v>524</v>
       </c>
       <c r="C528" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="D528" s="2" t="s">
         <v>679</v>
-      </c>
-      <c r="D528" s="2" t="s">
-        <v>680</v>
       </c>
       <c r="E528" s="1" t="s">
         <v>5</v>
@@ -11259,10 +11256,10 @@
         <v>525</v>
       </c>
       <c r="C529" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D529" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E529" s="1" t="s">
         <v>5</v>
@@ -11275,7 +11272,7 @@
         <v>526</v>
       </c>
       <c r="C530" s="1" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D530" s="2" t="s">
         <v>5</v>
@@ -11291,10 +11288,10 @@
         <v>527</v>
       </c>
       <c r="C531" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="D531" s="2" t="s">
         <v>683</v>
-      </c>
-      <c r="D531" s="2" t="s">
-        <v>684</v>
       </c>
       <c r="E531" s="1" t="s">
         <v>5</v>
@@ -11307,13 +11304,13 @@
         <v>528</v>
       </c>
       <c r="C532" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="D532" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="D532" s="2" t="s">
-        <v>686</v>
-      </c>
       <c r="E532" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="F532" s="3"/>
     </row>
@@ -11323,10 +11320,10 @@
         <v>529</v>
       </c>
       <c r="C533" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="D533" s="2" t="s">
         <v>687</v>
-      </c>
-      <c r="D533" s="2" t="s">
-        <v>688</v>
       </c>
       <c r="E533" s="1" t="s">
         <v>5</v>
@@ -11339,10 +11336,10 @@
         <v>530</v>
       </c>
       <c r="C534" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D534" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E534" s="1" t="s">
         <v>5</v>
@@ -11355,10 +11352,10 @@
         <v>531</v>
       </c>
       <c r="C535" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="D535" s="2" t="s">
         <v>690</v>
-      </c>
-      <c r="D535" s="2" t="s">
-        <v>691</v>
       </c>
       <c r="E535" s="1" t="s">
         <v>5</v>
@@ -11371,10 +11368,10 @@
         <v>532</v>
       </c>
       <c r="C536" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="D536" s="2" t="s">
         <v>692</v>
-      </c>
-      <c r="D536" s="2" t="s">
-        <v>693</v>
       </c>
       <c r="E536" s="1" t="s">
         <v>5</v>
@@ -11387,10 +11384,10 @@
         <v>533</v>
       </c>
       <c r="C537" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D537" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E537" s="1" t="s">
         <v>5</v>
@@ -11403,10 +11400,10 @@
         <v>534</v>
       </c>
       <c r="C538" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="D538" s="2" t="s">
         <v>695</v>
-      </c>
-      <c r="D538" s="2" t="s">
-        <v>696</v>
       </c>
       <c r="E538" s="1" t="s">
         <v>5</v>
@@ -11419,10 +11416,10 @@
         <v>535</v>
       </c>
       <c r="C539" s="1" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D539" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E539" s="1" t="s">
         <v>5</v>
@@ -11435,10 +11432,10 @@
         <v>536</v>
       </c>
       <c r="C540" s="1" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D540" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E540" s="1" t="s">
         <v>5</v>
@@ -11451,10 +11448,10 @@
         <v>537</v>
       </c>
       <c r="C541" s="1" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D541" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E541" s="1" t="s">
         <v>5</v>
@@ -11467,10 +11464,10 @@
         <v>538</v>
       </c>
       <c r="C542" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D542" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E542" s="1" t="s">
         <v>5</v>
@@ -11483,10 +11480,10 @@
         <v>539</v>
       </c>
       <c r="C543" s="1" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D543" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E543" s="1" t="s">
         <v>5</v>
@@ -11499,10 +11496,10 @@
         <v>540</v>
       </c>
       <c r="C544" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D544" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E544" s="1" t="s">
         <v>5</v>
@@ -11515,10 +11512,10 @@
         <v>541</v>
       </c>
       <c r="C545" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D545" s="2" t="s">
         <v>703</v>
-      </c>
-      <c r="D545" s="2" t="s">
-        <v>704</v>
       </c>
       <c r="E545" s="1" t="s">
         <v>5</v>
@@ -11531,13 +11528,13 @@
         <v>542</v>
       </c>
       <c r="C546" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="D546" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E546" s="2" t="s">
         <v>705</v>
-      </c>
-      <c r="D546" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E546" s="2" t="s">
-        <v>706</v>
       </c>
       <c r="F546" s="3"/>
     </row>
@@ -11547,13 +11544,13 @@
         <v>543</v>
       </c>
       <c r="C547" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="D547" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E547" s="2" t="s">
         <v>707</v>
-      </c>
-      <c r="D547" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E547" s="2" t="s">
-        <v>708</v>
       </c>
       <c r="F547" s="3"/>
     </row>
@@ -11563,93 +11560,93 @@
         <v>544</v>
       </c>
       <c r="C548" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="D548" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="D548" s="2" t="s">
-        <v>710</v>
-      </c>
       <c r="E548" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F548" s="3"/>
     </row>
-    <row r="549" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B549" s="2">
         <f t="shared" si="8"/>
         <v>545</v>
       </c>
       <c r="C549" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D549" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E549" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F549" s="3"/>
     </row>
-    <row r="550" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B550" s="2">
         <f t="shared" si="8"/>
         <v>546</v>
       </c>
       <c r="C550" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="D550" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="D550" s="2" t="s">
-        <v>713</v>
-      </c>
       <c r="E550" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F550" s="3"/>
     </row>
-    <row r="551" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B551" s="2">
         <f t="shared" si="8"/>
         <v>547</v>
       </c>
       <c r="C551" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D551" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E551" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F551" s="3"/>
     </row>
-    <row r="552" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B552" s="2">
         <f t="shared" si="8"/>
         <v>548</v>
       </c>
       <c r="C552" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="D552" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="D552" s="2" t="s">
-        <v>715</v>
-      </c>
       <c r="E552" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F552" s="3"/>
     </row>
-    <row r="553" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B553" s="2">
         <f t="shared" si="8"/>
         <v>549</v>
       </c>
       <c r="C553" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D553" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="E553" s="13" t="s">
         <v>799</v>
-      </c>
-      <c r="E553" s="13" t="s">
-        <v>800</v>
       </c>
       <c r="F553" s="3"/>
     </row>
@@ -11659,10 +11656,10 @@
         <v>550</v>
       </c>
       <c r="C554" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="D554" s="2" t="s">
         <v>717</v>
-      </c>
-      <c r="D554" s="2" t="s">
-        <v>718</v>
       </c>
       <c r="E554" s="1" t="s">
         <v>5</v>
@@ -11675,10 +11672,10 @@
         <v>551</v>
       </c>
       <c r="C555" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="D555" s="2" t="s">
         <v>719</v>
-      </c>
-      <c r="D555" s="2" t="s">
-        <v>720</v>
       </c>
       <c r="E555" s="1" t="s">
         <v>5</v>
@@ -11691,10 +11688,10 @@
         <v>552</v>
       </c>
       <c r="C556" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="D556" s="2" t="s">
         <v>721</v>
-      </c>
-      <c r="D556" s="2" t="s">
-        <v>722</v>
       </c>
       <c r="E556" s="1" t="s">
         <v>5</v>
@@ -11707,10 +11704,10 @@
         <v>553</v>
       </c>
       <c r="C557" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="D557" s="2" t="s">
         <v>723</v>
-      </c>
-      <c r="D557" s="2" t="s">
-        <v>724</v>
       </c>
       <c r="E557" s="1" t="s">
         <v>5</v>
@@ -11723,10 +11720,10 @@
         <v>554</v>
       </c>
       <c r="C558" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D558" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E558" s="1" t="s">
         <v>5</v>
@@ -11739,10 +11736,10 @@
         <v>555</v>
       </c>
       <c r="C559" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D559" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E559" s="1" t="s">
         <v>5</v>
@@ -11755,10 +11752,10 @@
         <v>556</v>
       </c>
       <c r="C560" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D560" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E560" s="1" t="s">
         <v>5</v>
@@ -11771,10 +11768,10 @@
         <v>557</v>
       </c>
       <c r="C561" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="D561" s="2" t="s">
         <v>728</v>
-      </c>
-      <c r="D561" s="2" t="s">
-        <v>729</v>
       </c>
       <c r="E561" s="1" t="s">
         <v>5</v>
@@ -11787,10 +11784,10 @@
         <v>558</v>
       </c>
       <c r="C562" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="D562" s="2" t="s">
         <v>730</v>
-      </c>
-      <c r="D562" s="2" t="s">
-        <v>731</v>
       </c>
       <c r="E562" s="1" t="s">
         <v>5</v>
@@ -11803,10 +11800,10 @@
         <v>559</v>
       </c>
       <c r="C563" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="D563" s="2" t="s">
         <v>732</v>
-      </c>
-      <c r="D563" s="2" t="s">
-        <v>733</v>
       </c>
       <c r="E563" s="1" t="s">
         <v>5</v>
@@ -11819,10 +11816,10 @@
         <v>560</v>
       </c>
       <c r="C564" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D564" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E564" s="1" t="s">
         <v>5</v>
@@ -11835,10 +11832,10 @@
         <v>561</v>
       </c>
       <c r="C565" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D565" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E565" s="1" t="s">
         <v>5</v>
@@ -11851,10 +11848,10 @@
         <v>562</v>
       </c>
       <c r="C566" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D566" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E566" s="1" t="s">
         <v>5</v>
@@ -11867,10 +11864,10 @@
         <v>563</v>
       </c>
       <c r="C567" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D567" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E567" s="1" t="s">
         <v>5</v>
@@ -11883,10 +11880,10 @@
         <v>564</v>
       </c>
       <c r="C568" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D568" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E568" s="1" t="s">
         <v>5</v>
@@ -11899,10 +11896,10 @@
         <v>565</v>
       </c>
       <c r="C569" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D569" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E569" s="1" t="s">
         <v>5</v>
@@ -11915,10 +11912,10 @@
         <v>566</v>
       </c>
       <c r="C570" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D570" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E570" s="1" t="s">
         <v>5</v>
@@ -11931,10 +11928,10 @@
         <v>567</v>
       </c>
       <c r="C571" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D571" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E571" s="1" t="s">
         <v>5</v>
@@ -11947,10 +11944,10 @@
         <v>568</v>
       </c>
       <c r="C572" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D572" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E572" s="1" t="s">
         <v>5</v>
@@ -11963,10 +11960,10 @@
         <v>569</v>
       </c>
       <c r="C573" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D573" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E573" s="1" t="s">
         <v>5</v>
@@ -11979,10 +11976,10 @@
         <v>570</v>
       </c>
       <c r="C574" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D574" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E574" s="1" t="s">
         <v>5</v>
@@ -11995,10 +11992,10 @@
         <v>571</v>
       </c>
       <c r="C575" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D575" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E575" s="1" t="s">
         <v>5</v>
@@ -12011,10 +12008,10 @@
         <v>572</v>
       </c>
       <c r="C576" s="1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D576" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E576" s="1" t="s">
         <v>5</v>
@@ -12027,10 +12024,10 @@
         <v>573</v>
       </c>
       <c r="C577" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="D577" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="D577" s="2" t="s">
-        <v>748</v>
       </c>
       <c r="E577" s="2" t="s">
         <v>5</v>
@@ -12043,10 +12040,10 @@
         <v>574</v>
       </c>
       <c r="C578" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="D578" s="2" t="s">
         <v>749</v>
-      </c>
-      <c r="D578" s="2" t="s">
-        <v>750</v>
       </c>
       <c r="E578" s="1" t="s">
         <v>5</v>
@@ -12059,10 +12056,10 @@
         <v>575</v>
       </c>
       <c r="C579" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="D579" s="2" t="s">
         <v>751</v>
-      </c>
-      <c r="D579" s="2" t="s">
-        <v>752</v>
       </c>
       <c r="E579" s="1" t="s">
         <v>5</v>
@@ -12075,10 +12072,10 @@
         <v>576</v>
       </c>
       <c r="C580" s="1" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D580" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="E580" s="1" t="s">
         <v>5</v>
@@ -12091,10 +12088,10 @@
         <v>577</v>
       </c>
       <c r="C581" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="D581" s="2" t="s">
         <v>754</v>
-      </c>
-      <c r="D581" s="2" t="s">
-        <v>755</v>
       </c>
       <c r="E581" s="1" t="s">
         <v>5</v>
@@ -12107,10 +12104,10 @@
         <v>578</v>
       </c>
       <c r="C582" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="D582" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="E582" s="7">
         <v>3520268948847</v>
@@ -12123,10 +12120,10 @@
         <v>579</v>
       </c>
       <c r="C583" s="1" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D583" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="E583" s="1" t="s">
         <v>5</v>
@@ -12139,10 +12136,10 @@
         <v>580</v>
       </c>
       <c r="C584" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="D584" s="2" t="s">
         <v>758</v>
-      </c>
-      <c r="D584" s="2" t="s">
-        <v>759</v>
       </c>
       <c r="E584" s="1" t="s">
         <v>5</v>
@@ -12155,10 +12152,10 @@
         <v>581</v>
       </c>
       <c r="C585" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="D585" s="2" t="s">
         <v>760</v>
-      </c>
-      <c r="D585" s="2" t="s">
-        <v>761</v>
       </c>
       <c r="E585" s="1" t="s">
         <v>5</v>
@@ -12171,10 +12168,10 @@
         <v>582</v>
       </c>
       <c r="C586" s="1" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D586" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="E586" s="1" t="s">
         <v>5</v>
@@ -12187,10 +12184,10 @@
         <v>583</v>
       </c>
       <c r="C587" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="D587" s="2" t="s">
         <v>763</v>
-      </c>
-      <c r="D587" s="2" t="s">
-        <v>764</v>
       </c>
       <c r="E587" s="1" t="s">
         <v>5</v>
@@ -12203,10 +12200,10 @@
         <v>584</v>
       </c>
       <c r="C588" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="D588" s="2" t="s">
         <v>765</v>
-      </c>
-      <c r="D588" s="2" t="s">
-        <v>766</v>
       </c>
       <c r="E588" s="1" t="s">
         <v>5</v>
@@ -12219,10 +12216,10 @@
         <v>585</v>
       </c>
       <c r="C589" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="D589" s="2" t="s">
         <v>767</v>
-      </c>
-      <c r="D589" s="2" t="s">
-        <v>768</v>
       </c>
       <c r="E589" s="1" t="s">
         <v>5</v>
@@ -12235,10 +12232,10 @@
         <v>586</v>
       </c>
       <c r="C590" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="D590" s="2" t="s">
         <v>769</v>
-      </c>
-      <c r="D590" s="2" t="s">
-        <v>770</v>
       </c>
       <c r="E590" s="1" t="s">
         <v>5</v>
@@ -12251,10 +12248,10 @@
         <v>587</v>
       </c>
       <c r="C591" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="D591" s="2" t="s">
         <v>771</v>
-      </c>
-      <c r="D591" s="2" t="s">
-        <v>772</v>
       </c>
       <c r="E591" s="1" t="s">
         <v>5</v>
@@ -12267,10 +12264,10 @@
         <v>588</v>
       </c>
       <c r="C592" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="D592" s="2" t="s">
         <v>773</v>
-      </c>
-      <c r="D592" s="2" t="s">
-        <v>774</v>
       </c>
       <c r="E592" s="1" t="s">
         <v>5</v>
@@ -12283,10 +12280,10 @@
         <v>589</v>
       </c>
       <c r="C593" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="D593" s="2" t="s">
         <v>775</v>
-      </c>
-      <c r="D593" s="2" t="s">
-        <v>776</v>
       </c>
       <c r="E593" s="1" t="s">
         <v>5</v>
@@ -12299,10 +12296,10 @@
         <v>590</v>
       </c>
       <c r="C594" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="D594" s="2" t="s">
         <v>777</v>
-      </c>
-      <c r="D594" s="2" t="s">
-        <v>778</v>
       </c>
       <c r="E594" s="1" t="s">
         <v>5</v>
@@ -12315,10 +12312,10 @@
         <v>591</v>
       </c>
       <c r="C595" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="D595" s="2" t="s">
         <v>779</v>
-      </c>
-      <c r="D595" s="2" t="s">
-        <v>780</v>
       </c>
       <c r="E595" s="1" t="s">
         <v>5</v>
@@ -12331,10 +12328,10 @@
         <v>592</v>
       </c>
       <c r="C596" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="D596" s="2" t="s">
         <v>781</v>
-      </c>
-      <c r="D596" s="2" t="s">
-        <v>782</v>
       </c>
       <c r="E596" s="1" t="s">
         <v>5</v>
@@ -12347,10 +12344,10 @@
         <v>593</v>
       </c>
       <c r="C597" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="D597" s="2" t="s">
         <v>783</v>
-      </c>
-      <c r="D597" s="2" t="s">
-        <v>784</v>
       </c>
       <c r="E597" s="1" t="s">
         <v>5</v>
@@ -12363,10 +12360,10 @@
         <v>594</v>
       </c>
       <c r="C598" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="D598" s="2" t="s">
         <v>785</v>
-      </c>
-      <c r="D598" s="2" t="s">
-        <v>786</v>
       </c>
       <c r="E598" s="1" t="s">
         <v>5</v>
@@ -12378,10 +12375,10 @@
         <v>595</v>
       </c>
       <c r="C599" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="D599" s="2" t="s">
         <v>787</v>
-      </c>
-      <c r="D599" s="2" t="s">
-        <v>788</v>
       </c>
       <c r="E599" s="5"/>
     </row>
@@ -12390,10 +12387,10 @@
         <v>596</v>
       </c>
       <c r="C600" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="D600" s="6" t="s">
         <v>789</v>
-      </c>
-      <c r="D600" s="6" t="s">
-        <v>790</v>
       </c>
       <c r="E600" s="5"/>
     </row>
@@ -12405,10 +12402,10 @@
         <v>509</v>
       </c>
       <c r="C602" s="4" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D602" s="8" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="603" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
@@ -12416,10 +12413,10 @@
         <v>334</v>
       </c>
       <c r="C603" s="10" t="s">
+        <v>794</v>
+      </c>
+      <c r="D603" t="s">
         <v>795</v>
-      </c>
-      <c r="D603" t="s">
-        <v>796</v>
       </c>
       <c r="E603" s="11">
         <v>3277876171384</v>
@@ -12430,10 +12427,10 @@
         <v>263</v>
       </c>
       <c r="C604" s="10" t="s">
+        <v>796</v>
+      </c>
+      <c r="D604" s="12" t="s">
         <v>797</v>
-      </c>
-      <c r="D604" s="12" t="s">
-        <v>798</v>
       </c>
       <c r="E604" s="11">
         <v>3520210170957</v>
@@ -12443,41 +12440,12 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="JALAL SONS  (COLLEGE ROAD) 02"/>
-        <filter val="Jalal sons  (Izmair Town) 01"/>
-        <filter val="Jalal sons (Askari 10 F sector ) 01"/>
-        <filter val="JALAL SONS (ASKARI 11 B BLOCK) 02"/>
-        <filter val="JALAL SONS (AYUBIA) 02"/>
-        <filter val="JALAL SONS (Bahira Orchard) 01"/>
-        <filter val="Jalal Sons (Bahria Town)  01"/>
-        <filter val="JALAL SONS (C BLOCK MODEL TOWN) 02"/>
-        <filter val="JALAL SONS (DHA C BLOCK,PHASE 6) 02"/>
-        <filter val="JALAL SONS (DHA PH IV) 02"/>
-        <filter val="JALAL SONS (DHA PH V) 02"/>
-        <filter val="JALAL SONS (DHA Y BLOCK) 02"/>
-        <filter val="JALAL SONS (EME) 02"/>
-        <filter val="JALAL SONS (FAISAL TOWN) 02"/>
-        <filter val="Jalal Sons (H Block) 01"/>
-        <filter val="JALAL SONS (HUSSAIN CHOWK GULBERG III) 02"/>
-        <filter val="JALAL SONS (IQBAL TOWN) 02"/>
-        <filter val="Jalal Sons (J.T Shadewal) 01"/>
-        <filter val="JALAL SONS (JOHER TOWN) 02"/>
-        <filter val="Jalal Sons (Lake City) 01"/>
-        <filter val="Jalal sons (Main Market) 01"/>
-        <filter val="JALAL SONS (MODEL TOWN LINK ROAD) 02"/>
-        <filter val="Jalal Sons (PAF Market) 01 main Market"/>
-        <filter val="JALAL SONS (PARAGON CITY) 02"/>
-        <filter val="JALAL SONS (PH VI) 02"/>
-        <filter val="JALAL SONS (PHASE 8 EX PARK VIEW) 02"/>
-        <filter val="JALAL SONS (REVAZ GARDEN) 02"/>
-        <filter val="JALAL SONS (SHADMAN) 02"/>
-        <filter val="JALAL SONS (SHAUKAT KHANUM) 02"/>
-        <filter val="JALAL SONS (STATE LIFE) 02"/>
-        <filter val="JALAL SONS (TALWAR CHOWK) 02"/>
-        <filter val="JALAL SONS (VALENCIA TOWN) 02"/>
-        <filter val="JALAL SONS (WAPDA TOWN) 02"/>
-        <filter val="JALAL SONS (XX) 02"/>
-        <filter val="Jalal Sons Askari X (01)"/>
+        <filter val="M.S Traders Harbanspura (Risen)"/>
+        <filter val="Risen / Gajjumata _Rafaqat Sons"/>
+        <filter val="Risen / Manawa _CB TRADERS"/>
+        <filter val="Risen / Sabzazar _Rafaqat Sons"/>
+        <filter val="Risen / Shadbagh _SB Traders"/>
+        <filter val="Risen / TN Traders (Raiwind Road )"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{809C59B2-7AD5-43ED-AF36-CCB22A300CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83AFCF80-683D-47F3-9993-980885995E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6658,7 +6658,7 @@
       </c>
       <c r="F241" s="3"/>
     </row>
-    <row r="242" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B242" s="2">
         <f t="shared" si="3"/>
         <v>238</v>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="F242" s="3"/>
     </row>
-    <row r="243" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B243" s="2">
         <f t="shared" si="3"/>
         <v>239</v>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="F466" s="3"/>
     </row>
-    <row r="467" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="467" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B467" s="2">
         <f t="shared" si="7"/>
         <v>463</v>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="F548" s="3"/>
     </row>
-    <row r="549" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="549" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B549" s="2">
         <f t="shared" si="8"/>
         <v>545</v>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="F549" s="3"/>
     </row>
-    <row r="550" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="550" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B550" s="2">
         <f t="shared" si="8"/>
         <v>546</v>
@@ -11602,7 +11602,7 @@
       </c>
       <c r="F550" s="3"/>
     </row>
-    <row r="551" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="551" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B551" s="2">
         <f t="shared" si="8"/>
         <v>547</v>
@@ -11618,7 +11618,7 @@
       </c>
       <c r="F551" s="3"/>
     </row>
-    <row r="552" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="552" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B552" s="2">
         <f t="shared" si="8"/>
         <v>548</v>
@@ -11634,7 +11634,7 @@
       </c>
       <c r="F552" s="3"/>
     </row>
-    <row r="553" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="553" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B553" s="2">
         <f t="shared" si="8"/>
         <v>549</v>
@@ -12440,12 +12440,8 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="M.S Traders Harbanspura (Risen)"/>
-        <filter val="Risen / Gajjumata _Rafaqat Sons"/>
-        <filter val="Risen / Manawa _CB TRADERS"/>
-        <filter val="Risen / Sabzazar _Rafaqat Sons"/>
-        <filter val="Risen / Shadbagh _SB Traders"/>
-        <filter val="Risen / TN Traders (Raiwind Road )"/>
+        <filter val="Decent Dept Store (Wahdat)"/>
+        <filter val="Decent Store (Johar Town)"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83AFCF80-683D-47F3-9993-980885995E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABAE6494-2B2C-4332-8C43-7CB4BB3F20B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6658,7 +6658,7 @@
       </c>
       <c r="F241" s="3"/>
     </row>
-    <row r="242" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="242" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B242" s="2">
         <f t="shared" si="3"/>
         <v>238</v>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="F242" s="3"/>
     </row>
-    <row r="243" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="243" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B243" s="2">
         <f t="shared" si="3"/>
         <v>239</v>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="F466" s="3"/>
     </row>
-    <row r="467" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B467" s="2">
         <f t="shared" si="7"/>
         <v>463</v>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="F467" s="3"/>
     </row>
-    <row r="468" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B468" s="2">
         <f t="shared" si="7"/>
         <v>464</v>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="F548" s="3"/>
     </row>
-    <row r="549" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B549" s="2">
         <f t="shared" si="8"/>
         <v>545</v>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="F549" s="3"/>
     </row>
-    <row r="550" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B550" s="2">
         <f t="shared" si="8"/>
         <v>546</v>
@@ -11602,7 +11602,7 @@
       </c>
       <c r="F550" s="3"/>
     </row>
-    <row r="551" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B551" s="2">
         <f t="shared" si="8"/>
         <v>547</v>
@@ -11618,7 +11618,7 @@
       </c>
       <c r="F551" s="3"/>
     </row>
-    <row r="552" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B552" s="2">
         <f t="shared" si="8"/>
         <v>548</v>
@@ -11634,7 +11634,7 @@
       </c>
       <c r="F552" s="3"/>
     </row>
-    <row r="553" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B553" s="2">
         <f t="shared" si="8"/>
         <v>549</v>
@@ -12440,8 +12440,13 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Decent Dept Store (Wahdat)"/>
-        <filter val="Decent Store (Johar Town)"/>
+        <filter val="M.S Traders Harbanspura (Risen)"/>
+        <filter val="M/S AL- JANNAT ENTERPRISES"/>
+        <filter val="Risen / Gajjumata _Rafaqat Sons"/>
+        <filter val="Risen / Manawa _CB TRADERS"/>
+        <filter val="Risen / Sabzazar _Rafaqat Sons"/>
+        <filter val="Risen / Shadbagh _SB Traders"/>
+        <filter val="Risen / TN Traders (Raiwind Road )"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABAE6494-2B2C-4332-8C43-7CB4BB3F20B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E6FE075-F40F-448E-A402-FA325D75E3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="F463" s="3"/>
     </row>
-    <row r="464" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B464" s="2">
         <f t="shared" si="7"/>
         <v>460</v>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="F464" s="3"/>
     </row>
-    <row r="465" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B465" s="2">
         <f t="shared" si="7"/>
         <v>461</v>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="F466" s="3"/>
     </row>
-    <row r="467" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="467" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B467" s="2">
         <f t="shared" si="7"/>
         <v>463</v>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="F467" s="3"/>
     </row>
-    <row r="468" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="468" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B468" s="2">
         <f t="shared" si="7"/>
         <v>464</v>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="F548" s="3"/>
     </row>
-    <row r="549" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="549" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B549" s="2">
         <f t="shared" si="8"/>
         <v>545</v>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="F549" s="3"/>
     </row>
-    <row r="550" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="550" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B550" s="2">
         <f t="shared" si="8"/>
         <v>546</v>
@@ -11602,7 +11602,7 @@
       </c>
       <c r="F550" s="3"/>
     </row>
-    <row r="551" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="551" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B551" s="2">
         <f t="shared" si="8"/>
         <v>547</v>
@@ -11618,7 +11618,7 @@
       </c>
       <c r="F551" s="3"/>
     </row>
-    <row r="552" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="552" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B552" s="2">
         <f t="shared" si="8"/>
         <v>548</v>
@@ -11634,7 +11634,7 @@
       </c>
       <c r="F552" s="3"/>
     </row>
-    <row r="553" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="553" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B553" s="2">
         <f t="shared" si="8"/>
         <v>549</v>
@@ -12440,13 +12440,8 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="M.S Traders Harbanspura (Risen)"/>
-        <filter val="M/S AL- JANNAT ENTERPRISES"/>
-        <filter val="Risen / Gajjumata _Rafaqat Sons"/>
-        <filter val="Risen / Manawa _CB TRADERS"/>
-        <filter val="Risen / Sabzazar _Rafaqat Sons"/>
-        <filter val="Risen / Shadbagh _SB Traders"/>
-        <filter val="Risen / TN Traders (Raiwind Road )"/>
+        <filter val="Lutf Mart"/>
+        <filter val="LUTF MART (Barki Road)"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E6FE075-F40F-448E-A402-FA325D75E3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30EC63ED-00B4-4711-A046-DC785B164172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="F50" s="3"/>
     </row>
-    <row r="51" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B51" s="2">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F96" s="3"/>
     </row>
-    <row r="97" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B97" s="2">
         <f t="shared" si="1"/>
         <v>93</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="F104" s="3"/>
     </row>
-    <row r="105" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B105" s="2">
         <f t="shared" si="1"/>
         <v>101</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="F137" s="3"/>
     </row>
-    <row r="138" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B138" s="2">
         <f t="shared" ref="B138:B201" si="2">B137+1</f>
         <v>134</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="F195" s="3"/>
     </row>
-    <row r="196" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B196" s="2">
         <f t="shared" si="2"/>
         <v>192</v>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="F264" s="3"/>
     </row>
-    <row r="265" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B265" s="2">
         <f t="shared" si="3"/>
         <v>261</v>
@@ -8738,7 +8738,7 @@
       </c>
       <c r="F371" s="3"/>
     </row>
-    <row r="372" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B372" s="2">
         <f t="shared" si="5"/>
         <v>368</v>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="F438" s="3"/>
     </row>
-    <row r="439" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B439" s="2">
         <f t="shared" si="6"/>
         <v>435</v>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="F463" s="3"/>
     </row>
-    <row r="464" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="464" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B464" s="2">
         <f t="shared" si="7"/>
         <v>460</v>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="F464" s="3"/>
     </row>
-    <row r="465" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="465" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B465" s="2">
         <f t="shared" si="7"/>
         <v>461</v>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="F592" s="3"/>
     </row>
-    <row r="593" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B593" s="2">
         <f t="shared" si="9"/>
         <v>589</v>
@@ -12440,8 +12440,15 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Lutf Mart"/>
-        <filter val="LUTF MART (Barki Road)"/>
+        <filter val="Ajmair Foods Pvt LTD (Valencia)"/>
+        <filter val="AL KHAN FOODS VALENCIA"/>
+        <filter val="Al-Fatah (Valencia) Zubaida Associates Warrehouse"/>
+        <filter val="BIN KHALID STORE VALENCIA TOWN"/>
+        <filter val="BUTT SWEETS &amp; BAKERS (VALENCIA)"/>
+        <filter val="Family Store (Valencia Town)"/>
+        <filter val="Gourmet Valencia"/>
+        <filter val="JALAL SONS (VALENCIA TOWN) 02"/>
+        <filter val="Valencia Cash And Carry"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30EC63ED-00B4-4711-A046-DC785B164172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F270EB-892B-4C67-B3F2-F322A00C40E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="F50" s="3"/>
     </row>
-    <row r="51" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B51" s="2">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F96" s="3"/>
     </row>
-    <row r="97" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B97" s="2">
         <f t="shared" si="1"/>
         <v>93</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="F104" s="3"/>
     </row>
-    <row r="105" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B105" s="2">
         <f t="shared" si="1"/>
         <v>101</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="F137" s="3"/>
     </row>
-    <row r="138" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B138" s="2">
         <f t="shared" ref="B138:B201" si="2">B137+1</f>
         <v>134</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="F195" s="3"/>
     </row>
-    <row r="196" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B196" s="2">
         <f t="shared" si="2"/>
         <v>192</v>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="F264" s="3"/>
     </row>
-    <row r="265" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="265" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B265" s="2">
         <f t="shared" si="3"/>
         <v>261</v>
@@ -8738,7 +8738,7 @@
       </c>
       <c r="F371" s="3"/>
     </row>
-    <row r="372" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="372" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B372" s="2">
         <f t="shared" si="5"/>
         <v>368</v>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="F438" s="3"/>
     </row>
-    <row r="439" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="439" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B439" s="2">
         <f t="shared" si="6"/>
         <v>435</v>
@@ -11122,7 +11122,7 @@
       </c>
       <c r="F520" s="3"/>
     </row>
-    <row r="521" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B521" s="2">
         <f t="shared" si="7"/>
         <v>517</v>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="F592" s="3"/>
     </row>
-    <row r="593" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="593" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B593" s="2">
         <f t="shared" si="9"/>
         <v>589</v>
@@ -12440,15 +12440,7 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Ajmair Foods Pvt LTD (Valencia)"/>
-        <filter val="AL KHAN FOODS VALENCIA"/>
-        <filter val="Al-Fatah (Valencia) Zubaida Associates Warrehouse"/>
-        <filter val="BIN KHALID STORE VALENCIA TOWN"/>
-        <filter val="BUTT SWEETS &amp; BAKERS (VALENCIA)"/>
-        <filter val="Family Store (Valencia Town)"/>
-        <filter val="Gourmet Valencia"/>
-        <filter val="JALAL SONS (VALENCIA TOWN) 02"/>
-        <filter val="Valencia Cash And Carry"/>
+        <filter val="PEERS CASH N CARRY."/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F270EB-892B-4C67-B3F2-F322A00C40E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3BECAF3-7C13-426E-A4C0-071A0675DB72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="F245" s="3"/>
     </row>
-    <row r="246" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B246" s="2">
         <f t="shared" si="3"/>
         <v>242</v>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="F246" s="3"/>
     </row>
-    <row r="247" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B247" s="2">
         <f t="shared" si="3"/>
         <v>243</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="F247" s="3"/>
     </row>
-    <row r="248" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B248" s="2">
         <f t="shared" si="3"/>
         <v>244</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="F248" s="3"/>
     </row>
-    <row r="249" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B249" s="2">
         <f t="shared" si="3"/>
         <v>245</v>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="F249" s="3"/>
     </row>
-    <row r="250" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B250" s="2">
         <f t="shared" si="3"/>
         <v>246</v>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="F250" s="3"/>
     </row>
-    <row r="251" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B251" s="2">
         <f t="shared" si="3"/>
         <v>247</v>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="F251" s="3"/>
     </row>
-    <row r="252" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B252" s="2">
         <f t="shared" si="3"/>
         <v>248</v>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="F252" s="3"/>
     </row>
-    <row r="253" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B253" s="2">
         <f t="shared" si="3"/>
         <v>249</v>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="F253" s="3"/>
     </row>
-    <row r="254" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B254" s="2">
         <f t="shared" si="3"/>
         <v>250</v>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F254" s="3"/>
     </row>
-    <row r="255" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B255" s="2">
         <f t="shared" si="3"/>
         <v>251</v>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="F255" s="3"/>
     </row>
-    <row r="256" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B256" s="2">
         <f t="shared" si="3"/>
         <v>252</v>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="F256" s="3"/>
     </row>
-    <row r="257" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B257" s="2">
         <f t="shared" si="3"/>
         <v>253</v>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="F257" s="3"/>
     </row>
-    <row r="258" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B258" s="2">
         <f t="shared" si="3"/>
         <v>254</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="F258" s="3"/>
     </row>
-    <row r="259" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B259" s="2">
         <f t="shared" si="3"/>
         <v>255</v>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="F259" s="3"/>
     </row>
-    <row r="260" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B260" s="2">
         <f t="shared" si="3"/>
         <v>256</v>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="F260" s="3"/>
     </row>
-    <row r="261" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B261" s="2">
         <f t="shared" si="3"/>
         <v>257</v>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="F261" s="3"/>
     </row>
-    <row r="262" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B262" s="2">
         <f t="shared" si="3"/>
         <v>258</v>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="F262" s="3"/>
     </row>
-    <row r="263" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B263" s="2">
         <f t="shared" si="3"/>
         <v>259</v>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="F263" s="3"/>
     </row>
-    <row r="264" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B264" s="2">
         <f t="shared" si="3"/>
         <v>260</v>
@@ -11122,7 +11122,7 @@
       </c>
       <c r="F520" s="3"/>
     </row>
-    <row r="521" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="521" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B521" s="2">
         <f t="shared" si="7"/>
         <v>517</v>
@@ -12440,7 +12440,25 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="PEERS CASH N CARRY."/>
+        <filter val="EURO RANJERS MART"/>
+        <filter val="Euro store  (Academy Road)"/>
+        <filter val="EURO STORE (N F C )"/>
+        <filter val="EURO STORE (Rahamt chowk)"/>
+        <filter val="Euro Store (Scheme Mor)"/>
+        <filter val="Euro Store Airport Road"/>
+        <filter val="Euro Store Bedian Road"/>
+        <filter val="Euro Store College Road (Model Town)"/>
+        <filter val="EURO STORE CROWN BEHRIA TOWN"/>
+        <filter val="Euro Store E-2 (Wapda Town)"/>
+        <filter val="EURO STORE FATAH GARH"/>
+        <filter val="Euro Store G.T Road"/>
+        <filter val="Euro Store Garhi Shahu"/>
+        <filter val="EURO Store Hypermarket (Raiwind Road)"/>
+        <filter val="Euro Store Iqbal Town (Ranchna)"/>
+        <filter val="EURO STORE MARIYA STOP"/>
+        <filter val="EURO STORE PH VIII PARK VIEW"/>
+        <filter val="Euro Stores (G-1 Market)"/>
+        <filter val="EURO Stores (Nishat Colony)"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3BECAF3-7C13-426E-A4C0-071A0675DB72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{203A4D7B-C929-41F7-996D-E9AE54F944CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="F245" s="3"/>
     </row>
-    <row r="246" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B246" s="2">
         <f t="shared" si="3"/>
         <v>242</v>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="F246" s="3"/>
     </row>
-    <row r="247" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B247" s="2">
         <f t="shared" si="3"/>
         <v>243</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="F247" s="3"/>
     </row>
-    <row r="248" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B248" s="2">
         <f t="shared" si="3"/>
         <v>244</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="F248" s="3"/>
     </row>
-    <row r="249" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B249" s="2">
         <f t="shared" si="3"/>
         <v>245</v>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="F249" s="3"/>
     </row>
-    <row r="250" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B250" s="2">
         <f t="shared" si="3"/>
         <v>246</v>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="F250" s="3"/>
     </row>
-    <row r="251" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B251" s="2">
         <f t="shared" si="3"/>
         <v>247</v>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="F251" s="3"/>
     </row>
-    <row r="252" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B252" s="2">
         <f t="shared" si="3"/>
         <v>248</v>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="F252" s="3"/>
     </row>
-    <row r="253" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B253" s="2">
         <f t="shared" si="3"/>
         <v>249</v>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="F253" s="3"/>
     </row>
-    <row r="254" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B254" s="2">
         <f t="shared" si="3"/>
         <v>250</v>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F254" s="3"/>
     </row>
-    <row r="255" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B255" s="2">
         <f t="shared" si="3"/>
         <v>251</v>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="F255" s="3"/>
     </row>
-    <row r="256" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B256" s="2">
         <f t="shared" si="3"/>
         <v>252</v>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="F256" s="3"/>
     </row>
-    <row r="257" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B257" s="2">
         <f t="shared" si="3"/>
         <v>253</v>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="F257" s="3"/>
     </row>
-    <row r="258" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B258" s="2">
         <f t="shared" si="3"/>
         <v>254</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="F258" s="3"/>
     </row>
-    <row r="259" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B259" s="2">
         <f t="shared" si="3"/>
         <v>255</v>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="F259" s="3"/>
     </row>
-    <row r="260" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B260" s="2">
         <f t="shared" si="3"/>
         <v>256</v>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="F260" s="3"/>
     </row>
-    <row r="261" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B261" s="2">
         <f t="shared" si="3"/>
         <v>257</v>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="F261" s="3"/>
     </row>
-    <row r="262" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B262" s="2">
         <f t="shared" si="3"/>
         <v>258</v>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="F262" s="3"/>
     </row>
-    <row r="263" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B263" s="2">
         <f t="shared" si="3"/>
         <v>259</v>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="F263" s="3"/>
     </row>
-    <row r="264" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B264" s="2">
         <f t="shared" si="3"/>
         <v>260</v>
@@ -12306,7 +12306,7 @@
       </c>
       <c r="F594" s="3"/>
     </row>
-    <row r="595" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B595" s="2">
         <f t="shared" si="9"/>
         <v>591</v>
@@ -12440,25 +12440,7 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="EURO RANJERS MART"/>
-        <filter val="Euro store  (Academy Road)"/>
-        <filter val="EURO STORE (N F C )"/>
-        <filter val="EURO STORE (Rahamt chowk)"/>
-        <filter val="Euro Store (Scheme Mor)"/>
-        <filter val="Euro Store Airport Road"/>
-        <filter val="Euro Store Bedian Road"/>
-        <filter val="Euro Store College Road (Model Town)"/>
-        <filter val="EURO STORE CROWN BEHRIA TOWN"/>
-        <filter val="Euro Store E-2 (Wapda Town)"/>
-        <filter val="EURO STORE FATAH GARH"/>
-        <filter val="Euro Store G.T Road"/>
-        <filter val="Euro Store Garhi Shahu"/>
-        <filter val="EURO Store Hypermarket (Raiwind Road)"/>
-        <filter val="Euro Store Iqbal Town (Ranchna)"/>
-        <filter val="EURO STORE MARIYA STOP"/>
-        <filter val="EURO STORE PH VIII PARK VIEW"/>
-        <filter val="Euro Stores (G-1 Market)"/>
-        <filter val="EURO Stores (Nishat Colony)"/>
+        <filter val="Victoria (Link Road)"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{203A4D7B-C929-41F7-996D-E9AE54F944CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F20D4850-5B4A-4811-A253-1F0E685D7F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="F301" s="3"/>
     </row>
-    <row r="302" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B302" s="2">
         <f t="shared" si="4"/>
         <v>298</v>
@@ -12306,7 +12306,7 @@
       </c>
       <c r="F594" s="3"/>
     </row>
-    <row r="595" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="595" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B595" s="2">
         <f t="shared" si="9"/>
         <v>591</v>
@@ -12440,7 +12440,7 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Victoria (Link Road)"/>
+        <filter val="GOURMET BAKERS (KOT ABDUL MALIK)"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F20D4850-5B4A-4811-A253-1F0E685D7F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C80FDAF9-322B-41A3-95AB-3F72ECF97298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="F301" s="3"/>
     </row>
-    <row r="302" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="302" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B302" s="2">
         <f t="shared" si="4"/>
         <v>298</v>
@@ -10482,7 +10482,7 @@
       </c>
       <c r="F480" s="3"/>
     </row>
-    <row r="481" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B481" s="2">
         <f t="shared" si="7"/>
         <v>477</v>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="F591" s="3"/>
     </row>
-    <row r="592" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B592" s="2">
         <f t="shared" si="9"/>
         <v>588</v>
@@ -12440,7 +12440,8 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="GOURMET BAKERS (KOT ABDUL MALIK)"/>
+        <filter val="Malmo Bakers (Usmania Tower)"/>
+        <filter val="Usman Store"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C80FDAF9-322B-41A3-95AB-3F72ECF97298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9A3EB7-3091-4912-B9A7-5B66829D7B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="F187" s="3"/>
     </row>
-    <row r="188" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B188" s="2">
         <f t="shared" si="2"/>
         <v>184</v>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="F188" s="3"/>
     </row>
-    <row r="189" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B189" s="2">
         <f t="shared" si="2"/>
         <v>185</v>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="F189" s="3"/>
     </row>
-    <row r="190" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B190" s="2">
         <f t="shared" si="2"/>
         <v>186</v>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="F190" s="3"/>
     </row>
-    <row r="191" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B191" s="2">
         <f t="shared" si="2"/>
         <v>187</v>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="F191" s="3"/>
     </row>
-    <row r="192" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B192" s="2">
         <f t="shared" si="2"/>
         <v>188</v>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="F192" s="3"/>
     </row>
-    <row r="193" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B193" s="2">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="F193" s="3"/>
     </row>
-    <row r="194" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B194" s="2">
         <f t="shared" si="2"/>
         <v>190</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="F194" s="3"/>
     </row>
-    <row r="195" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B195" s="2">
         <f t="shared" si="2"/>
         <v>191</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="F195" s="3"/>
     </row>
-    <row r="196" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B196" s="2">
         <f t="shared" si="2"/>
         <v>192</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="F196" s="3"/>
     </row>
-    <row r="197" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B197" s="2">
         <f t="shared" si="2"/>
         <v>193</v>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="F197" s="3"/>
     </row>
-    <row r="198" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B198" s="2">
         <f t="shared" si="2"/>
         <v>194</v>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="F198" s="3"/>
     </row>
-    <row r="199" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B199" s="2">
         <f t="shared" si="2"/>
         <v>195</v>
@@ -5986,7 +5986,7 @@
       </c>
       <c r="F199" s="3"/>
     </row>
-    <row r="200" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B200" s="2">
         <f t="shared" si="2"/>
         <v>196</v>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="F200" s="3"/>
     </row>
-    <row r="201" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B201" s="2">
         <f t="shared" si="2"/>
         <v>197</v>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="F243" s="3"/>
     </row>
-    <row r="244" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B244" s="2">
         <f t="shared" si="3"/>
         <v>240</v>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="F389" s="3"/>
     </row>
-    <row r="390" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B390" s="2">
         <f t="shared" si="5"/>
         <v>386</v>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="F390" s="3"/>
     </row>
-    <row r="391" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B391" s="2">
         <f t="shared" si="5"/>
         <v>387</v>
@@ -9922,7 +9922,7 @@
       </c>
       <c r="F445" s="3"/>
     </row>
-    <row r="446" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B446" s="2">
         <f t="shared" si="6"/>
         <v>442</v>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="F446" s="3"/>
     </row>
-    <row r="447" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B447" s="2">
         <f t="shared" si="6"/>
         <v>443</v>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="F449" s="3"/>
     </row>
-    <row r="450" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B450" s="2">
         <f t="shared" si="6"/>
         <v>446</v>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="F450" s="3"/>
     </row>
-    <row r="451" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B451" s="2">
         <f t="shared" si="6"/>
         <v>447</v>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="F473" s="3"/>
     </row>
-    <row r="474" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B474" s="2">
         <f t="shared" si="7"/>
         <v>470</v>
@@ -10482,7 +10482,7 @@
       </c>
       <c r="F480" s="3"/>
     </row>
-    <row r="481" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="481" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B481" s="2">
         <f t="shared" si="7"/>
         <v>477</v>
@@ -10690,7 +10690,7 @@
       </c>
       <c r="F493" s="3"/>
     </row>
-    <row r="494" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B494" s="2">
         <f t="shared" si="7"/>
         <v>490</v>
@@ -10706,7 +10706,7 @@
       </c>
       <c r="F494" s="3"/>
     </row>
-    <row r="495" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B495" s="2">
         <f t="shared" si="7"/>
         <v>491</v>
@@ -12082,7 +12082,7 @@
       </c>
       <c r="F580" s="3"/>
     </row>
-    <row r="581" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B581" s="2">
         <f t="shared" si="8"/>
         <v>577</v>
@@ -12098,7 +12098,7 @@
       </c>
       <c r="F581" s="3"/>
     </row>
-    <row r="582" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B582" s="2">
         <f t="shared" si="8"/>
         <v>578</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="F582" s="3"/>
     </row>
-    <row r="583" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B583" s="2">
         <f t="shared" si="8"/>
         <v>579</v>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="F591" s="3"/>
     </row>
-    <row r="592" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="592" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B592" s="2">
         <f t="shared" si="9"/>
         <v>588</v>
@@ -12440,8 +12440,33 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Malmo Bakers (Usmania Tower)"/>
-        <filter val="Usman Store"/>
+        <filter val="Butt Sweet (Bata Pur)"/>
+        <filter val="Butt Sweet (DHA Phase-1)"/>
+        <filter val="Butt Sweet (G-1 Market)"/>
+        <filter val="Butt Sweet (Yuhannabad)"/>
+        <filter val="Butt sweet Ghazi Road"/>
+        <filter val="BUTT SWEET SHAHDRA MORE"/>
+        <filter val="BUTT SWEETS &amp; BAKERS  (PIA ROAD)"/>
+        <filter val="BUTT SWEETS &amp; BAKERS (GT ROAD)"/>
+        <filter val="BUTT SWEETS &amp; BAKERS (VALENCIA)"/>
+        <filter val="BUTT SWEETS (LIAQAT CHOWK)"/>
+        <filter val="BUTT SWEETS (Walton)"/>
+        <filter val="Butt Sweets Laxmi Chowk"/>
+        <filter val="BUTT SWEETS MAIIN G.T Roads"/>
+        <filter val="Butt Sweets Taxali Gate"/>
+        <filter val="DIVINE BAKERS &amp; SWEETS (WAHDAT ROAD)"/>
+        <filter val="Hafiz Sweet Bakers"/>
+        <filter val="Hafiz Sweets Unit 2"/>
+        <filter val="LARAIB BAKERS &amp; SWEET (SHADMAN)"/>
+        <filter val="LARAIB BAKERS &amp; SWEETS (YATEEM kHANA)"/>
+        <filter val="LARAIB BAKERS SWEETS (Ghulshan Ravi)"/>
+        <filter val="LARAIB BAKERS SWEETS (YOUHANABAD)"/>
+        <filter val="M/S BUTT SWEETS &amp; BAKERS (KUTCHEHRI BAZAR)"/>
+        <filter val="MALMO SWEETS &amp; BAKERS (AL-KABIR TOWN)"/>
+        <filter val="MALMO SWEETS &amp; BAKERS (BEHRIA ORCHARD)"/>
+        <filter val="Swera Departmental Store (Punjab Society)"/>
+        <filter val="Swera Store (Shadman)"/>
+        <filter val="Swera Store G.T Road"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9A3EB7-3091-4912-B9A7-5B66829D7B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCBB1C78-2BE9-45A9-AEFC-8BB055FA6725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="F134" s="3"/>
     </row>
-    <row r="135" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B135" s="2">
         <f t="shared" si="1"/>
         <v>131</v>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="F135" s="3"/>
     </row>
-    <row r="136" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B136" s="2">
         <f t="shared" si="1"/>
         <v>132</v>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="F187" s="3"/>
     </row>
-    <row r="188" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B188" s="2">
         <f t="shared" si="2"/>
         <v>184</v>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="F188" s="3"/>
     </row>
-    <row r="189" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B189" s="2">
         <f t="shared" si="2"/>
         <v>185</v>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="F189" s="3"/>
     </row>
-    <row r="190" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B190" s="2">
         <f t="shared" si="2"/>
         <v>186</v>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="F190" s="3"/>
     </row>
-    <row r="191" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B191" s="2">
         <f t="shared" si="2"/>
         <v>187</v>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="F191" s="3"/>
     </row>
-    <row r="192" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B192" s="2">
         <f t="shared" si="2"/>
         <v>188</v>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="F192" s="3"/>
     </row>
-    <row r="193" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B193" s="2">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="F193" s="3"/>
     </row>
-    <row r="194" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B194" s="2">
         <f t="shared" si="2"/>
         <v>190</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="F194" s="3"/>
     </row>
-    <row r="195" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B195" s="2">
         <f t="shared" si="2"/>
         <v>191</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="F195" s="3"/>
     </row>
-    <row r="196" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B196" s="2">
         <f t="shared" si="2"/>
         <v>192</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="F196" s="3"/>
     </row>
-    <row r="197" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B197" s="2">
         <f t="shared" si="2"/>
         <v>193</v>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="F197" s="3"/>
     </row>
-    <row r="198" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B198" s="2">
         <f t="shared" si="2"/>
         <v>194</v>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="F198" s="3"/>
     </row>
-    <row r="199" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B199" s="2">
         <f t="shared" si="2"/>
         <v>195</v>
@@ -5986,7 +5986,7 @@
       </c>
       <c r="F199" s="3"/>
     </row>
-    <row r="200" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B200" s="2">
         <f t="shared" si="2"/>
         <v>196</v>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="F200" s="3"/>
     </row>
-    <row r="201" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B201" s="2">
         <f t="shared" si="2"/>
         <v>197</v>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="F243" s="3"/>
     </row>
-    <row r="244" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="244" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B244" s="2">
         <f t="shared" si="3"/>
         <v>240</v>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="F389" s="3"/>
     </row>
-    <row r="390" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="390" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B390" s="2">
         <f t="shared" si="5"/>
         <v>386</v>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="F390" s="3"/>
     </row>
-    <row r="391" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="391" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B391" s="2">
         <f t="shared" si="5"/>
         <v>387</v>
@@ -9922,7 +9922,7 @@
       </c>
       <c r="F445" s="3"/>
     </row>
-    <row r="446" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="446" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B446" s="2">
         <f t="shared" si="6"/>
         <v>442</v>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="F446" s="3"/>
     </row>
-    <row r="447" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="447" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B447" s="2">
         <f t="shared" si="6"/>
         <v>443</v>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="F449" s="3"/>
     </row>
-    <row r="450" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="450" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B450" s="2">
         <f t="shared" si="6"/>
         <v>446</v>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="F450" s="3"/>
     </row>
-    <row r="451" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="451" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B451" s="2">
         <f t="shared" si="6"/>
         <v>447</v>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="F473" s="3"/>
     </row>
-    <row r="474" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="474" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B474" s="2">
         <f t="shared" si="7"/>
         <v>470</v>
@@ -10690,7 +10690,7 @@
       </c>
       <c r="F493" s="3"/>
     </row>
-    <row r="494" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="494" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B494" s="2">
         <f t="shared" si="7"/>
         <v>490</v>
@@ -10706,7 +10706,7 @@
       </c>
       <c r="F494" s="3"/>
     </row>
-    <row r="495" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="495" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B495" s="2">
         <f t="shared" si="7"/>
         <v>491</v>
@@ -12082,7 +12082,7 @@
       </c>
       <c r="F580" s="3"/>
     </row>
-    <row r="581" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="581" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B581" s="2">
         <f t="shared" si="8"/>
         <v>577</v>
@@ -12098,7 +12098,7 @@
       </c>
       <c r="F581" s="3"/>
     </row>
-    <row r="582" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="582" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B582" s="2">
         <f t="shared" si="8"/>
         <v>578</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="F582" s="3"/>
     </row>
-    <row r="583" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="583" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B583" s="2">
         <f t="shared" si="8"/>
         <v>579</v>
@@ -12440,33 +12440,8 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Butt Sweet (Bata Pur)"/>
-        <filter val="Butt Sweet (DHA Phase-1)"/>
-        <filter val="Butt Sweet (G-1 Market)"/>
-        <filter val="Butt Sweet (Yuhannabad)"/>
-        <filter val="Butt sweet Ghazi Road"/>
-        <filter val="BUTT SWEET SHAHDRA MORE"/>
-        <filter val="BUTT SWEETS &amp; BAKERS  (PIA ROAD)"/>
-        <filter val="BUTT SWEETS &amp; BAKERS (GT ROAD)"/>
-        <filter val="BUTT SWEETS &amp; BAKERS (VALENCIA)"/>
-        <filter val="BUTT SWEETS (LIAQAT CHOWK)"/>
-        <filter val="BUTT SWEETS (Walton)"/>
-        <filter val="Butt Sweets Laxmi Chowk"/>
-        <filter val="BUTT SWEETS MAIIN G.T Roads"/>
-        <filter val="Butt Sweets Taxali Gate"/>
-        <filter val="DIVINE BAKERS &amp; SWEETS (WAHDAT ROAD)"/>
-        <filter val="Hafiz Sweet Bakers"/>
-        <filter val="Hafiz Sweets Unit 2"/>
-        <filter val="LARAIB BAKERS &amp; SWEET (SHADMAN)"/>
-        <filter val="LARAIB BAKERS &amp; SWEETS (YATEEM kHANA)"/>
-        <filter val="LARAIB BAKERS SWEETS (Ghulshan Ravi)"/>
-        <filter val="LARAIB BAKERS SWEETS (YOUHANABAD)"/>
-        <filter val="M/S BUTT SWEETS &amp; BAKERS (KUTCHEHRI BAZAR)"/>
-        <filter val="MALMO SWEETS &amp; BAKERS (AL-KABIR TOWN)"/>
-        <filter val="MALMO SWEETS &amp; BAKERS (BEHRIA ORCHARD)"/>
-        <filter val="Swera Departmental Store (Punjab Society)"/>
-        <filter val="Swera Store (Shadman)"/>
-        <filter val="Swera Store G.T Road"/>
+        <filter val="BEST BUY  (C.GROUND)"/>
+        <filter val="Best Buy-2 (Nisaar)"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCBB1C78-2BE9-45A9-AEFC-8BB055FA6725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7723AD-354A-4F70-B38F-D51AC465DC0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="F134" s="3"/>
     </row>
-    <row r="135" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B135" s="2">
         <f t="shared" si="1"/>
         <v>131</v>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="F135" s="3"/>
     </row>
-    <row r="136" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B136" s="2">
         <f t="shared" si="1"/>
         <v>132</v>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="F245" s="3"/>
     </row>
-    <row r="246" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B246" s="2">
         <f t="shared" si="3"/>
         <v>242</v>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="F246" s="3"/>
     </row>
-    <row r="247" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B247" s="2">
         <f t="shared" si="3"/>
         <v>243</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="F247" s="3"/>
     </row>
-    <row r="248" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B248" s="2">
         <f t="shared" si="3"/>
         <v>244</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="F248" s="3"/>
     </row>
-    <row r="249" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B249" s="2">
         <f t="shared" si="3"/>
         <v>245</v>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="F249" s="3"/>
     </row>
-    <row r="250" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B250" s="2">
         <f t="shared" si="3"/>
         <v>246</v>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="F250" s="3"/>
     </row>
-    <row r="251" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B251" s="2">
         <f t="shared" si="3"/>
         <v>247</v>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="F251" s="3"/>
     </row>
-    <row r="252" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B252" s="2">
         <f t="shared" si="3"/>
         <v>248</v>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="F252" s="3"/>
     </row>
-    <row r="253" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B253" s="2">
         <f t="shared" si="3"/>
         <v>249</v>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="F253" s="3"/>
     </row>
-    <row r="254" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B254" s="2">
         <f t="shared" si="3"/>
         <v>250</v>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F254" s="3"/>
     </row>
-    <row r="255" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B255" s="2">
         <f t="shared" si="3"/>
         <v>251</v>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="F255" s="3"/>
     </row>
-    <row r="256" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B256" s="2">
         <f t="shared" si="3"/>
         <v>252</v>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="F256" s="3"/>
     </row>
-    <row r="257" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B257" s="2">
         <f t="shared" si="3"/>
         <v>253</v>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="F257" s="3"/>
     </row>
-    <row r="258" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B258" s="2">
         <f t="shared" si="3"/>
         <v>254</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="F258" s="3"/>
     </row>
-    <row r="259" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B259" s="2">
         <f t="shared" si="3"/>
         <v>255</v>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="F259" s="3"/>
     </row>
-    <row r="260" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B260" s="2">
         <f t="shared" si="3"/>
         <v>256</v>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="F260" s="3"/>
     </row>
-    <row r="261" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B261" s="2">
         <f t="shared" si="3"/>
         <v>257</v>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="F261" s="3"/>
     </row>
-    <row r="262" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B262" s="2">
         <f t="shared" si="3"/>
         <v>258</v>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="F262" s="3"/>
     </row>
-    <row r="263" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B263" s="2">
         <f t="shared" si="3"/>
         <v>259</v>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="F263" s="3"/>
     </row>
-    <row r="264" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B264" s="2">
         <f t="shared" si="3"/>
         <v>260</v>
@@ -12440,8 +12440,25 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="BEST BUY  (C.GROUND)"/>
-        <filter val="Best Buy-2 (Nisaar)"/>
+        <filter val="EURO RANJERS MART"/>
+        <filter val="Euro store  (Academy Road)"/>
+        <filter val="EURO STORE (N F C )"/>
+        <filter val="EURO STORE (Rahamt chowk)"/>
+        <filter val="Euro Store (Scheme Mor)"/>
+        <filter val="Euro Store Airport Road"/>
+        <filter val="Euro Store Bedian Road"/>
+        <filter val="Euro Store College Road (Model Town)"/>
+        <filter val="EURO STORE CROWN BEHRIA TOWN"/>
+        <filter val="Euro Store E-2 (Wapda Town)"/>
+        <filter val="EURO STORE FATAH GARH"/>
+        <filter val="Euro Store G.T Road"/>
+        <filter val="Euro Store Garhi Shahu"/>
+        <filter val="EURO Store Hypermarket (Raiwind Road)"/>
+        <filter val="Euro Store Iqbal Town (Ranchna)"/>
+        <filter val="EURO STORE MARIYA STOP"/>
+        <filter val="EURO STORE PH VIII PARK VIEW"/>
+        <filter val="Euro Stores (G-1 Market)"/>
+        <filter val="EURO Stores (Nishat Colony)"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7723AD-354A-4F70-B38F-D51AC465DC0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E1799AF-5D36-4EB0-B565-44CA0AD297D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E1799AF-5D36-4EB0-B565-44CA0AD297D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504C138E-AAD0-480C-8E9D-F4584A21A5A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504C138E-AAD0-480C-8E9D-F4584A21A5A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00772B0C-B924-414E-B49C-57FF32697012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="F23" s="3"/>
     </row>
-    <row r="24" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B24" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="F82" s="3"/>
     </row>
-    <row r="83" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B83" s="2">
         <f t="shared" si="1"/>
         <v>79</v>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="F245" s="3"/>
     </row>
-    <row r="246" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B246" s="2">
         <f t="shared" si="3"/>
         <v>242</v>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="F246" s="3"/>
     </row>
-    <row r="247" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B247" s="2">
         <f t="shared" si="3"/>
         <v>243</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="F247" s="3"/>
     </row>
-    <row r="248" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B248" s="2">
         <f t="shared" si="3"/>
         <v>244</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="F248" s="3"/>
     </row>
-    <row r="249" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B249" s="2">
         <f t="shared" si="3"/>
         <v>245</v>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="F249" s="3"/>
     </row>
-    <row r="250" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B250" s="2">
         <f t="shared" si="3"/>
         <v>246</v>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="F250" s="3"/>
     </row>
-    <row r="251" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B251" s="2">
         <f t="shared" si="3"/>
         <v>247</v>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="F251" s="3"/>
     </row>
-    <row r="252" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B252" s="2">
         <f t="shared" si="3"/>
         <v>248</v>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="F252" s="3"/>
     </row>
-    <row r="253" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B253" s="2">
         <f t="shared" si="3"/>
         <v>249</v>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="F253" s="3"/>
     </row>
-    <row r="254" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B254" s="2">
         <f t="shared" si="3"/>
         <v>250</v>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F254" s="3"/>
     </row>
-    <row r="255" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B255" s="2">
         <f t="shared" si="3"/>
         <v>251</v>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="F255" s="3"/>
     </row>
-    <row r="256" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B256" s="2">
         <f t="shared" si="3"/>
         <v>252</v>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="F256" s="3"/>
     </row>
-    <row r="257" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B257" s="2">
         <f t="shared" si="3"/>
         <v>253</v>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="F257" s="3"/>
     </row>
-    <row r="258" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B258" s="2">
         <f t="shared" si="3"/>
         <v>254</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="F258" s="3"/>
     </row>
-    <row r="259" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B259" s="2">
         <f t="shared" si="3"/>
         <v>255</v>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="F259" s="3"/>
     </row>
-    <row r="260" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B260" s="2">
         <f t="shared" si="3"/>
         <v>256</v>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="F260" s="3"/>
     </row>
-    <row r="261" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B261" s="2">
         <f t="shared" si="3"/>
         <v>257</v>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="F261" s="3"/>
     </row>
-    <row r="262" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B262" s="2">
         <f t="shared" si="3"/>
         <v>258</v>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="F262" s="3"/>
     </row>
-    <row r="263" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B263" s="2">
         <f t="shared" si="3"/>
         <v>259</v>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="F263" s="3"/>
     </row>
-    <row r="264" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B264" s="2">
         <f t="shared" si="3"/>
         <v>260</v>
@@ -9890,7 +9890,7 @@
       </c>
       <c r="F443" s="3"/>
     </row>
-    <row r="444" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B444" s="2">
         <f t="shared" si="6"/>
         <v>440</v>
@@ -10034,7 +10034,7 @@
       </c>
       <c r="F452" s="3"/>
     </row>
-    <row r="453" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B453" s="2">
         <f t="shared" si="6"/>
         <v>449</v>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="F519" s="3"/>
     </row>
-    <row r="520" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B520" s="2">
         <f t="shared" si="7"/>
         <v>516</v>
@@ -12440,25 +12440,11 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="EURO RANJERS MART"/>
-        <filter val="Euro store  (Academy Road)"/>
-        <filter val="EURO STORE (N F C )"/>
-        <filter val="EURO STORE (Rahamt chowk)"/>
-        <filter val="Euro Store (Scheme Mor)"/>
-        <filter val="Euro Store Airport Road"/>
-        <filter val="Euro Store Bedian Road"/>
-        <filter val="Euro Store College Road (Model Town)"/>
-        <filter val="EURO STORE CROWN BEHRIA TOWN"/>
-        <filter val="Euro Store E-2 (Wapda Town)"/>
-        <filter val="EURO STORE FATAH GARH"/>
-        <filter val="Euro Store G.T Road"/>
-        <filter val="Euro Store Garhi Shahu"/>
-        <filter val="EURO Store Hypermarket (Raiwind Road)"/>
-        <filter val="Euro Store Iqbal Town (Ranchna)"/>
-        <filter val="EURO STORE MARIYA STOP"/>
-        <filter val="EURO STORE PH VIII PARK VIEW"/>
-        <filter val="Euro Stores (G-1 Market)"/>
-        <filter val="EURO Stores (Nishat Colony)"/>
+        <filter val="Ajmair Foods (Lahore Hotel)"/>
+        <filter val="Al Fatah (Model Town Lahore)"/>
+        <filter val="Lahore Cash &amp; Carry"/>
+        <filter val="LARAIB FOODS  MARGZAR ROAD LAHORE"/>
+        <filter val="PEARL CONTINENTAL LAHORE (MALL ROAD)"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00772B0C-B924-414E-B49C-57FF32697012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C2A1D9-A639-407E-BB3D-42A455601AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="F23" s="3"/>
     </row>
-    <row r="24" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B24" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="F82" s="3"/>
     </row>
-    <row r="83" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B83" s="2">
         <f t="shared" si="1"/>
         <v>79</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="F258" s="3"/>
     </row>
-    <row r="259" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B259" s="2">
         <f t="shared" si="3"/>
         <v>255</v>
@@ -9890,7 +9890,7 @@
       </c>
       <c r="F443" s="3"/>
     </row>
-    <row r="444" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="444" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B444" s="2">
         <f t="shared" si="6"/>
         <v>440</v>
@@ -10034,7 +10034,7 @@
       </c>
       <c r="F452" s="3"/>
     </row>
-    <row r="453" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="453" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B453" s="2">
         <f t="shared" si="6"/>
         <v>449</v>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="F519" s="3"/>
     </row>
-    <row r="520" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="520" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B520" s="2">
         <f t="shared" si="7"/>
         <v>516</v>
@@ -12440,11 +12440,7 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Ajmair Foods (Lahore Hotel)"/>
-        <filter val="Al Fatah (Model Town Lahore)"/>
-        <filter val="Lahore Cash &amp; Carry"/>
-        <filter val="LARAIB FOODS  MARGZAR ROAD LAHORE"/>
-        <filter val="PEARL CONTINENTAL LAHORE (MALL ROAD)"/>
+        <filter val="EURO Store Hypermarket (Raiwind Road)"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C2A1D9-A639-407E-BB3D-42A455601AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CEB88BB-0886-4C0C-8E29-C6B714B25665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="F258" s="3"/>
     </row>
-    <row r="259" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B259" s="2">
         <f t="shared" si="3"/>
         <v>255</v>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="F267" s="3"/>
     </row>
-    <row r="268" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B268" s="2">
         <f t="shared" si="4"/>
         <v>264</v>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="F268" s="3"/>
     </row>
-    <row r="269" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B269" s="2">
         <f t="shared" si="4"/>
         <v>265</v>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="F269" s="3"/>
     </row>
-    <row r="270" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B270" s="2">
         <f t="shared" si="4"/>
         <v>266</v>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="F270" s="3"/>
     </row>
-    <row r="271" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B271" s="2">
         <f t="shared" si="4"/>
         <v>267</v>
@@ -7138,7 +7138,7 @@
       </c>
       <c r="F271" s="3"/>
     </row>
-    <row r="272" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B272" s="2">
         <f t="shared" si="4"/>
         <v>268</v>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="F272" s="3"/>
     </row>
-    <row r="273" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B273" s="2">
         <f t="shared" si="4"/>
         <v>269</v>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="F273" s="3"/>
     </row>
-    <row r="274" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B274" s="2">
         <f t="shared" si="4"/>
         <v>270</v>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="F274" s="3"/>
     </row>
-    <row r="275" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B275" s="2">
         <f t="shared" si="4"/>
         <v>271</v>
@@ -8722,7 +8722,7 @@
       </c>
       <c r="F370" s="3"/>
     </row>
-    <row r="371" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B371" s="2">
         <f t="shared" si="5"/>
         <v>367</v>
@@ -12210,7 +12210,7 @@
       </c>
       <c r="F588" s="3"/>
     </row>
-    <row r="589" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B589" s="2">
         <f t="shared" si="9"/>
         <v>585</v>
@@ -12226,7 +12226,7 @@
       </c>
       <c r="F589" s="3"/>
     </row>
-    <row r="590" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B590" s="2">
         <f t="shared" si="9"/>
         <v>586</v>
@@ -12440,7 +12440,17 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="EURO Store Hypermarket (Raiwind Road)"/>
+        <filter val="FDPP CONSUMER (AWAISIA HOUSING SOCIETY)"/>
+        <filter val="FDPP CONSUMER Behria Town"/>
+        <filter val="FDPP CONSUMER H BLOCK DHA"/>
+        <filter val="FDPP CONSUMER Iqbal Town"/>
+        <filter val="FDPP CONSUMER Joher Town"/>
+        <filter val="FDPP CONSUMER Main Market"/>
+        <filter val="FDPP CONSUMER Model Town"/>
+        <filter val="FDPP CONSUMER(FRANCHISE ENGINEER TOWN)"/>
+        <filter val="Gourmet Umer Chowk"/>
+        <filter val="Umer Cash And Carry (Punjab Society)"/>
+        <filter val="Umer Super Market (Joher Town)"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CEB88BB-0886-4C0C-8E29-C6B714B25665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06069065-1092-4907-9095-9F80F6616A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="F113" s="3"/>
     </row>
-    <row r="114" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B114" s="2">
         <f t="shared" si="1"/>
         <v>110</v>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="F114" s="3"/>
     </row>
-    <row r="115" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B115" s="2">
         <f t="shared" si="1"/>
         <v>111</v>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="F115" s="3"/>
     </row>
-    <row r="116" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B116" s="2">
         <f t="shared" si="1"/>
         <v>112</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="F116" s="3"/>
     </row>
-    <row r="117" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B117" s="2">
         <f t="shared" si="1"/>
         <v>113</v>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="F267" s="3"/>
     </row>
-    <row r="268" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="268" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B268" s="2">
         <f t="shared" si="4"/>
         <v>264</v>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="F268" s="3"/>
     </row>
-    <row r="269" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="269" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B269" s="2">
         <f t="shared" si="4"/>
         <v>265</v>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="F269" s="3"/>
     </row>
-    <row r="270" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="270" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B270" s="2">
         <f t="shared" si="4"/>
         <v>266</v>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="F270" s="3"/>
     </row>
-    <row r="271" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="271" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B271" s="2">
         <f t="shared" si="4"/>
         <v>267</v>
@@ -7138,7 +7138,7 @@
       </c>
       <c r="F271" s="3"/>
     </row>
-    <row r="272" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="272" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B272" s="2">
         <f t="shared" si="4"/>
         <v>268</v>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="F272" s="3"/>
     </row>
-    <row r="273" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="273" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B273" s="2">
         <f t="shared" si="4"/>
         <v>269</v>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="F273" s="3"/>
     </row>
-    <row r="274" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="274" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B274" s="2">
         <f t="shared" si="4"/>
         <v>270</v>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="F274" s="3"/>
     </row>
-    <row r="275" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="275" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B275" s="2">
         <f t="shared" si="4"/>
         <v>271</v>
@@ -8722,7 +8722,7 @@
       </c>
       <c r="F370" s="3"/>
     </row>
-    <row r="371" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="371" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B371" s="2">
         <f t="shared" si="5"/>
         <v>367</v>
@@ -12210,7 +12210,7 @@
       </c>
       <c r="F588" s="3"/>
     </row>
-    <row r="589" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="589" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B589" s="2">
         <f t="shared" si="9"/>
         <v>585</v>
@@ -12226,7 +12226,7 @@
       </c>
       <c r="F589" s="3"/>
     </row>
-    <row r="590" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="590" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B590" s="2">
         <f t="shared" si="9"/>
         <v>586</v>
@@ -12440,17 +12440,10 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="FDPP CONSUMER (AWAISIA HOUSING SOCIETY)"/>
-        <filter val="FDPP CONSUMER Behria Town"/>
-        <filter val="FDPP CONSUMER H BLOCK DHA"/>
-        <filter val="FDPP CONSUMER Iqbal Town"/>
-        <filter val="FDPP CONSUMER Joher Town"/>
-        <filter val="FDPP CONSUMER Main Market"/>
-        <filter val="FDPP CONSUMER Model Town"/>
-        <filter val="FDPP CONSUMER(FRANCHISE ENGINEER TOWN)"/>
-        <filter val="Gourmet Umer Chowk"/>
-        <filter val="Umer Cash And Carry (Punjab Society)"/>
-        <filter val="Umer Super Market (Joher Town)"/>
+        <filter val="ASLAM CASH &amp; CARRY (COLLEGER ROAD)"/>
+        <filter val="Aslam Mart (Behria Orchard)"/>
+        <filter val="Aslam Super Market ( LDA )"/>
+        <filter val="Aslam Super Market EME"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06069065-1092-4907-9095-9F80F6616A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E8C828-E845-4673-B087-50215619DEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="F113" s="3"/>
     </row>
-    <row r="114" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B114" s="2">
         <f t="shared" si="1"/>
         <v>110</v>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="F114" s="3"/>
     </row>
-    <row r="115" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B115" s="2">
         <f t="shared" si="1"/>
         <v>111</v>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="F115" s="3"/>
     </row>
-    <row r="116" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B116" s="2">
         <f t="shared" si="1"/>
         <v>112</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="F116" s="3"/>
     </row>
-    <row r="117" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B117" s="2">
         <f t="shared" si="1"/>
         <v>113</v>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="F245" s="3"/>
     </row>
-    <row r="246" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B246" s="2">
         <f t="shared" si="3"/>
         <v>242</v>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="F246" s="3"/>
     </row>
-    <row r="247" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B247" s="2">
         <f t="shared" si="3"/>
         <v>243</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="F247" s="3"/>
     </row>
-    <row r="248" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B248" s="2">
         <f t="shared" si="3"/>
         <v>244</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="F248" s="3"/>
     </row>
-    <row r="249" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B249" s="2">
         <f t="shared" si="3"/>
         <v>245</v>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="F249" s="3"/>
     </row>
-    <row r="250" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B250" s="2">
         <f t="shared" si="3"/>
         <v>246</v>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="F250" s="3"/>
     </row>
-    <row r="251" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B251" s="2">
         <f t="shared" si="3"/>
         <v>247</v>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="F251" s="3"/>
     </row>
-    <row r="252" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B252" s="2">
         <f t="shared" si="3"/>
         <v>248</v>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="F252" s="3"/>
     </row>
-    <row r="253" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B253" s="2">
         <f t="shared" si="3"/>
         <v>249</v>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="F253" s="3"/>
     </row>
-    <row r="254" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B254" s="2">
         <f t="shared" si="3"/>
         <v>250</v>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F254" s="3"/>
     </row>
-    <row r="255" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B255" s="2">
         <f t="shared" si="3"/>
         <v>251</v>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="F255" s="3"/>
     </row>
-    <row r="256" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B256" s="2">
         <f t="shared" si="3"/>
         <v>252</v>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="F256" s="3"/>
     </row>
-    <row r="257" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B257" s="2">
         <f t="shared" si="3"/>
         <v>253</v>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="F257" s="3"/>
     </row>
-    <row r="258" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B258" s="2">
         <f t="shared" si="3"/>
         <v>254</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="F258" s="3"/>
     </row>
-    <row r="259" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B259" s="2">
         <f t="shared" si="3"/>
         <v>255</v>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="F259" s="3"/>
     </row>
-    <row r="260" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B260" s="2">
         <f t="shared" si="3"/>
         <v>256</v>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="F260" s="3"/>
     </row>
-    <row r="261" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B261" s="2">
         <f t="shared" si="3"/>
         <v>257</v>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="F261" s="3"/>
     </row>
-    <row r="262" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B262" s="2">
         <f t="shared" si="3"/>
         <v>258</v>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="F262" s="3"/>
     </row>
-    <row r="263" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B263" s="2">
         <f t="shared" si="3"/>
         <v>259</v>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="F263" s="3"/>
     </row>
-    <row r="264" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B264" s="2">
         <f t="shared" si="3"/>
         <v>260</v>
@@ -12440,10 +12440,25 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="ASLAM CASH &amp; CARRY (COLLEGER ROAD)"/>
-        <filter val="Aslam Mart (Behria Orchard)"/>
-        <filter val="Aslam Super Market ( LDA )"/>
-        <filter val="Aslam Super Market EME"/>
+        <filter val="EURO RANJERS MART"/>
+        <filter val="Euro store  (Academy Road)"/>
+        <filter val="EURO STORE (N F C )"/>
+        <filter val="EURO STORE (Rahamt chowk)"/>
+        <filter val="Euro Store (Scheme Mor)"/>
+        <filter val="Euro Store Airport Road"/>
+        <filter val="Euro Store Bedian Road"/>
+        <filter val="Euro Store College Road (Model Town)"/>
+        <filter val="EURO STORE CROWN BEHRIA TOWN"/>
+        <filter val="Euro Store E-2 (Wapda Town)"/>
+        <filter val="EURO STORE FATAH GARH"/>
+        <filter val="Euro Store G.T Road"/>
+        <filter val="Euro Store Garhi Shahu"/>
+        <filter val="EURO Store Hypermarket (Raiwind Road)"/>
+        <filter val="Euro Store Iqbal Town (Ranchna)"/>
+        <filter val="EURO STORE MARIYA STOP"/>
+        <filter val="EURO STORE PH VIII PARK VIEW"/>
+        <filter val="Euro Stores (G-1 Market)"/>
+        <filter val="EURO Stores (Nishat Colony)"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E8C828-E845-4673-B087-50215619DEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE0A262-0059-4ACA-82DF-B43ABCE679C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2867,7 +2867,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <f>B6+1</f>
         <v>3</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B22" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B23" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="F24" s="3"/>
     </row>
-    <row r="25" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B25" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="F27" s="3"/>
     </row>
-    <row r="28" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B28" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="F29" s="3"/>
     </row>
-    <row r="30" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B30" s="2">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="F36" s="3"/>
     </row>
-    <row r="37" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B37" s="2">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="F42" s="3"/>
     </row>
-    <row r="43" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B43" s="2">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="F47" s="3"/>
     </row>
-    <row r="48" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B48" s="2">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="F48" s="3"/>
     </row>
-    <row r="49" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B49" s="2">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="F49" s="3"/>
     </row>
-    <row r="50" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B50" s="2">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="F52" s="3"/>
     </row>
-    <row r="53" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B53" s="2">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="F54" s="3"/>
     </row>
-    <row r="55" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B55" s="2">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="F63" s="3"/>
     </row>
-    <row r="64" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B64" s="2">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="F67" s="3"/>
     </row>
-    <row r="68" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B68" s="2">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="F68" s="3"/>
     </row>
-    <row r="69" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B69" s="2">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="F70" s="3"/>
     </row>
-    <row r="71" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B71" s="2">
         <f t="shared" si="0"/>
         <v>67</v>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="F73" s="3"/>
     </row>
-    <row r="74" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B74" s="2">
         <f t="shared" ref="B74:B137" si="1">B73+1</f>
         <v>70</v>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="F74" s="3"/>
     </row>
-    <row r="75" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B75" s="2">
         <f t="shared" si="1"/>
         <v>71</v>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="F80" s="3"/>
     </row>
-    <row r="81" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B81" s="2">
         <f t="shared" si="1"/>
         <v>77</v>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="F81" s="3"/>
     </row>
-    <row r="82" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B82" s="2">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="F88" s="3"/>
     </row>
-    <row r="89" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B89" s="2">
         <f t="shared" si="1"/>
         <v>85</v>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="F91" s="3"/>
     </row>
-    <row r="92" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B92" s="2">
         <f t="shared" si="1"/>
         <v>88</v>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F92" s="3"/>
     </row>
-    <row r="93" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B93" s="2">
         <f t="shared" si="1"/>
         <v>89</v>
@@ -4290,7 +4290,7 @@
       </c>
       <c r="F93" s="3"/>
     </row>
-    <row r="94" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B94" s="2">
         <f t="shared" si="1"/>
         <v>90</v>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="F94" s="3"/>
     </row>
-    <row r="95" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B95" s="2">
         <f t="shared" si="1"/>
         <v>91</v>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="F95" s="3"/>
     </row>
-    <row r="96" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B96" s="2">
         <f t="shared" si="1"/>
         <v>92</v>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F96" s="3"/>
     </row>
-    <row r="97" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B97" s="2">
         <f t="shared" si="1"/>
         <v>93</v>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="F97" s="3"/>
     </row>
-    <row r="98" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B98" s="2">
         <f t="shared" si="1"/>
         <v>94</v>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="F102" s="3"/>
     </row>
-    <row r="103" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B103" s="2">
         <f t="shared" si="1"/>
         <v>99</v>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="F103" s="3"/>
     </row>
-    <row r="104" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B104" s="2">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="F106" s="3"/>
     </row>
-    <row r="107" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B107" s="2">
         <f t="shared" si="1"/>
         <v>103</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="F107" s="3"/>
     </row>
-    <row r="108" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B108" s="2">
         <f t="shared" si="1"/>
         <v>104</v>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="F108" s="3"/>
     </row>
-    <row r="109" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B109" s="2">
         <f t="shared" si="1"/>
         <v>105</v>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="F111" s="3"/>
     </row>
-    <row r="112" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B112" s="2">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="F112" s="3"/>
     </row>
-    <row r="113" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B113" s="2">
         <f t="shared" si="1"/>
         <v>109</v>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="F115" s="3"/>
     </row>
-    <row r="116" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B116" s="2">
         <f t="shared" si="1"/>
         <v>112</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="F116" s="3"/>
     </row>
-    <row r="117" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B117" s="2">
         <f t="shared" si="1"/>
         <v>113</v>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="F117" s="3"/>
     </row>
-    <row r="118" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B118" s="2">
         <f t="shared" si="1"/>
         <v>114</v>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="F124" s="3"/>
     </row>
-    <row r="125" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B125" s="2">
         <f t="shared" si="1"/>
         <v>121</v>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="F125" s="3"/>
     </row>
-    <row r="126" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B126" s="2">
         <f t="shared" si="1"/>
         <v>122</v>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="F129" s="3"/>
     </row>
-    <row r="130" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B130" s="2">
         <f t="shared" si="1"/>
         <v>126</v>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="F130" s="3"/>
     </row>
-    <row r="131" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B131" s="2">
         <f t="shared" si="1"/>
         <v>127</v>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="F132" s="3"/>
     </row>
-    <row r="133" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B133" s="2">
         <f t="shared" si="1"/>
         <v>129</v>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="F136" s="3"/>
     </row>
-    <row r="137" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B137" s="2">
         <f t="shared" si="1"/>
         <v>133</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="F137" s="3"/>
     </row>
-    <row r="138" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B138" s="2">
         <f t="shared" ref="B138:B201" si="2">B137+1</f>
         <v>134</v>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="F140" s="3"/>
     </row>
-    <row r="141" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B141" s="2">
         <f t="shared" si="2"/>
         <v>137</v>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="F141" s="3"/>
     </row>
-    <row r="142" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B142" s="2">
         <f t="shared" si="2"/>
         <v>138</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="F142" s="3"/>
     </row>
-    <row r="143" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B143" s="2">
         <f t="shared" si="2"/>
         <v>139</v>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="F143" s="3"/>
     </row>
-    <row r="144" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B144" s="2">
         <f t="shared" si="2"/>
         <v>140</v>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="F144" s="3"/>
     </row>
-    <row r="145" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B145" s="2">
         <f t="shared" si="2"/>
         <v>141</v>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="F145" s="3"/>
     </row>
-    <row r="146" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B146" s="2">
         <f t="shared" si="2"/>
         <v>142</v>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="F146" s="3"/>
     </row>
-    <row r="147" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B147" s="2">
         <f t="shared" si="2"/>
         <v>143</v>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="F147" s="3"/>
     </row>
-    <row r="148" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B148" s="2">
         <f t="shared" si="2"/>
         <v>144</v>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="F148" s="3"/>
     </row>
-    <row r="149" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B149" s="2">
         <f t="shared" si="2"/>
         <v>145</v>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="F149" s="3"/>
     </row>
-    <row r="150" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B150" s="2">
         <f t="shared" si="2"/>
         <v>146</v>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="F150" s="3"/>
     </row>
-    <row r="151" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B151" s="2">
         <f t="shared" si="2"/>
         <v>147</v>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="F151" s="3"/>
     </row>
-    <row r="152" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B152" s="2">
         <f t="shared" si="2"/>
         <v>148</v>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="F152" s="3"/>
     </row>
-    <row r="153" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B153" s="2">
         <f t="shared" si="2"/>
         <v>149</v>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="F153" s="3"/>
     </row>
-    <row r="154" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B154" s="2">
         <f t="shared" si="2"/>
         <v>150</v>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="F154" s="3"/>
     </row>
-    <row r="155" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B155" s="2">
         <f t="shared" si="2"/>
         <v>151</v>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="F155" s="3"/>
     </row>
-    <row r="156" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B156" s="2">
         <f t="shared" si="2"/>
         <v>152</v>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="F156" s="3"/>
     </row>
-    <row r="157" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B157" s="2">
         <f t="shared" si="2"/>
         <v>153</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="F157" s="3"/>
     </row>
-    <row r="158" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B158" s="2">
         <f t="shared" si="2"/>
         <v>154</v>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="F158" s="3"/>
     </row>
-    <row r="159" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B159" s="2">
         <f t="shared" si="2"/>
         <v>155</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F159" s="3"/>
     </row>
-    <row r="160" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B160" s="2">
         <f t="shared" si="2"/>
         <v>156</v>
@@ -5362,7 +5362,7 @@
       </c>
       <c r="F160" s="3"/>
     </row>
-    <row r="161" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B161" s="2">
         <f t="shared" si="2"/>
         <v>157</v>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="F161" s="3"/>
     </row>
-    <row r="162" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B162" s="2">
         <f t="shared" si="2"/>
         <v>158</v>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="F162" s="3"/>
     </row>
-    <row r="163" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B163" s="2">
         <f t="shared" si="2"/>
         <v>159</v>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="F163" s="3"/>
     </row>
-    <row r="164" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B164" s="2">
         <f t="shared" si="2"/>
         <v>160</v>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="F164" s="3"/>
     </row>
-    <row r="165" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B165" s="2">
         <f t="shared" si="2"/>
         <v>161</v>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="F165" s="3"/>
     </row>
-    <row r="166" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B166" s="2">
         <f t="shared" si="2"/>
         <v>162</v>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="F166" s="3"/>
     </row>
-    <row r="167" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B167" s="2">
         <f t="shared" si="2"/>
         <v>163</v>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="F167" s="3"/>
     </row>
-    <row r="168" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B168" s="2">
         <f t="shared" si="2"/>
         <v>164</v>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="F168" s="3"/>
     </row>
-    <row r="169" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B169" s="2">
         <f t="shared" si="2"/>
         <v>165</v>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="F169" s="3"/>
     </row>
-    <row r="170" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B170" s="2">
         <f t="shared" si="2"/>
         <v>166</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="F170" s="3"/>
     </row>
-    <row r="171" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B171" s="2">
         <f t="shared" si="2"/>
         <v>167</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="F171" s="3"/>
     </row>
-    <row r="172" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B172" s="2">
         <f t="shared" si="2"/>
         <v>168</v>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="F172" s="3"/>
     </row>
-    <row r="173" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B173" s="2">
         <f t="shared" si="2"/>
         <v>169</v>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="F173" s="3"/>
     </row>
-    <row r="174" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B174" s="2">
         <f t="shared" si="2"/>
         <v>170</v>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="F174" s="3"/>
     </row>
-    <row r="175" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B175" s="2">
         <f t="shared" si="2"/>
         <v>171</v>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="F175" s="3"/>
     </row>
-    <row r="176" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B176" s="2">
         <f t="shared" si="2"/>
         <v>172</v>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="F176" s="3"/>
     </row>
-    <row r="177" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B177" s="2">
         <f t="shared" si="2"/>
         <v>173</v>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F177" s="3"/>
     </row>
-    <row r="178" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B178" s="2">
         <f t="shared" si="2"/>
         <v>174</v>
@@ -5650,7 +5650,7 @@
       </c>
       <c r="F178" s="3"/>
     </row>
-    <row r="179" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B179" s="2">
         <f t="shared" si="2"/>
         <v>175</v>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F179" s="3"/>
     </row>
-    <row r="180" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B180" s="2">
         <f t="shared" si="2"/>
         <v>176</v>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="F180" s="3"/>
     </row>
-    <row r="181" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B181" s="2">
         <f t="shared" si="2"/>
         <v>177</v>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="F181" s="3"/>
     </row>
-    <row r="182" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B182" s="2">
         <f t="shared" si="2"/>
         <v>178</v>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="F182" s="3"/>
     </row>
-    <row r="183" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B183" s="2">
         <f t="shared" si="2"/>
         <v>179</v>
@@ -5730,7 +5730,7 @@
       </c>
       <c r="F183" s="3"/>
     </row>
-    <row r="184" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B184" s="2">
         <f t="shared" si="2"/>
         <v>180</v>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="F184" s="3"/>
     </row>
-    <row r="185" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B185" s="2">
         <f t="shared" si="2"/>
         <v>181</v>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="F185" s="3"/>
     </row>
-    <row r="186" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B186" s="2">
         <f t="shared" si="2"/>
         <v>182</v>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F186" s="3"/>
     </row>
-    <row r="187" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B187" s="2">
         <f t="shared" si="2"/>
         <v>183</v>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="F189" s="3"/>
     </row>
-    <row r="190" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B190" s="2">
         <f t="shared" si="2"/>
         <v>186</v>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="F193" s="3"/>
     </row>
-    <row r="194" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B194" s="2">
         <f t="shared" si="2"/>
         <v>190</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="F194" s="3"/>
     </row>
-    <row r="195" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B195" s="2">
         <f t="shared" si="2"/>
         <v>191</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="F195" s="3"/>
     </row>
-    <row r="196" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B196" s="2">
         <f t="shared" si="2"/>
         <v>192</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="F196" s="3"/>
     </row>
-    <row r="197" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B197" s="2">
         <f t="shared" si="2"/>
         <v>193</v>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="F198" s="3"/>
     </row>
-    <row r="199" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B199" s="2">
         <f t="shared" si="2"/>
         <v>195</v>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F208" s="3"/>
     </row>
-    <row r="209" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B209" s="2">
         <f t="shared" si="3"/>
         <v>205</v>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="F218" s="3"/>
     </row>
-    <row r="219" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B219" s="2">
         <f t="shared" si="3"/>
         <v>215</v>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="F219" s="3"/>
     </row>
-    <row r="220" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B220" s="2">
         <f t="shared" si="3"/>
         <v>216</v>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="F221" s="3"/>
     </row>
-    <row r="222" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B222" s="2">
         <f t="shared" si="3"/>
         <v>218</v>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="F222" s="3"/>
     </row>
-    <row r="223" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B223" s="2">
         <f t="shared" si="3"/>
         <v>219</v>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="F225" s="3"/>
     </row>
-    <row r="226" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B226" s="2">
         <f t="shared" si="3"/>
         <v>222</v>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="F226" s="3"/>
     </row>
-    <row r="227" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B227" s="2">
         <f t="shared" si="3"/>
         <v>223</v>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="F227" s="3"/>
     </row>
-    <row r="228" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B228" s="2">
         <f t="shared" si="3"/>
         <v>224</v>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="F228" s="3"/>
     </row>
-    <row r="229" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B229" s="2">
         <f t="shared" si="3"/>
         <v>225</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="F229" s="3"/>
     </row>
-    <row r="230" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B230" s="2">
         <f t="shared" si="3"/>
         <v>226</v>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="F230" s="3"/>
     </row>
-    <row r="231" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B231" s="2">
         <f t="shared" si="3"/>
         <v>227</v>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="F231" s="3"/>
     </row>
-    <row r="232" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B232" s="2">
         <f t="shared" si="3"/>
         <v>228</v>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="F232" s="3"/>
     </row>
-    <row r="233" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B233" s="2">
         <f t="shared" si="3"/>
         <v>229</v>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="F233" s="3"/>
     </row>
-    <row r="234" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B234" s="2">
         <f t="shared" si="3"/>
         <v>230</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="F234" s="3"/>
     </row>
-    <row r="235" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B235" s="2">
         <f t="shared" si="3"/>
         <v>231</v>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="F239" s="3"/>
     </row>
-    <row r="240" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B240" s="2">
         <f t="shared" si="3"/>
         <v>236</v>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="F243" s="3"/>
     </row>
-    <row r="244" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B244" s="2">
         <f t="shared" si="3"/>
         <v>240</v>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="F244" s="3"/>
     </row>
-    <row r="245" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B245" s="2">
         <f t="shared" si="3"/>
         <v>241</v>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="F245" s="3"/>
     </row>
-    <row r="246" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B246" s="2">
         <f t="shared" si="3"/>
         <v>242</v>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="F246" s="3"/>
     </row>
-    <row r="247" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B247" s="2">
         <f t="shared" si="3"/>
         <v>243</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="F247" s="3"/>
     </row>
-    <row r="248" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B248" s="2">
         <f t="shared" si="3"/>
         <v>244</v>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="F249" s="3"/>
     </row>
-    <row r="250" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B250" s="2">
         <f t="shared" si="3"/>
         <v>246</v>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="F250" s="3"/>
     </row>
-    <row r="251" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B251" s="2">
         <f t="shared" si="3"/>
         <v>247</v>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="F251" s="3"/>
     </row>
-    <row r="252" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B252" s="2">
         <f t="shared" si="3"/>
         <v>248</v>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="F252" s="3"/>
     </row>
-    <row r="253" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B253" s="2">
         <f t="shared" si="3"/>
         <v>249</v>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="F253" s="3"/>
     </row>
-    <row r="254" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B254" s="2">
         <f t="shared" si="3"/>
         <v>250</v>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F254" s="3"/>
     </row>
-    <row r="255" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B255" s="2">
         <f t="shared" si="3"/>
         <v>251</v>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="F255" s="3"/>
     </row>
-    <row r="256" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B256" s="2">
         <f t="shared" si="3"/>
         <v>252</v>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="F256" s="3"/>
     </row>
-    <row r="257" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B257" s="2">
         <f t="shared" si="3"/>
         <v>253</v>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="F257" s="3"/>
     </row>
-    <row r="258" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B258" s="2">
         <f t="shared" si="3"/>
         <v>254</v>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="F259" s="3"/>
     </row>
-    <row r="260" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B260" s="2">
         <f t="shared" si="3"/>
         <v>256</v>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="F260" s="3"/>
     </row>
-    <row r="261" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B261" s="2">
         <f t="shared" si="3"/>
         <v>257</v>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="F263" s="3"/>
     </row>
-    <row r="264" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B264" s="2">
         <f t="shared" si="3"/>
         <v>260</v>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="F269" s="3"/>
     </row>
-    <row r="270" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B270" s="2">
         <f t="shared" si="4"/>
         <v>266</v>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="F272" s="3"/>
     </row>
-    <row r="273" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B273" s="2">
         <f t="shared" si="4"/>
         <v>269</v>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="F278" s="3"/>
     </row>
-    <row r="279" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B279" s="2">
         <f t="shared" si="4"/>
         <v>275</v>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="F279" s="3"/>
     </row>
-    <row r="280" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B280" s="2">
         <f t="shared" si="4"/>
         <v>276</v>
@@ -7282,7 +7282,7 @@
       </c>
       <c r="F280" s="3"/>
     </row>
-    <row r="281" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B281" s="2">
         <f t="shared" si="4"/>
         <v>277</v>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="F282" s="3"/>
     </row>
-    <row r="283" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B283" s="2">
         <f t="shared" si="4"/>
         <v>279</v>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="F283" s="3"/>
     </row>
-    <row r="284" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B284" s="2">
         <f t="shared" si="4"/>
         <v>280</v>
@@ -7378,7 +7378,7 @@
       </c>
       <c r="F286" s="3"/>
     </row>
-    <row r="287" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B287" s="2">
         <f t="shared" si="4"/>
         <v>283</v>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="F290" s="3"/>
     </row>
-    <row r="291" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B291" s="2">
         <f t="shared" si="4"/>
         <v>287</v>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="F292" s="3"/>
     </row>
-    <row r="293" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B293" s="2">
         <f t="shared" si="4"/>
         <v>289</v>
@@ -7522,7 +7522,7 @@
       </c>
       <c r="F295" s="3"/>
     </row>
-    <row r="296" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B296" s="2">
         <f t="shared" si="4"/>
         <v>292</v>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="F297" s="3"/>
     </row>
-    <row r="298" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B298" s="2">
         <f t="shared" si="4"/>
         <v>294</v>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="F299" s="3"/>
     </row>
-    <row r="300" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B300" s="2">
         <f t="shared" si="4"/>
         <v>296</v>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="F300" s="3"/>
     </row>
-    <row r="301" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B301" s="2">
         <f t="shared" si="4"/>
         <v>297</v>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="F301" s="3"/>
     </row>
-    <row r="302" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B302" s="2">
         <f t="shared" si="4"/>
         <v>298</v>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="F302" s="3"/>
     </row>
-    <row r="303" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B303" s="2">
         <f t="shared" si="4"/>
         <v>299</v>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="F303" s="3"/>
     </row>
-    <row r="304" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B304" s="2">
         <f t="shared" si="4"/>
         <v>300</v>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="F304" s="3"/>
     </row>
-    <row r="305" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B305" s="2">
         <f t="shared" si="4"/>
         <v>301</v>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="F305" s="3"/>
     </row>
-    <row r="306" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B306" s="2">
         <f t="shared" si="4"/>
         <v>302</v>
@@ -7714,7 +7714,7 @@
       </c>
       <c r="F307" s="3"/>
     </row>
-    <row r="308" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B308" s="2">
         <f t="shared" si="4"/>
         <v>304</v>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="F309" s="3"/>
     </row>
-    <row r="310" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B310" s="2">
         <f t="shared" si="4"/>
         <v>306</v>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="F319" s="3"/>
     </row>
-    <row r="320" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B320" s="2">
         <f t="shared" si="4"/>
         <v>316</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="F321" s="3"/>
     </row>
-    <row r="322" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B322" s="2">
         <f t="shared" si="4"/>
         <v>318</v>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="F323" s="3"/>
     </row>
-    <row r="324" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B324" s="2">
         <f t="shared" si="4"/>
         <v>320</v>
@@ -8002,7 +8002,7 @@
       </c>
       <c r="F325" s="3"/>
     </row>
-    <row r="326" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B326" s="2">
         <f t="shared" si="4"/>
         <v>322</v>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="F330" s="3"/>
     </row>
-    <row r="331" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B331" s="2">
         <f t="shared" si="5"/>
         <v>327</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="F331" s="3"/>
     </row>
-    <row r="332" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B332" s="2">
         <f t="shared" si="5"/>
         <v>328</v>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="F332" s="3"/>
     </row>
-    <row r="333" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B333" s="2">
         <f t="shared" si="5"/>
         <v>329</v>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="F333" s="3"/>
     </row>
-    <row r="334" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B334" s="2">
         <f t="shared" si="5"/>
         <v>330</v>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="F335" s="3"/>
     </row>
-    <row r="336" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B336" s="2">
         <f t="shared" si="5"/>
         <v>332</v>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="F337" s="3"/>
     </row>
-    <row r="338" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B338" s="2">
         <f t="shared" si="5"/>
         <v>334</v>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="F358" s="3"/>
     </row>
-    <row r="359" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B359" s="2">
         <f t="shared" si="5"/>
         <v>355</v>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="F365" s="3"/>
     </row>
-    <row r="366" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B366" s="2">
         <f t="shared" si="5"/>
         <v>362</v>
@@ -8722,7 +8722,7 @@
       </c>
       <c r="F370" s="3"/>
     </row>
-    <row r="371" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B371" s="2">
         <f t="shared" si="5"/>
         <v>367</v>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="F374" s="3"/>
     </row>
-    <row r="375" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B375" s="2">
         <f t="shared" si="5"/>
         <v>371</v>
@@ -8802,7 +8802,7 @@
       </c>
       <c r="F375" s="3"/>
     </row>
-    <row r="376" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B376" s="2">
         <f t="shared" si="5"/>
         <v>372</v>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="F389" s="3"/>
     </row>
-    <row r="390" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B390" s="2">
         <f t="shared" si="5"/>
         <v>386</v>
@@ -9074,7 +9074,7 @@
       </c>
       <c r="F392" s="3"/>
     </row>
-    <row r="393" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B393" s="2">
         <f t="shared" si="5"/>
         <v>389</v>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="F393" s="3"/>
     </row>
-    <row r="394" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B394" s="2">
         <f t="shared" ref="B394:B457" si="6">B393+1</f>
         <v>390</v>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="F394" s="3"/>
     </row>
-    <row r="395" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B395" s="2">
         <f t="shared" si="6"/>
         <v>391</v>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="F395" s="3"/>
     </row>
-    <row r="396" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B396" s="2">
         <f t="shared" si="6"/>
         <v>392</v>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="F396" s="3"/>
     </row>
-    <row r="397" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B397" s="2">
         <f t="shared" si="6"/>
         <v>393</v>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="F397" s="3"/>
     </row>
-    <row r="398" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B398" s="2">
         <f t="shared" si="6"/>
         <v>394</v>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="F398" s="3"/>
     </row>
-    <row r="399" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B399" s="2">
         <f t="shared" si="6"/>
         <v>395</v>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="F399" s="3"/>
     </row>
-    <row r="400" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B400" s="2">
         <f t="shared" si="6"/>
         <v>396</v>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="F400" s="3"/>
     </row>
-    <row r="401" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B401" s="2">
         <f t="shared" si="6"/>
         <v>397</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="F401" s="3"/>
     </row>
-    <row r="402" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B402" s="2">
         <f t="shared" si="6"/>
         <v>398</v>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="F402" s="3"/>
     </row>
-    <row r="403" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B403" s="2">
         <f t="shared" si="6"/>
         <v>399</v>
@@ -9250,7 +9250,7 @@
       </c>
       <c r="F403" s="3"/>
     </row>
-    <row r="404" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B404" s="2">
         <f t="shared" si="6"/>
         <v>400</v>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="F404" s="3"/>
     </row>
-    <row r="405" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B405" s="2">
         <f t="shared" si="6"/>
         <v>401</v>
@@ -9346,7 +9346,7 @@
       </c>
       <c r="F409" s="3"/>
     </row>
-    <row r="410" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B410" s="2">
         <f t="shared" si="6"/>
         <v>406</v>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="F410" s="3"/>
     </row>
-    <row r="411" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B411" s="2">
         <f t="shared" si="6"/>
         <v>407</v>
@@ -9426,7 +9426,7 @@
       </c>
       <c r="F414" s="3"/>
     </row>
-    <row r="415" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B415" s="2">
         <f t="shared" si="6"/>
         <v>411</v>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="F415" s="3"/>
     </row>
-    <row r="416" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B416" s="2">
         <f t="shared" si="6"/>
         <v>412</v>
@@ -9490,7 +9490,7 @@
       </c>
       <c r="F418" s="3"/>
     </row>
-    <row r="419" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B419" s="2">
         <f t="shared" si="6"/>
         <v>415</v>
@@ -9538,7 +9538,7 @@
       </c>
       <c r="F421" s="3"/>
     </row>
-    <row r="422" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B422" s="2">
         <f t="shared" si="6"/>
         <v>418</v>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="F422" s="3"/>
     </row>
-    <row r="423" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B423" s="2">
         <f t="shared" si="6"/>
         <v>419</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F426" s="3"/>
     </row>
-    <row r="427" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B427" s="2">
         <f t="shared" si="6"/>
         <v>423</v>
@@ -9634,7 +9634,7 @@
       </c>
       <c r="F427" s="3"/>
     </row>
-    <row r="428" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B428" s="2">
         <f t="shared" si="6"/>
         <v>424</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="F428" s="3"/>
     </row>
-    <row r="429" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B429" s="2">
         <f t="shared" si="6"/>
         <v>425</v>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="F429" s="3"/>
     </row>
-    <row r="430" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B430" s="2">
         <f t="shared" si="6"/>
         <v>426</v>
@@ -9714,7 +9714,7 @@
       </c>
       <c r="F432" s="3"/>
     </row>
-    <row r="433" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B433" s="2">
         <f t="shared" si="6"/>
         <v>429</v>
@@ -9762,7 +9762,7 @@
       </c>
       <c r="F435" s="3"/>
     </row>
-    <row r="436" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B436" s="2">
         <f t="shared" si="6"/>
         <v>432</v>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="F437" s="3"/>
     </row>
-    <row r="438" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B438" s="2">
         <f t="shared" si="6"/>
         <v>434</v>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="F441" s="3"/>
     </row>
-    <row r="442" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B442" s="2">
         <f t="shared" si="6"/>
         <v>438</v>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="F442" s="3"/>
     </row>
-    <row r="443" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B443" s="2">
         <f t="shared" si="6"/>
         <v>439</v>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="F444" s="3"/>
     </row>
-    <row r="445" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B445" s="2">
         <f t="shared" si="6"/>
         <v>441</v>
@@ -9922,7 +9922,7 @@
       </c>
       <c r="F445" s="3"/>
     </row>
-    <row r="446" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B446" s="2">
         <f t="shared" si="6"/>
         <v>442</v>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="F446" s="3"/>
     </row>
-    <row r="447" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B447" s="2">
         <f t="shared" si="6"/>
         <v>443</v>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="F447" s="3"/>
     </row>
-    <row r="448" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B448" s="2">
         <f t="shared" si="6"/>
         <v>444</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="F448" s="3"/>
     </row>
-    <row r="449" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B449" s="2">
         <f t="shared" si="6"/>
         <v>445</v>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="F449" s="3"/>
     </row>
-    <row r="450" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B450" s="2">
         <f t="shared" si="6"/>
         <v>446</v>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="F450" s="3"/>
     </row>
-    <row r="451" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B451" s="2">
         <f t="shared" si="6"/>
         <v>447</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="F453" s="3"/>
     </row>
-    <row r="454" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B454" s="2">
         <f t="shared" si="6"/>
         <v>450</v>
@@ -10098,7 +10098,7 @@
       </c>
       <c r="F456" s="3"/>
     </row>
-    <row r="457" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B457" s="2">
         <f t="shared" si="6"/>
         <v>453</v>
@@ -10130,7 +10130,7 @@
       </c>
       <c r="F458" s="3"/>
     </row>
-    <row r="459" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B459" s="2">
         <f t="shared" si="7"/>
         <v>455</v>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="F464" s="3"/>
     </row>
-    <row r="465" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B465" s="2">
         <f t="shared" si="7"/>
         <v>461</v>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="F468" s="3"/>
     </row>
-    <row r="469" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B469" s="2">
         <f t="shared" si="7"/>
         <v>465</v>
@@ -10306,7 +10306,7 @@
       </c>
       <c r="F469" s="3"/>
     </row>
-    <row r="470" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B470" s="2">
         <f t="shared" si="7"/>
         <v>466</v>
@@ -10322,7 +10322,7 @@
       </c>
       <c r="F470" s="3"/>
     </row>
-    <row r="471" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B471" s="2">
         <f t="shared" si="7"/>
         <v>467</v>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="F471" s="3"/>
     </row>
-    <row r="472" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B472" s="2">
         <f t="shared" si="7"/>
         <v>468</v>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="F473" s="3"/>
     </row>
-    <row r="474" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B474" s="2">
         <f t="shared" si="7"/>
         <v>470</v>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="F474" s="3"/>
     </row>
-    <row r="475" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B475" s="2">
         <f t="shared" si="7"/>
         <v>471</v>
@@ -10418,7 +10418,7 @@
       </c>
       <c r="F476" s="3"/>
     </row>
-    <row r="477" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B477" s="2">
         <f t="shared" si="7"/>
         <v>473</v>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="F477" s="3"/>
     </row>
-    <row r="478" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B478" s="2">
         <f t="shared" si="7"/>
         <v>474</v>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="F478" s="3"/>
     </row>
-    <row r="479" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B479" s="2">
         <f t="shared" si="7"/>
         <v>475</v>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="F479" s="3"/>
     </row>
-    <row r="480" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B480" s="2">
         <f t="shared" si="7"/>
         <v>476</v>
@@ -10482,7 +10482,7 @@
       </c>
       <c r="F480" s="3"/>
     </row>
-    <row r="481" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B481" s="2">
         <f t="shared" si="7"/>
         <v>477</v>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="F481" s="3"/>
     </row>
-    <row r="482" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B482" s="2">
         <f t="shared" si="7"/>
         <v>478</v>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="F482" s="3"/>
     </row>
-    <row r="483" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B483" s="2">
         <f t="shared" si="7"/>
         <v>479</v>
@@ -10530,7 +10530,7 @@
       </c>
       <c r="F483" s="3"/>
     </row>
-    <row r="484" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B484" s="2">
         <f t="shared" si="7"/>
         <v>480</v>
@@ -10546,7 +10546,7 @@
       </c>
       <c r="F484" s="3"/>
     </row>
-    <row r="485" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B485" s="2">
         <f t="shared" si="7"/>
         <v>481</v>
@@ -10562,7 +10562,7 @@
       </c>
       <c r="F485" s="3"/>
     </row>
-    <row r="486" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B486" s="2">
         <f t="shared" si="7"/>
         <v>482</v>
@@ -10578,7 +10578,7 @@
       </c>
       <c r="F486" s="3"/>
     </row>
-    <row r="487" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B487" s="2">
         <f t="shared" si="7"/>
         <v>483</v>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="F487" s="3"/>
     </row>
-    <row r="488" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B488" s="2">
         <f t="shared" si="7"/>
         <v>484</v>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="F489" s="3"/>
     </row>
-    <row r="490" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B490" s="2">
         <f t="shared" si="7"/>
         <v>486</v>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="F490" s="3"/>
     </row>
-    <row r="491" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B491" s="2">
         <f t="shared" si="7"/>
         <v>487</v>
@@ -10690,7 +10690,7 @@
       </c>
       <c r="F493" s="3"/>
     </row>
-    <row r="494" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B494" s="2">
         <f t="shared" si="7"/>
         <v>490</v>
@@ -10706,7 +10706,7 @@
       </c>
       <c r="F494" s="3"/>
     </row>
-    <row r="495" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B495" s="2">
         <f t="shared" si="7"/>
         <v>491</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="F496" s="3"/>
     </row>
-    <row r="497" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B497" s="2">
         <f t="shared" si="7"/>
         <v>493</v>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="F499" s="3"/>
     </row>
-    <row r="500" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B500" s="2">
         <f t="shared" si="7"/>
         <v>496</v>
@@ -10818,7 +10818,7 @@
       </c>
       <c r="F501" s="3"/>
     </row>
-    <row r="502" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B502" s="2">
         <f t="shared" si="7"/>
         <v>498</v>
@@ -10882,7 +10882,7 @@
       </c>
       <c r="F505" s="3"/>
     </row>
-    <row r="506" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B506" s="2">
         <f t="shared" si="7"/>
         <v>502</v>
@@ -10898,7 +10898,7 @@
       </c>
       <c r="F506" s="3"/>
     </row>
-    <row r="507" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B507" s="2">
         <f t="shared" si="7"/>
         <v>503</v>
@@ -10962,7 +10962,7 @@
       </c>
       <c r="F510" s="3"/>
     </row>
-    <row r="511" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B511" s="2">
         <f t="shared" si="7"/>
         <v>507</v>
@@ -11026,7 +11026,7 @@
       </c>
       <c r="F514" s="3"/>
     </row>
-    <row r="515" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B515" s="2">
         <f t="shared" si="7"/>
         <v>511</v>
@@ -11058,7 +11058,7 @@
       </c>
       <c r="F516" s="3"/>
     </row>
-    <row r="517" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B517" s="2">
         <f t="shared" si="7"/>
         <v>513</v>
@@ -11154,7 +11154,7 @@
       </c>
       <c r="F522" s="3"/>
     </row>
-    <row r="523" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B523" s="2">
         <f t="shared" si="8"/>
         <v>519</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="F525" s="3"/>
     </row>
-    <row r="526" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B526" s="2">
         <f t="shared" si="8"/>
         <v>522</v>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="F526" s="3"/>
     </row>
-    <row r="527" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B527" s="2">
         <f t="shared" si="8"/>
         <v>523</v>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="F527" s="3"/>
     </row>
-    <row r="528" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B528" s="2">
         <f t="shared" si="8"/>
         <v>524</v>
@@ -11266,7 +11266,7 @@
       </c>
       <c r="F529" s="3"/>
     </row>
-    <row r="530" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B530" s="2">
         <f t="shared" si="8"/>
         <v>526</v>
@@ -11282,7 +11282,7 @@
       </c>
       <c r="F530" s="3"/>
     </row>
-    <row r="531" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B531" s="2">
         <f t="shared" si="8"/>
         <v>527</v>
@@ -11362,7 +11362,7 @@
       </c>
       <c r="F535" s="3"/>
     </row>
-    <row r="536" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B536" s="2">
         <f t="shared" si="8"/>
         <v>532</v>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="F539" s="3"/>
     </row>
-    <row r="540" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B540" s="2">
         <f t="shared" si="8"/>
         <v>536</v>
@@ -11554,7 +11554,7 @@
       </c>
       <c r="F547" s="3"/>
     </row>
-    <row r="548" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B548" s="2">
         <f t="shared" si="8"/>
         <v>544</v>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="F553" s="3"/>
     </row>
-    <row r="554" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B554" s="2">
         <f t="shared" si="8"/>
         <v>550</v>
@@ -11714,7 +11714,7 @@
       </c>
       <c r="F557" s="3"/>
     </row>
-    <row r="558" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B558" s="2">
         <f t="shared" si="8"/>
         <v>554</v>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="F562" s="3"/>
     </row>
-    <row r="563" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B563" s="2">
         <f t="shared" si="8"/>
         <v>559</v>
@@ -11810,7 +11810,7 @@
       </c>
       <c r="F563" s="3"/>
     </row>
-    <row r="564" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B564" s="2">
         <f t="shared" si="8"/>
         <v>560</v>
@@ -11826,7 +11826,7 @@
       </c>
       <c r="F564" s="3"/>
     </row>
-    <row r="565" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B565" s="2">
         <f t="shared" si="8"/>
         <v>561</v>
@@ -11842,7 +11842,7 @@
       </c>
       <c r="F565" s="3"/>
     </row>
-    <row r="566" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B566" s="2">
         <f t="shared" si="8"/>
         <v>562</v>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="F566" s="3"/>
     </row>
-    <row r="567" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B567" s="2">
         <f t="shared" si="8"/>
         <v>563</v>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="F567" s="3"/>
     </row>
-    <row r="568" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B568" s="2">
         <f t="shared" si="8"/>
         <v>564</v>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="F568" s="3"/>
     </row>
-    <row r="569" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B569" s="2">
         <f t="shared" si="8"/>
         <v>565</v>
@@ -11906,7 +11906,7 @@
       </c>
       <c r="F569" s="3"/>
     </row>
-    <row r="570" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B570" s="2">
         <f t="shared" si="8"/>
         <v>566</v>
@@ -11922,7 +11922,7 @@
       </c>
       <c r="F570" s="3"/>
     </row>
-    <row r="571" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B571" s="2">
         <f t="shared" si="8"/>
         <v>567</v>
@@ -11938,7 +11938,7 @@
       </c>
       <c r="F571" s="3"/>
     </row>
-    <row r="572" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B572" s="2">
         <f t="shared" si="8"/>
         <v>568</v>
@@ -11954,7 +11954,7 @@
       </c>
       <c r="F572" s="3"/>
     </row>
-    <row r="573" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B573" s="2">
         <f t="shared" si="8"/>
         <v>569</v>
@@ -11970,7 +11970,7 @@
       </c>
       <c r="F573" s="3"/>
     </row>
-    <row r="574" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B574" s="2">
         <f t="shared" si="8"/>
         <v>570</v>
@@ -11986,7 +11986,7 @@
       </c>
       <c r="F574" s="3"/>
     </row>
-    <row r="575" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B575" s="2">
         <f t="shared" si="8"/>
         <v>571</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="F575" s="3"/>
     </row>
-    <row r="576" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B576" s="2">
         <f t="shared" si="8"/>
         <v>572</v>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="F583" s="3"/>
     </row>
-    <row r="584" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B584" s="2">
         <f t="shared" si="8"/>
         <v>580</v>
@@ -12226,7 +12226,7 @@
       </c>
       <c r="F589" s="3"/>
     </row>
-    <row r="590" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B590" s="2">
         <f t="shared" si="9"/>
         <v>586</v>
@@ -12306,7 +12306,7 @@
       </c>
       <c r="F594" s="3"/>
     </row>
-    <row r="595" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B595" s="2">
         <f t="shared" si="9"/>
         <v>591</v>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="F596" s="3"/>
     </row>
-    <row r="597" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B597" s="2">
         <f t="shared" si="9"/>
         <v>593</v>
@@ -12370,7 +12370,7 @@
       </c>
       <c r="F598" s="3"/>
     </row>
-    <row r="599" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B599" s="6">
         <v>595</v>
       </c>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="E600" s="5"/>
     </row>
-    <row r="601" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="C601" s="4"/>
     </row>
     <row r="602" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
@@ -12439,26 +12439,268 @@
   </sheetData>
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
-      <filters>
-        <filter val="EURO RANJERS MART"/>
-        <filter val="Euro store  (Academy Road)"/>
-        <filter val="EURO STORE (N F C )"/>
+      <filters blank="1">
+        <filter val="24/7 MART ASKARI X SECTOR F"/>
+        <filter val="ACE MART P BLOCK SABZAZAR"/>
+        <filter val="Ajmair Food (Main Market)"/>
+        <filter val="Ajmair Foods (Abdali Chowk)"/>
+        <filter val="Ajmair Foods (Karim Block)"/>
+        <filter val="Ajmair Foods (Kashmir Block)"/>
+        <filter val="Ajmair Foods (Liaqat Chowk)"/>
+        <filter val="Ajmair Foods (Maulana Shaukat Ali Road LHR)"/>
+        <filter val="Ajmair Foods (Neelam Block)"/>
+        <filter val="Ajmair Foods (Shalimar Link Road)"/>
+        <filter val="Ajmair Foods Ameer Chowk"/>
+        <filter val="Ajmair Foods Pvt LTD (M-T C Block)"/>
+        <filter val="Ajmair Foods Pvt LTD (M-T M Block)"/>
+        <filter val="Ajmair Foods Pvt LTD (Tulip Block)"/>
+        <filter val="Ajmair Foods Pvt LTD Rehmat Chowk"/>
+        <filter val="Ajmair Foods Pvt.LTD (Barket Market)"/>
+        <filter val="Ajmair Foods PvtLTD (H Block)"/>
+        <filter val="Ajmair Foods PvtLTD (Raja Market)"/>
+        <filter val="Ajmair Foods PvtLTD (Shaday Wal Chowk)"/>
+        <filter val="Ajmair Foods PvtLTD H-3 Block Joher Town"/>
+        <filter val="Akbari Store (Jain Mandir)"/>
+        <filter val="AL BARKAT MART"/>
+        <filter val="Al Fatah (Hussian Chowk)"/>
+        <filter val="Al Fatah (Lake City)"/>
+        <filter val="AL GHANI ROSE BLOCK"/>
+        <filter val="Al Karim Departmental Store (Model Town)"/>
+        <filter val="AL KHAN (SHAHDHRA CHOWK)"/>
+        <filter val="AL KHAN BAKERS  (BHOBTIAN CHOWK)"/>
+        <filter val="AL KHAN BAKERS (NESPAK)"/>
+        <filter val="AL KHAN FOODS (BEHRIA TOWN)"/>
+        <filter val="AL KHAN FOODS VALENCIA"/>
+        <filter val="AL KOSAR DEPARTMENTAL STORE (SHAH FAREED)"/>
+        <filter val="Al Sheikh Bakers"/>
+        <filter val="AL ZEESHAN SUPER MARKET"/>
+        <filter val="AL-FATAH H-BLOCK"/>
+        <filter val="ALI SUPER STORE BHATA CHOWK"/>
+        <filter val="AL-KHAN FOODS (WAPDA TOWN)"/>
+        <filter val="Askari  Depsrtmental Store Punjab Society"/>
+        <filter val="Askari Departmental Store College Road"/>
+        <filter val="Aslam Super Market ( LDA )"/>
+        <filter val="Aslam Super Market EME"/>
+        <filter val="ASTER SUPERMARKET"/>
+        <filter val="BASHIR SONS PHARMACY (AMEER CHOWK)"/>
+        <filter val="BASHIR SONS PHARMACY (ASKARI XI)"/>
+        <filter val="BASHIR SONS PHARMACY (LAKE CITY)"/>
+        <filter val="BASHIR SONS PHARMACY (NAKHUDA CHOWK)"/>
+        <filter val="BASHIR SONS PHARMACY (RACHNA BLOCK)"/>
+        <filter val="BILAL SUPER STORE H BLOCK DHA"/>
+        <filter val="BIN KHALID STORE VALENCIA TOWN"/>
+        <filter val="BLINK MART STORE PVT LTD"/>
+        <filter val="BUNDU KHAN (AIRPORT)"/>
+        <filter val="BUNDU KHAN (AKBAR CHOWK)"/>
+        <filter val="BUNDU KHAN (ALLAMA IQBAL TOWN)"/>
+        <filter val="BUNDU KHAN (CHUBURJI)"/>
+        <filter val="BUNDU KHAN (DHAROGEWALA)"/>
+        <filter val="BUNDU KHAN (FF DHA)"/>
+        <filter val="BUNDU KHAN (GARI SHAHU)"/>
+        <filter val="BUNDU KHAN (GULSHAN RAVI)"/>
+        <filter val="BUNDU KHAN (HUSSAIN CHOWK)."/>
+        <filter val="BUNDU KHAN (JALLO MORE)"/>
+        <filter val="BUNDU KHAN (KARIM PARK)"/>
+        <filter val="BUNDU KHAN (LAKSHAMI CHOWK)"/>
+        <filter val="BUNDU KHAN (LIAQAT CHOWK)"/>
+        <filter val="BUNDU KHAN (MODEL TOWN LINK ROAD)"/>
+        <filter val="BUNDU KHAN (OUTFALL ROAD)"/>
+        <filter val="BUNDU KHAN (PARAGON CITY)"/>
+        <filter val="BUNDU KHAN (PARK VIEW)"/>
+        <filter val="BUNDU KHAN (PIA ROAD)"/>
+        <filter val="BUNDU KHAN (PUNJAB SOCIETY)"/>
+        <filter val="BUNDU KHAN (REHMAN GARDEN)"/>
+        <filter val="BUNDU KHAN (SADDAR)"/>
+        <filter val="BUNDU KHAN (SAFA WALA CHOWK)"/>
+        <filter val="BUNDU KHAN (SAMNABAD)"/>
+        <filter val="BUNDU KHAN (SHADBAGH TOKY WALA CHOWK)"/>
+        <filter val="BUNDU KHAN (SHAHDHRA GT ROAD)"/>
+        <filter val="BUNDU KHAN (SHAMA CINEMA)"/>
+        <filter val="BUNDU KHAN (TAJ BAGH)"/>
+        <filter val="BUNDU KHAN (YATEEM KHANA)"/>
+        <filter val="BUNDU KHAN ASKARI 11"/>
+        <filter val="BUNDU KHAN BEHRIA TOWN"/>
+        <filter val="BUNDU KHAN EME"/>
+        <filter val="BUNDU KHAN FAISAL TOWN"/>
+        <filter val="BUNDU KHAN G-1 MARKET"/>
+        <filter val="BUNDU KHAN GT-ROAD"/>
+        <filter val="BUNDU KHAN H BLOCK (DHA)"/>
+        <filter val="BUNDU KHAN LAKE CITY"/>
+        <filter val="BUNDU KHAN MAIN BLVD DHA"/>
+        <filter val="BUNDU KHAN NASEER ABAD"/>
+        <filter val="BUNDU KHAN PINE AVENUE"/>
+        <filter val="BUNDU KHAN RAIWIND ROAD"/>
+        <filter val="BUNDU KHAN T BLOCK"/>
+        <filter val="BUNDU KHAN TAJ PURA"/>
+        <filter val="BUNDU KHAN WAPDA TOWN"/>
+        <filter val="BUNDU KHAN YOUHANABAD"/>
+        <filter val="BUNDUN KHAN (DHA PHASE-6)"/>
+        <filter val="BUNDUN KHAN (ISLAMPURA)"/>
+        <filter val="Butt Sweet (G-1 Market)"/>
+        <filter val="BUTT SWEETS &amp; BAKERS  (PIA ROAD)"/>
+        <filter val="BUTT SWEETS &amp; BAKERS (GT ROAD)"/>
+        <filter val="BUTT SWEETS &amp; BAKERS (VALENCIA)"/>
+        <filter val="BUTT SWEETS (LIAQAT CHOWK)"/>
+        <filter val="Butt Sweets Laxmi Chowk"/>
+        <filter val="CITY GENERAL STORE BEGUM KOT"/>
+        <filter val="CLINIX PHARMACY ASKARI 11"/>
+        <filter val="CLINIX PHARMACY LIAQAT CHOWK SABZAZAR"/>
+        <filter val="CLINIX PHARMACY SHAHKAM CHOWK"/>
+        <filter val="CLINIX PHARMACY Z BLOCK"/>
+        <filter val="CLINIX SUPER MARKET  (THOKER)"/>
+        <filter val="CLINIX SUPER MARKET (AMEER CHOWK)"/>
+        <filter val="CLINIX SUPERMARKET (CHOWK NAKHUDA)"/>
+        <filter val="CLINIX SUPERMARKET (JOHAR TOWN)"/>
+        <filter val="CLINIX SUPERMARKET (LAKE CITY)"/>
+        <filter val="CLINIX SUPERMARKET (MANAWAN)"/>
+        <filter val="CLINIX SUPERMARKET (SAMANABAD)"/>
+        <filter val="CLINIX SUPERMARKET (SHAM NAGAR)"/>
+        <filter val="CROWN SUPER MARKET"/>
+        <filter val="CSD Askari X"/>
+        <filter val="DAILY BASKET STORES (ICON VALLETY SOCIETY)"/>
+        <filter val="DIVINE BAKERS &amp; SWEETS (WAHDAT ROAD)"/>
+        <filter val="Easy Mart (Talwar Chowk"/>
         <filter val="EURO STORE (Rahamt chowk)"/>
-        <filter val="Euro Store (Scheme Mor)"/>
-        <filter val="Euro Store Airport Road"/>
-        <filter val="Euro Store Bedian Road"/>
-        <filter val="Euro Store College Road (Model Town)"/>
-        <filter val="EURO STORE CROWN BEHRIA TOWN"/>
-        <filter val="Euro Store E-2 (Wapda Town)"/>
-        <filter val="EURO STORE FATAH GARH"/>
-        <filter val="Euro Store G.T Road"/>
-        <filter val="Euro Store Garhi Shahu"/>
         <filter val="EURO Store Hypermarket (Raiwind Road)"/>
-        <filter val="Euro Store Iqbal Town (Ranchna)"/>
-        <filter val="EURO STORE MARIYA STOP"/>
         <filter val="EURO STORE PH VIII PARK VIEW"/>
         <filter val="Euro Stores (G-1 Market)"/>
-        <filter val="EURO Stores (Nishat Colony)"/>
+        <filter val="FDPP CONSUMER H BLOCK DHA"/>
+        <filter val="FDPP CONSUMER Main Market"/>
+        <filter val="Fresh Inn Bakers (Johar Town)"/>
+        <filter val="Fresh Inn Bakers (Link Road)"/>
+        <filter val="FRESHLY MART SECTOR B ASKARI 11"/>
+        <filter val="Galaxy Super Market"/>
+        <filter val="GOOD LUCK MUSLIM TOWN"/>
+        <filter val="Gourmet - K Block"/>
+        <filter val="Gourmet - Z Block"/>
+        <filter val="Gourmet (Pak Arab)"/>
+        <filter val="Gourmet A  Block"/>
+        <filter val="Gourmet Awan Market"/>
+        <filter val="GOURMET BAKERS (25 NO STOP) BEGIUM KOT"/>
+        <filter val="GOURMET BAKERS (AL REHMAN GARDEN)"/>
+        <filter val="GOURMET BAKERS (KOT ABDUL MALIK)"/>
+        <filter val="GOURMET BAKERS (MACHIS FACTORY)"/>
+        <filter val="GOURMET BAKERS (MANAWWAN)"/>
+        <filter val="GOURMET BAKERS (SHAHDARA MORE)"/>
+        <filter val="Gourmet Barkat Market"/>
+        <filter val="Gourmet Bhatta Chowk"/>
+        <filter val="Gourmet C block"/>
+        <filter val="Gourmet FF Block"/>
+        <filter val="Gourmet Ghalib Market"/>
+        <filter val="Gourmet Girja Chowk"/>
+        <filter val="Gourmet H Block"/>
+        <filter val="Gourmet -Kareem Block"/>
+        <filter val="Gourmet -Kareem Park"/>
+        <filter val="Gourmet -Karishn nagar"/>
+        <filter val="Gourmet -Kot Khaja Saeed"/>
+        <filter val="Gourmet -Liaqat Chowk"/>
+        <filter val="Gourmet Link Rd"/>
+        <filter val="Gourmet -Rustam Park"/>
+        <filter val="Gourmet Shalimar Link Road"/>
+        <filter val="Gourmet Umer Chowk"/>
+        <filter val="Gourmet XX Block"/>
+        <filter val="Gourmet -Yateem Khana"/>
+        <filter val="Hafiz Sweet Bakers"/>
+        <filter val="HAJVERY FOODS (O G BAKERS MARGZAR ROAD)"/>
+        <filter val="HAJVERY FOODS (O G BAKERS) SHADBAGH"/>
+        <filter val="HAJVERY FOODS (OG BAKERS BADAMIBAGH)"/>
+        <filter val="HAJVERY FOODS (OG BAKERS KRISHAN NAGAR)"/>
+        <filter val="HAJVERY FOODS (OG BAKERS WALTON ROAD)"/>
+        <filter val="HASHMAT SUPER MARKET (AUDIT ACCOUNT)"/>
+        <filter val="HIKMA MART (PLAZA NO 60 PARAGON)"/>
+        <filter val="HIKMA MART 1 (81 BRADE WAY PARAGON)"/>
+        <filter val="HIKMA SUPER STORE ASKARI 11"/>
+        <filter val="HIKMAH SUPER STORE"/>
+        <filter val="HIMALAYA SUPER MARKET"/>
+        <filter val="HKB (Phase V)"/>
+        <filter val="HKB Y Block"/>
+        <filter val="Jalal sons (Askari 10 F sector ) 01"/>
+        <filter val="JALAL SONS (ASKARI 11 B BLOCK) 02"/>
+        <filter val="JALAL SONS (C BLOCK MODEL TOWN) 02"/>
+        <filter val="JALAL SONS (DHA C BLOCK,PHASE 6) 02"/>
+        <filter val="JALAL SONS (DHA Y BLOCK) 02"/>
+        <filter val="Jalal Sons (H Block) 01"/>
+        <filter val="JALAL SONS (HUSSAIN CHOWK GULBERG III) 02"/>
+        <filter val="Jalal Sons (Lake City) 01"/>
+        <filter val="Jalal sons (Main Market) 01"/>
+        <filter val="JALAL SONS (MODEL TOWN LINK ROAD) 02"/>
+        <filter val="Jalal Sons (PAF Market) 01 main Market"/>
+        <filter val="JALAL SONS (PHASE 8 EX PARK VIEW) 02"/>
+        <filter val="JALAL SONS (SHAUKAT KHANUM) 02"/>
+        <filter val="JALAL SONS (TALWAR CHOWK) 02"/>
+        <filter val="Jalal Sons Askari X (01)"/>
+        <filter val="K-mart"/>
+        <filter val="KRRAVE TECHNOLOGIES (PRIVATE) LIMITED"/>
+        <filter val="Lake City Management Pvt Ltd"/>
+        <filter val="LARAIB BAKERS &amp; SWEET (SHADMAN)"/>
+        <filter val="LARAIB BAKERS &amp; SWEETS (YATEEM kHANA)"/>
+        <filter val="LARAIB BAKERS (ISLAMPURA)"/>
+        <filter val="LARAIB BAKERS ALI TOWN (RAIWIND ROAD)"/>
+        <filter val="LARAIB BAKERS SWEETS (Ghulshan Ravi)"/>
+        <filter val="LARAIB BAKERS SWEETS (YOUHANABAD)"/>
+        <filter val="LARAIB FOODS (BEGUM KOT)"/>
+        <filter val="LARAIB FOODS (SHALIMAR LINK ROAD)"/>
+        <filter val="LARAIB FOODS LIAQAT CHOWK SABZAZAR"/>
+        <filter val="LUTF MART (Barki Road)"/>
+        <filter val="M/S AL KHAN FOODS (ALI TOWN) THOKAR"/>
+        <filter val="M/S AL KHAN FOODS (FAZAIA HOUSING SOCIETY)"/>
+        <filter val="M/S AL KHAN FOODS (REHMAN GARDEN)"/>
+        <filter val="M/S AL KHAN FOODS (WAHADAT ROAD)"/>
+        <filter val="M/S BUTT SWEETS &amp; BAKERS (KUTCHEHRI BAZAR)"/>
+        <filter val="M/S J.K.S Cash Carry"/>
+        <filter val="Malmo Bakers (Ali View garden)"/>
+        <filter val="Malmo Bakers (Chung )"/>
+        <filter val="Malmo Bakers (College Road)"/>
+        <filter val="Malmo Bakers (Punjab Soc)"/>
+        <filter val="Malmo Bakers (Usmania Tower)"/>
+        <filter val="Malmo Bakery G.T Road"/>
+        <filter val="Malmo Bakery Gulshan Ravi"/>
+        <filter val="Malmo Bakery Neelam Block"/>
+        <filter val="Malmo Bakery Samnabad"/>
+        <filter val="Malmo Bakery Shalimar Link Road"/>
+        <filter val="Malmo Bakery Shama"/>
+        <filter val="Malmo Bakery Wahdat Road"/>
+        <filter val="Malmo DHA Q- BLOCK"/>
+        <filter val="Malmo Liaqat chowk"/>
+        <filter val="MALMO SWEETS &amp; BAKERS (AL-KABIR TOWN)"/>
+        <filter val="MALMO SWEETS &amp; BAKERS (BEHRIA ORCHARD)"/>
+        <filter val="MARKET SECURE 1D HBFC"/>
+        <filter val="MM CASH &amp; CARRY ASKARI XI"/>
+        <filter val="MS RUBAIKA CASH AND CARRY"/>
+        <filter val="NEMAT KHANA STORES (PRIVATE) LIMITED"/>
+        <filter val="NEW RAHAT BAKERS GS (ALLAMA IQBAL ROAD)"/>
+        <filter val="OG BAKERS (GREENWOOD SOCIETY)"/>
+        <filter val="ORGANICS (PAK HEIGHTS BUILDING)"/>
+        <filter val="PAK MADINA SUPER STORE (BEGAM KOT)"/>
+        <filter val="PREMIER MART FP ROAD OPP AWAN MARKET"/>
+        <filter val="PRIME STORE MAIN MARKET"/>
+        <filter val="PRMIE PICK CASH &amp; CARRY REHMAN GARDEN"/>
+        <filter val="PUNJAB CASH &amp; CARRY (ASKARI 11)"/>
+        <filter val="Quick Check Departmental Store"/>
+        <filter val="QUICK MART PARK VIEW MULTAN RD"/>
+        <filter val="RAHIM STORE THOKAR NIAZ BAIG"/>
+        <filter val="RAINBOW CASH &amp; CARRY (MAIN BARKI ROAD)"/>
+        <filter val="REHMAN KHALIS (PVT.) LIMITED"/>
+        <filter val="SAFIA MANZOOR (LIAQAT CHOWK)"/>
+        <filter val="Servaid (T Block) DHA"/>
+        <filter val="SHEZAN BAKERS ABID MARKET"/>
+        <filter val="SHEZAN BAKERS AIRLINE SOCIETY"/>
+        <filter val="SHEZAN BAKERS C BLOCK MODEL TOWN"/>
+        <filter val="SHEZAN BAKERS CAVALRY GROUND"/>
+        <filter val="SHEZAN BAKERS DHA FF"/>
+        <filter val="SHEZAN BAKERS GARHI SHAHU"/>
+        <filter val="SHEZAN BAKERS GIRJA CHOWK"/>
+        <filter val="SHEZAN BAKERS H BLOCK"/>
+        <filter val="SHEZAN BAKERS IQBAL TOWN"/>
+        <filter val="SHEZAN BAKERS LIBERTY MARKET"/>
+        <filter val="SHEZAN BAKERS LOWER MALL"/>
+        <filter val="SHEZAN BAKERS MAIN MARKET"/>
+        <filter val="SHEZAN BAKERS MOCHI PURA"/>
+        <filter val="SHEZAN BAKERS SHER PAO"/>
+        <filter val="TARIQ MART (DHA M BLOCK)"/>
+        <filter val="Umer Super Market (Joher Town)"/>
+        <filter val="Victoria (Link Road)"/>
+        <filter val="ZOHRA MART MAIN MARKET"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE0A262-0059-4ACA-82DF-B43ABCE679C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38FA433E-5B73-46B9-8890-9811C350940E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2867,7 +2867,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <f>B6+1</f>
         <v>3</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B22" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B23" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="F24" s="3"/>
     </row>
-    <row r="25" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B25" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="F27" s="3"/>
     </row>
-    <row r="28" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B28" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="F29" s="3"/>
     </row>
-    <row r="30" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B30" s="2">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="F36" s="3"/>
     </row>
-    <row r="37" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B37" s="2">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="F42" s="3"/>
     </row>
-    <row r="43" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B43" s="2">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="F47" s="3"/>
     </row>
-    <row r="48" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B48" s="2">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="F48" s="3"/>
     </row>
-    <row r="49" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B49" s="2">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="F49" s="3"/>
     </row>
-    <row r="50" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B50" s="2">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="F52" s="3"/>
     </row>
-    <row r="53" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B53" s="2">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="F54" s="3"/>
     </row>
-    <row r="55" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B55" s="2">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="F63" s="3"/>
     </row>
-    <row r="64" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B64" s="2">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="F67" s="3"/>
     </row>
-    <row r="68" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B68" s="2">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="F68" s="3"/>
     </row>
-    <row r="69" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B69" s="2">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="F70" s="3"/>
     </row>
-    <row r="71" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B71" s="2">
         <f t="shared" si="0"/>
         <v>67</v>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="F73" s="3"/>
     </row>
-    <row r="74" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B74" s="2">
         <f t="shared" ref="B74:B137" si="1">B73+1</f>
         <v>70</v>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="F74" s="3"/>
     </row>
-    <row r="75" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B75" s="2">
         <f t="shared" si="1"/>
         <v>71</v>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="F80" s="3"/>
     </row>
-    <row r="81" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B81" s="2">
         <f t="shared" si="1"/>
         <v>77</v>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="F81" s="3"/>
     </row>
-    <row r="82" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B82" s="2">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="F88" s="3"/>
     </row>
-    <row r="89" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B89" s="2">
         <f t="shared" si="1"/>
         <v>85</v>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="F91" s="3"/>
     </row>
-    <row r="92" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B92" s="2">
         <f t="shared" si="1"/>
         <v>88</v>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F92" s="3"/>
     </row>
-    <row r="93" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B93" s="2">
         <f t="shared" si="1"/>
         <v>89</v>
@@ -4290,7 +4290,7 @@
       </c>
       <c r="F93" s="3"/>
     </row>
-    <row r="94" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B94" s="2">
         <f t="shared" si="1"/>
         <v>90</v>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="F94" s="3"/>
     </row>
-    <row r="95" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B95" s="2">
         <f t="shared" si="1"/>
         <v>91</v>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="F95" s="3"/>
     </row>
-    <row r="96" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B96" s="2">
         <f t="shared" si="1"/>
         <v>92</v>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F96" s="3"/>
     </row>
-    <row r="97" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B97" s="2">
         <f t="shared" si="1"/>
         <v>93</v>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="F97" s="3"/>
     </row>
-    <row r="98" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B98" s="2">
         <f t="shared" si="1"/>
         <v>94</v>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="F102" s="3"/>
     </row>
-    <row r="103" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B103" s="2">
         <f t="shared" si="1"/>
         <v>99</v>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="F103" s="3"/>
     </row>
-    <row r="104" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B104" s="2">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="F106" s="3"/>
     </row>
-    <row r="107" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B107" s="2">
         <f t="shared" si="1"/>
         <v>103</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="F107" s="3"/>
     </row>
-    <row r="108" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B108" s="2">
         <f t="shared" si="1"/>
         <v>104</v>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="F108" s="3"/>
     </row>
-    <row r="109" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B109" s="2">
         <f t="shared" si="1"/>
         <v>105</v>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="F111" s="3"/>
     </row>
-    <row r="112" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B112" s="2">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="F112" s="3"/>
     </row>
-    <row r="113" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B113" s="2">
         <f t="shared" si="1"/>
         <v>109</v>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="F115" s="3"/>
     </row>
-    <row r="116" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B116" s="2">
         <f t="shared" si="1"/>
         <v>112</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="F116" s="3"/>
     </row>
-    <row r="117" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B117" s="2">
         <f t="shared" si="1"/>
         <v>113</v>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="F117" s="3"/>
     </row>
-    <row r="118" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B118" s="2">
         <f t="shared" si="1"/>
         <v>114</v>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="F124" s="3"/>
     </row>
-    <row r="125" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B125" s="2">
         <f t="shared" si="1"/>
         <v>121</v>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="F125" s="3"/>
     </row>
-    <row r="126" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B126" s="2">
         <f t="shared" si="1"/>
         <v>122</v>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="F129" s="3"/>
     </row>
-    <row r="130" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B130" s="2">
         <f t="shared" si="1"/>
         <v>126</v>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="F130" s="3"/>
     </row>
-    <row r="131" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B131" s="2">
         <f t="shared" si="1"/>
         <v>127</v>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="F132" s="3"/>
     </row>
-    <row r="133" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B133" s="2">
         <f t="shared" si="1"/>
         <v>129</v>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="F136" s="3"/>
     </row>
-    <row r="137" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B137" s="2">
         <f t="shared" si="1"/>
         <v>133</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="F137" s="3"/>
     </row>
-    <row r="138" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B138" s="2">
         <f t="shared" ref="B138:B201" si="2">B137+1</f>
         <v>134</v>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="F140" s="3"/>
     </row>
-    <row r="141" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B141" s="2">
         <f t="shared" si="2"/>
         <v>137</v>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="F141" s="3"/>
     </row>
-    <row r="142" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B142" s="2">
         <f t="shared" si="2"/>
         <v>138</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="F142" s="3"/>
     </row>
-    <row r="143" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B143" s="2">
         <f t="shared" si="2"/>
         <v>139</v>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="F143" s="3"/>
     </row>
-    <row r="144" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B144" s="2">
         <f t="shared" si="2"/>
         <v>140</v>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="F144" s="3"/>
     </row>
-    <row r="145" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B145" s="2">
         <f t="shared" si="2"/>
         <v>141</v>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="F145" s="3"/>
     </row>
-    <row r="146" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B146" s="2">
         <f t="shared" si="2"/>
         <v>142</v>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="F146" s="3"/>
     </row>
-    <row r="147" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B147" s="2">
         <f t="shared" si="2"/>
         <v>143</v>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="F147" s="3"/>
     </row>
-    <row r="148" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B148" s="2">
         <f t="shared" si="2"/>
         <v>144</v>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="F148" s="3"/>
     </row>
-    <row r="149" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B149" s="2">
         <f t="shared" si="2"/>
         <v>145</v>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="F149" s="3"/>
     </row>
-    <row r="150" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B150" s="2">
         <f t="shared" si="2"/>
         <v>146</v>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="F150" s="3"/>
     </row>
-    <row r="151" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B151" s="2">
         <f t="shared" si="2"/>
         <v>147</v>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="F151" s="3"/>
     </row>
-    <row r="152" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B152" s="2">
         <f t="shared" si="2"/>
         <v>148</v>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="F152" s="3"/>
     </row>
-    <row r="153" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B153" s="2">
         <f t="shared" si="2"/>
         <v>149</v>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="F153" s="3"/>
     </row>
-    <row r="154" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B154" s="2">
         <f t="shared" si="2"/>
         <v>150</v>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="F154" s="3"/>
     </row>
-    <row r="155" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B155" s="2">
         <f t="shared" si="2"/>
         <v>151</v>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="F155" s="3"/>
     </row>
-    <row r="156" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B156" s="2">
         <f t="shared" si="2"/>
         <v>152</v>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="F156" s="3"/>
     </row>
-    <row r="157" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B157" s="2">
         <f t="shared" si="2"/>
         <v>153</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="F157" s="3"/>
     </row>
-    <row r="158" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B158" s="2">
         <f t="shared" si="2"/>
         <v>154</v>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="F158" s="3"/>
     </row>
-    <row r="159" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B159" s="2">
         <f t="shared" si="2"/>
         <v>155</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F159" s="3"/>
     </row>
-    <row r="160" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B160" s="2">
         <f t="shared" si="2"/>
         <v>156</v>
@@ -5362,7 +5362,7 @@
       </c>
       <c r="F160" s="3"/>
     </row>
-    <row r="161" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B161" s="2">
         <f t="shared" si="2"/>
         <v>157</v>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="F161" s="3"/>
     </row>
-    <row r="162" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B162" s="2">
         <f t="shared" si="2"/>
         <v>158</v>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="F162" s="3"/>
     </row>
-    <row r="163" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B163" s="2">
         <f t="shared" si="2"/>
         <v>159</v>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="F163" s="3"/>
     </row>
-    <row r="164" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B164" s="2">
         <f t="shared" si="2"/>
         <v>160</v>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="F164" s="3"/>
     </row>
-    <row r="165" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B165" s="2">
         <f t="shared" si="2"/>
         <v>161</v>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="F165" s="3"/>
     </row>
-    <row r="166" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B166" s="2">
         <f t="shared" si="2"/>
         <v>162</v>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="F166" s="3"/>
     </row>
-    <row r="167" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B167" s="2">
         <f t="shared" si="2"/>
         <v>163</v>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="F167" s="3"/>
     </row>
-    <row r="168" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B168" s="2">
         <f t="shared" si="2"/>
         <v>164</v>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="F168" s="3"/>
     </row>
-    <row r="169" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B169" s="2">
         <f t="shared" si="2"/>
         <v>165</v>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="F169" s="3"/>
     </row>
-    <row r="170" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B170" s="2">
         <f t="shared" si="2"/>
         <v>166</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="F170" s="3"/>
     </row>
-    <row r="171" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B171" s="2">
         <f t="shared" si="2"/>
         <v>167</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="F171" s="3"/>
     </row>
-    <row r="172" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B172" s="2">
         <f t="shared" si="2"/>
         <v>168</v>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="F172" s="3"/>
     </row>
-    <row r="173" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B173" s="2">
         <f t="shared" si="2"/>
         <v>169</v>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="F173" s="3"/>
     </row>
-    <row r="174" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B174" s="2">
         <f t="shared" si="2"/>
         <v>170</v>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="F174" s="3"/>
     </row>
-    <row r="175" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B175" s="2">
         <f t="shared" si="2"/>
         <v>171</v>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="F175" s="3"/>
     </row>
-    <row r="176" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B176" s="2">
         <f t="shared" si="2"/>
         <v>172</v>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="F176" s="3"/>
     </row>
-    <row r="177" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B177" s="2">
         <f t="shared" si="2"/>
         <v>173</v>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F177" s="3"/>
     </row>
-    <row r="178" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B178" s="2">
         <f t="shared" si="2"/>
         <v>174</v>
@@ -5650,7 +5650,7 @@
       </c>
       <c r="F178" s="3"/>
     </row>
-    <row r="179" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B179" s="2">
         <f t="shared" si="2"/>
         <v>175</v>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F179" s="3"/>
     </row>
-    <row r="180" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B180" s="2">
         <f t="shared" si="2"/>
         <v>176</v>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="F180" s="3"/>
     </row>
-    <row r="181" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B181" s="2">
         <f t="shared" si="2"/>
         <v>177</v>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="F181" s="3"/>
     </row>
-    <row r="182" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B182" s="2">
         <f t="shared" si="2"/>
         <v>178</v>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="F182" s="3"/>
     </row>
-    <row r="183" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B183" s="2">
         <f t="shared" si="2"/>
         <v>179</v>
@@ -5730,7 +5730,7 @@
       </c>
       <c r="F183" s="3"/>
     </row>
-    <row r="184" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B184" s="2">
         <f t="shared" si="2"/>
         <v>180</v>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="F184" s="3"/>
     </row>
-    <row r="185" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B185" s="2">
         <f t="shared" si="2"/>
         <v>181</v>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="F185" s="3"/>
     </row>
-    <row r="186" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B186" s="2">
         <f t="shared" si="2"/>
         <v>182</v>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F186" s="3"/>
     </row>
-    <row r="187" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B187" s="2">
         <f t="shared" si="2"/>
         <v>183</v>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="F189" s="3"/>
     </row>
-    <row r="190" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B190" s="2">
         <f t="shared" si="2"/>
         <v>186</v>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="F193" s="3"/>
     </row>
-    <row r="194" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B194" s="2">
         <f t="shared" si="2"/>
         <v>190</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="F194" s="3"/>
     </row>
-    <row r="195" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B195" s="2">
         <f t="shared" si="2"/>
         <v>191</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="F195" s="3"/>
     </row>
-    <row r="196" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B196" s="2">
         <f t="shared" si="2"/>
         <v>192</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="F196" s="3"/>
     </row>
-    <row r="197" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B197" s="2">
         <f t="shared" si="2"/>
         <v>193</v>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="F198" s="3"/>
     </row>
-    <row r="199" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B199" s="2">
         <f t="shared" si="2"/>
         <v>195</v>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F208" s="3"/>
     </row>
-    <row r="209" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B209" s="2">
         <f t="shared" si="3"/>
         <v>205</v>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="F218" s="3"/>
     </row>
-    <row r="219" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B219" s="2">
         <f t="shared" si="3"/>
         <v>215</v>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="F219" s="3"/>
     </row>
-    <row r="220" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B220" s="2">
         <f t="shared" si="3"/>
         <v>216</v>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="F221" s="3"/>
     </row>
-    <row r="222" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B222" s="2">
         <f t="shared" si="3"/>
         <v>218</v>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="F222" s="3"/>
     </row>
-    <row r="223" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B223" s="2">
         <f t="shared" si="3"/>
         <v>219</v>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="F225" s="3"/>
     </row>
-    <row r="226" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B226" s="2">
         <f t="shared" si="3"/>
         <v>222</v>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="F226" s="3"/>
     </row>
-    <row r="227" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B227" s="2">
         <f t="shared" si="3"/>
         <v>223</v>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="F227" s="3"/>
     </row>
-    <row r="228" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B228" s="2">
         <f t="shared" si="3"/>
         <v>224</v>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="F228" s="3"/>
     </row>
-    <row r="229" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="229" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B229" s="2">
         <f t="shared" si="3"/>
         <v>225</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="F229" s="3"/>
     </row>
-    <row r="230" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B230" s="2">
         <f t="shared" si="3"/>
         <v>226</v>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="F230" s="3"/>
     </row>
-    <row r="231" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="231" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B231" s="2">
         <f t="shared" si="3"/>
         <v>227</v>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="F231" s="3"/>
     </row>
-    <row r="232" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="232" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B232" s="2">
         <f t="shared" si="3"/>
         <v>228</v>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="F232" s="3"/>
     </row>
-    <row r="233" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="233" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B233" s="2">
         <f t="shared" si="3"/>
         <v>229</v>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="F233" s="3"/>
     </row>
-    <row r="234" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="234" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B234" s="2">
         <f t="shared" si="3"/>
         <v>230</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="F234" s="3"/>
     </row>
-    <row r="235" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="235" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B235" s="2">
         <f t="shared" si="3"/>
         <v>231</v>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="F239" s="3"/>
     </row>
-    <row r="240" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="240" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B240" s="2">
         <f t="shared" si="3"/>
         <v>236</v>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="F243" s="3"/>
     </row>
-    <row r="244" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="244" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B244" s="2">
         <f t="shared" si="3"/>
         <v>240</v>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="F244" s="3"/>
     </row>
-    <row r="245" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="245" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B245" s="2">
         <f t="shared" si="3"/>
         <v>241</v>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="F245" s="3"/>
     </row>
-    <row r="246" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B246" s="2">
         <f t="shared" si="3"/>
         <v>242</v>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="F246" s="3"/>
     </row>
-    <row r="247" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B247" s="2">
         <f t="shared" si="3"/>
         <v>243</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="F247" s="3"/>
     </row>
-    <row r="248" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B248" s="2">
         <f t="shared" si="3"/>
         <v>244</v>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="F249" s="3"/>
     </row>
-    <row r="250" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B250" s="2">
         <f t="shared" si="3"/>
         <v>246</v>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="F250" s="3"/>
     </row>
-    <row r="251" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B251" s="2">
         <f t="shared" si="3"/>
         <v>247</v>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="F251" s="3"/>
     </row>
-    <row r="252" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B252" s="2">
         <f t="shared" si="3"/>
         <v>248</v>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="F252" s="3"/>
     </row>
-    <row r="253" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B253" s="2">
         <f t="shared" si="3"/>
         <v>249</v>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="F253" s="3"/>
     </row>
-    <row r="254" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B254" s="2">
         <f t="shared" si="3"/>
         <v>250</v>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F254" s="3"/>
     </row>
-    <row r="255" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B255" s="2">
         <f t="shared" si="3"/>
         <v>251</v>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="F255" s="3"/>
     </row>
-    <row r="256" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B256" s="2">
         <f t="shared" si="3"/>
         <v>252</v>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="F256" s="3"/>
     </row>
-    <row r="257" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B257" s="2">
         <f t="shared" si="3"/>
         <v>253</v>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="F257" s="3"/>
     </row>
-    <row r="258" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B258" s="2">
         <f t="shared" si="3"/>
         <v>254</v>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="F259" s="3"/>
     </row>
-    <row r="260" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B260" s="2">
         <f t="shared" si="3"/>
         <v>256</v>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="F260" s="3"/>
     </row>
-    <row r="261" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B261" s="2">
         <f t="shared" si="3"/>
         <v>257</v>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="F263" s="3"/>
     </row>
-    <row r="264" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B264" s="2">
         <f t="shared" si="3"/>
         <v>260</v>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="F269" s="3"/>
     </row>
-    <row r="270" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="270" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B270" s="2">
         <f t="shared" si="4"/>
         <v>266</v>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="F272" s="3"/>
     </row>
-    <row r="273" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="273" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B273" s="2">
         <f t="shared" si="4"/>
         <v>269</v>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="F278" s="3"/>
     </row>
-    <row r="279" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="279" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B279" s="2">
         <f t="shared" si="4"/>
         <v>275</v>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="F279" s="3"/>
     </row>
-    <row r="280" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="280" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B280" s="2">
         <f t="shared" si="4"/>
         <v>276</v>
@@ -7282,7 +7282,7 @@
       </c>
       <c r="F280" s="3"/>
     </row>
-    <row r="281" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="281" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B281" s="2">
         <f t="shared" si="4"/>
         <v>277</v>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="F282" s="3"/>
     </row>
-    <row r="283" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="283" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B283" s="2">
         <f t="shared" si="4"/>
         <v>279</v>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="F283" s="3"/>
     </row>
-    <row r="284" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="284" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B284" s="2">
         <f t="shared" si="4"/>
         <v>280</v>
@@ -7378,7 +7378,7 @@
       </c>
       <c r="F286" s="3"/>
     </row>
-    <row r="287" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="287" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B287" s="2">
         <f t="shared" si="4"/>
         <v>283</v>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="F290" s="3"/>
     </row>
-    <row r="291" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="291" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B291" s="2">
         <f t="shared" si="4"/>
         <v>287</v>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="F292" s="3"/>
     </row>
-    <row r="293" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="293" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B293" s="2">
         <f t="shared" si="4"/>
         <v>289</v>
@@ -7522,7 +7522,7 @@
       </c>
       <c r="F295" s="3"/>
     </row>
-    <row r="296" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="296" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B296" s="2">
         <f t="shared" si="4"/>
         <v>292</v>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="F297" s="3"/>
     </row>
-    <row r="298" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="298" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B298" s="2">
         <f t="shared" si="4"/>
         <v>294</v>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="F299" s="3"/>
     </row>
-    <row r="300" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="300" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B300" s="2">
         <f t="shared" si="4"/>
         <v>296</v>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="F300" s="3"/>
     </row>
-    <row r="301" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="301" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B301" s="2">
         <f t="shared" si="4"/>
         <v>297</v>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="F301" s="3"/>
     </row>
-    <row r="302" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="302" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B302" s="2">
         <f t="shared" si="4"/>
         <v>298</v>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="F302" s="3"/>
     </row>
-    <row r="303" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="303" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B303" s="2">
         <f t="shared" si="4"/>
         <v>299</v>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="F303" s="3"/>
     </row>
-    <row r="304" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="304" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B304" s="2">
         <f t="shared" si="4"/>
         <v>300</v>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="F304" s="3"/>
     </row>
-    <row r="305" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="305" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B305" s="2">
         <f t="shared" si="4"/>
         <v>301</v>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="F305" s="3"/>
     </row>
-    <row r="306" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="306" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B306" s="2">
         <f t="shared" si="4"/>
         <v>302</v>
@@ -7714,7 +7714,7 @@
       </c>
       <c r="F307" s="3"/>
     </row>
-    <row r="308" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="308" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B308" s="2">
         <f t="shared" si="4"/>
         <v>304</v>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="F309" s="3"/>
     </row>
-    <row r="310" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="310" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B310" s="2">
         <f t="shared" si="4"/>
         <v>306</v>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="F319" s="3"/>
     </row>
-    <row r="320" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="320" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B320" s="2">
         <f t="shared" si="4"/>
         <v>316</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="F321" s="3"/>
     </row>
-    <row r="322" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="322" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B322" s="2">
         <f t="shared" si="4"/>
         <v>318</v>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="F323" s="3"/>
     </row>
-    <row r="324" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="324" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B324" s="2">
         <f t="shared" si="4"/>
         <v>320</v>
@@ -8002,7 +8002,7 @@
       </c>
       <c r="F325" s="3"/>
     </row>
-    <row r="326" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="326" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B326" s="2">
         <f t="shared" si="4"/>
         <v>322</v>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="F330" s="3"/>
     </row>
-    <row r="331" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="331" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B331" s="2">
         <f t="shared" si="5"/>
         <v>327</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="F331" s="3"/>
     </row>
-    <row r="332" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="332" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B332" s="2">
         <f t="shared" si="5"/>
         <v>328</v>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="F332" s="3"/>
     </row>
-    <row r="333" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="333" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B333" s="2">
         <f t="shared" si="5"/>
         <v>329</v>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="F333" s="3"/>
     </row>
-    <row r="334" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="334" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B334" s="2">
         <f t="shared" si="5"/>
         <v>330</v>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="F335" s="3"/>
     </row>
-    <row r="336" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="336" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B336" s="2">
         <f t="shared" si="5"/>
         <v>332</v>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="F337" s="3"/>
     </row>
-    <row r="338" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="338" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B338" s="2">
         <f t="shared" si="5"/>
         <v>334</v>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="F358" s="3"/>
     </row>
-    <row r="359" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="359" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B359" s="2">
         <f t="shared" si="5"/>
         <v>355</v>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="F365" s="3"/>
     </row>
-    <row r="366" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="366" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B366" s="2">
         <f t="shared" si="5"/>
         <v>362</v>
@@ -8722,7 +8722,7 @@
       </c>
       <c r="F370" s="3"/>
     </row>
-    <row r="371" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="371" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B371" s="2">
         <f t="shared" si="5"/>
         <v>367</v>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="F374" s="3"/>
     </row>
-    <row r="375" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="375" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B375" s="2">
         <f t="shared" si="5"/>
         <v>371</v>
@@ -8802,7 +8802,7 @@
       </c>
       <c r="F375" s="3"/>
     </row>
-    <row r="376" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="376" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B376" s="2">
         <f t="shared" si="5"/>
         <v>372</v>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="F389" s="3"/>
     </row>
-    <row r="390" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="390" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B390" s="2">
         <f t="shared" si="5"/>
         <v>386</v>
@@ -9074,7 +9074,7 @@
       </c>
       <c r="F392" s="3"/>
     </row>
-    <row r="393" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="393" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B393" s="2">
         <f t="shared" si="5"/>
         <v>389</v>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="F393" s="3"/>
     </row>
-    <row r="394" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="394" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B394" s="2">
         <f t="shared" ref="B394:B457" si="6">B393+1</f>
         <v>390</v>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="F394" s="3"/>
     </row>
-    <row r="395" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="395" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B395" s="2">
         <f t="shared" si="6"/>
         <v>391</v>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="F395" s="3"/>
     </row>
-    <row r="396" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="396" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B396" s="2">
         <f t="shared" si="6"/>
         <v>392</v>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="F396" s="3"/>
     </row>
-    <row r="397" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="397" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B397" s="2">
         <f t="shared" si="6"/>
         <v>393</v>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="F397" s="3"/>
     </row>
-    <row r="398" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="398" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B398" s="2">
         <f t="shared" si="6"/>
         <v>394</v>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="F398" s="3"/>
     </row>
-    <row r="399" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="399" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B399" s="2">
         <f t="shared" si="6"/>
         <v>395</v>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="F399" s="3"/>
     </row>
-    <row r="400" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="400" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B400" s="2">
         <f t="shared" si="6"/>
         <v>396</v>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="F400" s="3"/>
     </row>
-    <row r="401" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="401" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B401" s="2">
         <f t="shared" si="6"/>
         <v>397</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="F401" s="3"/>
     </row>
-    <row r="402" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="402" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B402" s="2">
         <f t="shared" si="6"/>
         <v>398</v>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="F402" s="3"/>
     </row>
-    <row r="403" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="403" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B403" s="2">
         <f t="shared" si="6"/>
         <v>399</v>
@@ -9250,7 +9250,7 @@
       </c>
       <c r="F403" s="3"/>
     </row>
-    <row r="404" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="404" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B404" s="2">
         <f t="shared" si="6"/>
         <v>400</v>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="F404" s="3"/>
     </row>
-    <row r="405" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="405" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B405" s="2">
         <f t="shared" si="6"/>
         <v>401</v>
@@ -9346,7 +9346,7 @@
       </c>
       <c r="F409" s="3"/>
     </row>
-    <row r="410" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="410" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B410" s="2">
         <f t="shared" si="6"/>
         <v>406</v>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="F410" s="3"/>
     </row>
-    <row r="411" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="411" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B411" s="2">
         <f t="shared" si="6"/>
         <v>407</v>
@@ -9426,7 +9426,7 @@
       </c>
       <c r="F414" s="3"/>
     </row>
-    <row r="415" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B415" s="2">
         <f t="shared" si="6"/>
         <v>411</v>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="F415" s="3"/>
     </row>
-    <row r="416" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B416" s="2">
         <f t="shared" si="6"/>
         <v>412</v>
@@ -9490,7 +9490,7 @@
       </c>
       <c r="F418" s="3"/>
     </row>
-    <row r="419" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="419" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B419" s="2">
         <f t="shared" si="6"/>
         <v>415</v>
@@ -9538,7 +9538,7 @@
       </c>
       <c r="F421" s="3"/>
     </row>
-    <row r="422" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="422" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B422" s="2">
         <f t="shared" si="6"/>
         <v>418</v>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="F422" s="3"/>
     </row>
-    <row r="423" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="423" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B423" s="2">
         <f t="shared" si="6"/>
         <v>419</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F426" s="3"/>
     </row>
-    <row r="427" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="427" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B427" s="2">
         <f t="shared" si="6"/>
         <v>423</v>
@@ -9634,7 +9634,7 @@
       </c>
       <c r="F427" s="3"/>
     </row>
-    <row r="428" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="428" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B428" s="2">
         <f t="shared" si="6"/>
         <v>424</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="F428" s="3"/>
     </row>
-    <row r="429" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="429" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B429" s="2">
         <f t="shared" si="6"/>
         <v>425</v>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="F429" s="3"/>
     </row>
-    <row r="430" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="430" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B430" s="2">
         <f t="shared" si="6"/>
         <v>426</v>
@@ -9714,7 +9714,7 @@
       </c>
       <c r="F432" s="3"/>
     </row>
-    <row r="433" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="433" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B433" s="2">
         <f t="shared" si="6"/>
         <v>429</v>
@@ -9762,7 +9762,7 @@
       </c>
       <c r="F435" s="3"/>
     </row>
-    <row r="436" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="436" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B436" s="2">
         <f t="shared" si="6"/>
         <v>432</v>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="F437" s="3"/>
     </row>
-    <row r="438" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="438" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B438" s="2">
         <f t="shared" si="6"/>
         <v>434</v>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="F441" s="3"/>
     </row>
-    <row r="442" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="442" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B442" s="2">
         <f t="shared" si="6"/>
         <v>438</v>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="F442" s="3"/>
     </row>
-    <row r="443" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="443" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B443" s="2">
         <f t="shared" si="6"/>
         <v>439</v>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="F444" s="3"/>
     </row>
-    <row r="445" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="445" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B445" s="2">
         <f t="shared" si="6"/>
         <v>441</v>
@@ -9922,7 +9922,7 @@
       </c>
       <c r="F445" s="3"/>
     </row>
-    <row r="446" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="446" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B446" s="2">
         <f t="shared" si="6"/>
         <v>442</v>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="F446" s="3"/>
     </row>
-    <row r="447" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="447" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B447" s="2">
         <f t="shared" si="6"/>
         <v>443</v>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="F447" s="3"/>
     </row>
-    <row r="448" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="448" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B448" s="2">
         <f t="shared" si="6"/>
         <v>444</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="F448" s="3"/>
     </row>
-    <row r="449" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="449" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B449" s="2">
         <f t="shared" si="6"/>
         <v>445</v>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="F449" s="3"/>
     </row>
-    <row r="450" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="450" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B450" s="2">
         <f t="shared" si="6"/>
         <v>446</v>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="F450" s="3"/>
     </row>
-    <row r="451" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="451" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B451" s="2">
         <f t="shared" si="6"/>
         <v>447</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="F453" s="3"/>
     </row>
-    <row r="454" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="454" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B454" s="2">
         <f t="shared" si="6"/>
         <v>450</v>
@@ -10098,7 +10098,7 @@
       </c>
       <c r="F456" s="3"/>
     </row>
-    <row r="457" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="457" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B457" s="2">
         <f t="shared" si="6"/>
         <v>453</v>
@@ -10130,7 +10130,7 @@
       </c>
       <c r="F458" s="3"/>
     </row>
-    <row r="459" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="459" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B459" s="2">
         <f t="shared" si="7"/>
         <v>455</v>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="F464" s="3"/>
     </row>
-    <row r="465" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="465" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B465" s="2">
         <f t="shared" si="7"/>
         <v>461</v>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="F468" s="3"/>
     </row>
-    <row r="469" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="469" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B469" s="2">
         <f t="shared" si="7"/>
         <v>465</v>
@@ -10306,7 +10306,7 @@
       </c>
       <c r="F469" s="3"/>
     </row>
-    <row r="470" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="470" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B470" s="2">
         <f t="shared" si="7"/>
         <v>466</v>
@@ -10322,7 +10322,7 @@
       </c>
       <c r="F470" s="3"/>
     </row>
-    <row r="471" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="471" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B471" s="2">
         <f t="shared" si="7"/>
         <v>467</v>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="F471" s="3"/>
     </row>
-    <row r="472" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="472" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B472" s="2">
         <f t="shared" si="7"/>
         <v>468</v>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="F473" s="3"/>
     </row>
-    <row r="474" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="474" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B474" s="2">
         <f t="shared" si="7"/>
         <v>470</v>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="F474" s="3"/>
     </row>
-    <row r="475" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="475" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B475" s="2">
         <f t="shared" si="7"/>
         <v>471</v>
@@ -10418,7 +10418,7 @@
       </c>
       <c r="F476" s="3"/>
     </row>
-    <row r="477" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="477" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B477" s="2">
         <f t="shared" si="7"/>
         <v>473</v>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="F477" s="3"/>
     </row>
-    <row r="478" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="478" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B478" s="2">
         <f t="shared" si="7"/>
         <v>474</v>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="F478" s="3"/>
     </row>
-    <row r="479" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="479" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B479" s="2">
         <f t="shared" si="7"/>
         <v>475</v>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="F479" s="3"/>
     </row>
-    <row r="480" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="480" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B480" s="2">
         <f t="shared" si="7"/>
         <v>476</v>
@@ -10482,7 +10482,7 @@
       </c>
       <c r="F480" s="3"/>
     </row>
-    <row r="481" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="481" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B481" s="2">
         <f t="shared" si="7"/>
         <v>477</v>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="F481" s="3"/>
     </row>
-    <row r="482" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="482" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B482" s="2">
         <f t="shared" si="7"/>
         <v>478</v>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="F482" s="3"/>
     </row>
-    <row r="483" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="483" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B483" s="2">
         <f t="shared" si="7"/>
         <v>479</v>
@@ -10530,7 +10530,7 @@
       </c>
       <c r="F483" s="3"/>
     </row>
-    <row r="484" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="484" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B484" s="2">
         <f t="shared" si="7"/>
         <v>480</v>
@@ -10546,7 +10546,7 @@
       </c>
       <c r="F484" s="3"/>
     </row>
-    <row r="485" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="485" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B485" s="2">
         <f t="shared" si="7"/>
         <v>481</v>
@@ -10562,7 +10562,7 @@
       </c>
       <c r="F485" s="3"/>
     </row>
-    <row r="486" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="486" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B486" s="2">
         <f t="shared" si="7"/>
         <v>482</v>
@@ -10578,7 +10578,7 @@
       </c>
       <c r="F486" s="3"/>
     </row>
-    <row r="487" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="487" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B487" s="2">
         <f t="shared" si="7"/>
         <v>483</v>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="F487" s="3"/>
     </row>
-    <row r="488" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="488" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B488" s="2">
         <f t="shared" si="7"/>
         <v>484</v>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="F489" s="3"/>
     </row>
-    <row r="490" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="490" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B490" s="2">
         <f t="shared" si="7"/>
         <v>486</v>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="F490" s="3"/>
     </row>
-    <row r="491" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="491" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B491" s="2">
         <f t="shared" si="7"/>
         <v>487</v>
@@ -10690,7 +10690,7 @@
       </c>
       <c r="F493" s="3"/>
     </row>
-    <row r="494" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="494" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B494" s="2">
         <f t="shared" si="7"/>
         <v>490</v>
@@ -10706,7 +10706,7 @@
       </c>
       <c r="F494" s="3"/>
     </row>
-    <row r="495" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="495" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B495" s="2">
         <f t="shared" si="7"/>
         <v>491</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="F496" s="3"/>
     </row>
-    <row r="497" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="497" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B497" s="2">
         <f t="shared" si="7"/>
         <v>493</v>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="F499" s="3"/>
     </row>
-    <row r="500" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="500" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B500" s="2">
         <f t="shared" si="7"/>
         <v>496</v>
@@ -10818,7 +10818,7 @@
       </c>
       <c r="F501" s="3"/>
     </row>
-    <row r="502" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="502" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B502" s="2">
         <f t="shared" si="7"/>
         <v>498</v>
@@ -10882,7 +10882,7 @@
       </c>
       <c r="F505" s="3"/>
     </row>
-    <row r="506" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="506" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B506" s="2">
         <f t="shared" si="7"/>
         <v>502</v>
@@ -10898,7 +10898,7 @@
       </c>
       <c r="F506" s="3"/>
     </row>
-    <row r="507" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="507" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B507" s="2">
         <f t="shared" si="7"/>
         <v>503</v>
@@ -10962,7 +10962,7 @@
       </c>
       <c r="F510" s="3"/>
     </row>
-    <row r="511" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="511" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B511" s="2">
         <f t="shared" si="7"/>
         <v>507</v>
@@ -11026,7 +11026,7 @@
       </c>
       <c r="F514" s="3"/>
     </row>
-    <row r="515" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="515" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B515" s="2">
         <f t="shared" si="7"/>
         <v>511</v>
@@ -11058,7 +11058,7 @@
       </c>
       <c r="F516" s="3"/>
     </row>
-    <row r="517" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="517" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B517" s="2">
         <f t="shared" si="7"/>
         <v>513</v>
@@ -11154,7 +11154,7 @@
       </c>
       <c r="F522" s="3"/>
     </row>
-    <row r="523" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="523" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B523" s="2">
         <f t="shared" si="8"/>
         <v>519</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="F525" s="3"/>
     </row>
-    <row r="526" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="526" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B526" s="2">
         <f t="shared" si="8"/>
         <v>522</v>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="F526" s="3"/>
     </row>
-    <row r="527" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="527" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B527" s="2">
         <f t="shared" si="8"/>
         <v>523</v>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="F527" s="3"/>
     </row>
-    <row r="528" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="528" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B528" s="2">
         <f t="shared" si="8"/>
         <v>524</v>
@@ -11266,7 +11266,7 @@
       </c>
       <c r="F529" s="3"/>
     </row>
-    <row r="530" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="530" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B530" s="2">
         <f t="shared" si="8"/>
         <v>526</v>
@@ -11282,7 +11282,7 @@
       </c>
       <c r="F530" s="3"/>
     </row>
-    <row r="531" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="531" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B531" s="2">
         <f t="shared" si="8"/>
         <v>527</v>
@@ -11362,7 +11362,7 @@
       </c>
       <c r="F535" s="3"/>
     </row>
-    <row r="536" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="536" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B536" s="2">
         <f t="shared" si="8"/>
         <v>532</v>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="F539" s="3"/>
     </row>
-    <row r="540" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="540" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B540" s="2">
         <f t="shared" si="8"/>
         <v>536</v>
@@ -11554,7 +11554,7 @@
       </c>
       <c r="F547" s="3"/>
     </row>
-    <row r="548" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="548" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B548" s="2">
         <f t="shared" si="8"/>
         <v>544</v>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="F553" s="3"/>
     </row>
-    <row r="554" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="554" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B554" s="2">
         <f t="shared" si="8"/>
         <v>550</v>
@@ -11714,7 +11714,7 @@
       </c>
       <c r="F557" s="3"/>
     </row>
-    <row r="558" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="558" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B558" s="2">
         <f t="shared" si="8"/>
         <v>554</v>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="F562" s="3"/>
     </row>
-    <row r="563" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="563" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B563" s="2">
         <f t="shared" si="8"/>
         <v>559</v>
@@ -11810,7 +11810,7 @@
       </c>
       <c r="F563" s="3"/>
     </row>
-    <row r="564" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="564" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B564" s="2">
         <f t="shared" si="8"/>
         <v>560</v>
@@ -11826,7 +11826,7 @@
       </c>
       <c r="F564" s="3"/>
     </row>
-    <row r="565" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="565" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B565" s="2">
         <f t="shared" si="8"/>
         <v>561</v>
@@ -11842,7 +11842,7 @@
       </c>
       <c r="F565" s="3"/>
     </row>
-    <row r="566" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="566" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B566" s="2">
         <f t="shared" si="8"/>
         <v>562</v>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="F566" s="3"/>
     </row>
-    <row r="567" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="567" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B567" s="2">
         <f t="shared" si="8"/>
         <v>563</v>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="F567" s="3"/>
     </row>
-    <row r="568" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="568" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B568" s="2">
         <f t="shared" si="8"/>
         <v>564</v>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="F568" s="3"/>
     </row>
-    <row r="569" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="569" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B569" s="2">
         <f t="shared" si="8"/>
         <v>565</v>
@@ -11906,7 +11906,7 @@
       </c>
       <c r="F569" s="3"/>
     </row>
-    <row r="570" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="570" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B570" s="2">
         <f t="shared" si="8"/>
         <v>566</v>
@@ -11922,7 +11922,7 @@
       </c>
       <c r="F570" s="3"/>
     </row>
-    <row r="571" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="571" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B571" s="2">
         <f t="shared" si="8"/>
         <v>567</v>
@@ -11938,7 +11938,7 @@
       </c>
       <c r="F571" s="3"/>
     </row>
-    <row r="572" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="572" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B572" s="2">
         <f t="shared" si="8"/>
         <v>568</v>
@@ -11954,7 +11954,7 @@
       </c>
       <c r="F572" s="3"/>
     </row>
-    <row r="573" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="573" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B573" s="2">
         <f t="shared" si="8"/>
         <v>569</v>
@@ -11970,7 +11970,7 @@
       </c>
       <c r="F573" s="3"/>
     </row>
-    <row r="574" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="574" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B574" s="2">
         <f t="shared" si="8"/>
         <v>570</v>
@@ -11986,7 +11986,7 @@
       </c>
       <c r="F574" s="3"/>
     </row>
-    <row r="575" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="575" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B575" s="2">
         <f t="shared" si="8"/>
         <v>571</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="F575" s="3"/>
     </row>
-    <row r="576" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="576" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B576" s="2">
         <f t="shared" si="8"/>
         <v>572</v>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="F583" s="3"/>
     </row>
-    <row r="584" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="584" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B584" s="2">
         <f t="shared" si="8"/>
         <v>580</v>
@@ -12226,7 +12226,7 @@
       </c>
       <c r="F589" s="3"/>
     </row>
-    <row r="590" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="590" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B590" s="2">
         <f t="shared" si="9"/>
         <v>586</v>
@@ -12306,7 +12306,7 @@
       </c>
       <c r="F594" s="3"/>
     </row>
-    <row r="595" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="595" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B595" s="2">
         <f t="shared" si="9"/>
         <v>591</v>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="F596" s="3"/>
     </row>
-    <row r="597" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="597" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B597" s="2">
         <f t="shared" si="9"/>
         <v>593</v>
@@ -12370,7 +12370,7 @@
       </c>
       <c r="F598" s="3"/>
     </row>
-    <row r="599" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="599" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B599" s="6">
         <v>595</v>
       </c>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="E600" s="5"/>
     </row>
-    <row r="601" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="601" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C601" s="4"/>
     </row>
     <row r="602" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
@@ -12439,268 +12439,26 @@
   </sheetData>
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
-      <filters blank="1">
-        <filter val="24/7 MART ASKARI X SECTOR F"/>
-        <filter val="ACE MART P BLOCK SABZAZAR"/>
-        <filter val="Ajmair Food (Main Market)"/>
-        <filter val="Ajmair Foods (Abdali Chowk)"/>
-        <filter val="Ajmair Foods (Karim Block)"/>
-        <filter val="Ajmair Foods (Kashmir Block)"/>
-        <filter val="Ajmair Foods (Liaqat Chowk)"/>
-        <filter val="Ajmair Foods (Maulana Shaukat Ali Road LHR)"/>
-        <filter val="Ajmair Foods (Neelam Block)"/>
-        <filter val="Ajmair Foods (Shalimar Link Road)"/>
-        <filter val="Ajmair Foods Ameer Chowk"/>
-        <filter val="Ajmair Foods Pvt LTD (M-T C Block)"/>
-        <filter val="Ajmair Foods Pvt LTD (M-T M Block)"/>
-        <filter val="Ajmair Foods Pvt LTD (Tulip Block)"/>
-        <filter val="Ajmair Foods Pvt LTD Rehmat Chowk"/>
-        <filter val="Ajmair Foods Pvt.LTD (Barket Market)"/>
-        <filter val="Ajmair Foods PvtLTD (H Block)"/>
-        <filter val="Ajmair Foods PvtLTD (Raja Market)"/>
-        <filter val="Ajmair Foods PvtLTD (Shaday Wal Chowk)"/>
-        <filter val="Ajmair Foods PvtLTD H-3 Block Joher Town"/>
-        <filter val="Akbari Store (Jain Mandir)"/>
-        <filter val="AL BARKAT MART"/>
-        <filter val="Al Fatah (Hussian Chowk)"/>
-        <filter val="Al Fatah (Lake City)"/>
-        <filter val="AL GHANI ROSE BLOCK"/>
-        <filter val="Al Karim Departmental Store (Model Town)"/>
-        <filter val="AL KHAN (SHAHDHRA CHOWK)"/>
-        <filter val="AL KHAN BAKERS  (BHOBTIAN CHOWK)"/>
-        <filter val="AL KHAN BAKERS (NESPAK)"/>
-        <filter val="AL KHAN FOODS (BEHRIA TOWN)"/>
-        <filter val="AL KHAN FOODS VALENCIA"/>
-        <filter val="AL KOSAR DEPARTMENTAL STORE (SHAH FAREED)"/>
-        <filter val="Al Sheikh Bakers"/>
-        <filter val="AL ZEESHAN SUPER MARKET"/>
-        <filter val="AL-FATAH H-BLOCK"/>
-        <filter val="ALI SUPER STORE BHATA CHOWK"/>
-        <filter val="AL-KHAN FOODS (WAPDA TOWN)"/>
-        <filter val="Askari  Depsrtmental Store Punjab Society"/>
-        <filter val="Askari Departmental Store College Road"/>
-        <filter val="Aslam Super Market ( LDA )"/>
-        <filter val="Aslam Super Market EME"/>
-        <filter val="ASTER SUPERMARKET"/>
-        <filter val="BASHIR SONS PHARMACY (AMEER CHOWK)"/>
-        <filter val="BASHIR SONS PHARMACY (ASKARI XI)"/>
-        <filter val="BASHIR SONS PHARMACY (LAKE CITY)"/>
-        <filter val="BASHIR SONS PHARMACY (NAKHUDA CHOWK)"/>
-        <filter val="BASHIR SONS PHARMACY (RACHNA BLOCK)"/>
-        <filter val="BILAL SUPER STORE H BLOCK DHA"/>
-        <filter val="BIN KHALID STORE VALENCIA TOWN"/>
-        <filter val="BLINK MART STORE PVT LTD"/>
-        <filter val="BUNDU KHAN (AIRPORT)"/>
-        <filter val="BUNDU KHAN (AKBAR CHOWK)"/>
-        <filter val="BUNDU KHAN (ALLAMA IQBAL TOWN)"/>
-        <filter val="BUNDU KHAN (CHUBURJI)"/>
-        <filter val="BUNDU KHAN (DHAROGEWALA)"/>
-        <filter val="BUNDU KHAN (FF DHA)"/>
-        <filter val="BUNDU KHAN (GARI SHAHU)"/>
-        <filter val="BUNDU KHAN (GULSHAN RAVI)"/>
-        <filter val="BUNDU KHAN (HUSSAIN CHOWK)."/>
-        <filter val="BUNDU KHAN (JALLO MORE)"/>
-        <filter val="BUNDU KHAN (KARIM PARK)"/>
-        <filter val="BUNDU KHAN (LAKSHAMI CHOWK)"/>
-        <filter val="BUNDU KHAN (LIAQAT CHOWK)"/>
-        <filter val="BUNDU KHAN (MODEL TOWN LINK ROAD)"/>
-        <filter val="BUNDU KHAN (OUTFALL ROAD)"/>
-        <filter val="BUNDU KHAN (PARAGON CITY)"/>
-        <filter val="BUNDU KHAN (PARK VIEW)"/>
-        <filter val="BUNDU KHAN (PIA ROAD)"/>
-        <filter val="BUNDU KHAN (PUNJAB SOCIETY)"/>
-        <filter val="BUNDU KHAN (REHMAN GARDEN)"/>
-        <filter val="BUNDU KHAN (SADDAR)"/>
-        <filter val="BUNDU KHAN (SAFA WALA CHOWK)"/>
-        <filter val="BUNDU KHAN (SAMNABAD)"/>
-        <filter val="BUNDU KHAN (SHADBAGH TOKY WALA CHOWK)"/>
-        <filter val="BUNDU KHAN (SHAHDHRA GT ROAD)"/>
-        <filter val="BUNDU KHAN (SHAMA CINEMA)"/>
-        <filter val="BUNDU KHAN (TAJ BAGH)"/>
-        <filter val="BUNDU KHAN (YATEEM KHANA)"/>
-        <filter val="BUNDU KHAN ASKARI 11"/>
-        <filter val="BUNDU KHAN BEHRIA TOWN"/>
-        <filter val="BUNDU KHAN EME"/>
-        <filter val="BUNDU KHAN FAISAL TOWN"/>
-        <filter val="BUNDU KHAN G-1 MARKET"/>
-        <filter val="BUNDU KHAN GT-ROAD"/>
-        <filter val="BUNDU KHAN H BLOCK (DHA)"/>
-        <filter val="BUNDU KHAN LAKE CITY"/>
-        <filter val="BUNDU KHAN MAIN BLVD DHA"/>
-        <filter val="BUNDU KHAN NASEER ABAD"/>
-        <filter val="BUNDU KHAN PINE AVENUE"/>
-        <filter val="BUNDU KHAN RAIWIND ROAD"/>
-        <filter val="BUNDU KHAN T BLOCK"/>
-        <filter val="BUNDU KHAN TAJ PURA"/>
-        <filter val="BUNDU KHAN WAPDA TOWN"/>
-        <filter val="BUNDU KHAN YOUHANABAD"/>
-        <filter val="BUNDUN KHAN (DHA PHASE-6)"/>
-        <filter val="BUNDUN KHAN (ISLAMPURA)"/>
-        <filter val="Butt Sweet (G-1 Market)"/>
-        <filter val="BUTT SWEETS &amp; BAKERS  (PIA ROAD)"/>
-        <filter val="BUTT SWEETS &amp; BAKERS (GT ROAD)"/>
-        <filter val="BUTT SWEETS &amp; BAKERS (VALENCIA)"/>
-        <filter val="BUTT SWEETS (LIAQAT CHOWK)"/>
-        <filter val="Butt Sweets Laxmi Chowk"/>
-        <filter val="CITY GENERAL STORE BEGUM KOT"/>
-        <filter val="CLINIX PHARMACY ASKARI 11"/>
-        <filter val="CLINIX PHARMACY LIAQAT CHOWK SABZAZAR"/>
-        <filter val="CLINIX PHARMACY SHAHKAM CHOWK"/>
-        <filter val="CLINIX PHARMACY Z BLOCK"/>
-        <filter val="CLINIX SUPER MARKET  (THOKER)"/>
-        <filter val="CLINIX SUPER MARKET (AMEER CHOWK)"/>
-        <filter val="CLINIX SUPERMARKET (CHOWK NAKHUDA)"/>
-        <filter val="CLINIX SUPERMARKET (JOHAR TOWN)"/>
-        <filter val="CLINIX SUPERMARKET (LAKE CITY)"/>
-        <filter val="CLINIX SUPERMARKET (MANAWAN)"/>
-        <filter val="CLINIX SUPERMARKET (SAMANABAD)"/>
-        <filter val="CLINIX SUPERMARKET (SHAM NAGAR)"/>
-        <filter val="CROWN SUPER MARKET"/>
-        <filter val="CSD Askari X"/>
-        <filter val="DAILY BASKET STORES (ICON VALLETY SOCIETY)"/>
-        <filter val="DIVINE BAKERS &amp; SWEETS (WAHDAT ROAD)"/>
-        <filter val="Easy Mart (Talwar Chowk"/>
+      <filters>
+        <filter val="EURO RANJERS MART"/>
+        <filter val="Euro store  (Academy Road)"/>
+        <filter val="EURO STORE (N F C )"/>
         <filter val="EURO STORE (Rahamt chowk)"/>
+        <filter val="Euro Store (Scheme Mor)"/>
+        <filter val="Euro Store Airport Road"/>
+        <filter val="Euro Store Bedian Road"/>
+        <filter val="Euro Store College Road (Model Town)"/>
+        <filter val="EURO STORE CROWN BEHRIA TOWN"/>
+        <filter val="Euro Store E-2 (Wapda Town)"/>
+        <filter val="EURO STORE FATAH GARH"/>
+        <filter val="Euro Store G.T Road"/>
+        <filter val="Euro Store Garhi Shahu"/>
         <filter val="EURO Store Hypermarket (Raiwind Road)"/>
+        <filter val="Euro Store Iqbal Town (Ranchna)"/>
+        <filter val="EURO STORE MARIYA STOP"/>
         <filter val="EURO STORE PH VIII PARK VIEW"/>
         <filter val="Euro Stores (G-1 Market)"/>
-        <filter val="FDPP CONSUMER H BLOCK DHA"/>
-        <filter val="FDPP CONSUMER Main Market"/>
-        <filter val="Fresh Inn Bakers (Johar Town)"/>
-        <filter val="Fresh Inn Bakers (Link Road)"/>
-        <filter val="FRESHLY MART SECTOR B ASKARI 11"/>
-        <filter val="Galaxy Super Market"/>
-        <filter val="GOOD LUCK MUSLIM TOWN"/>
-        <filter val="Gourmet - K Block"/>
-        <filter val="Gourmet - Z Block"/>
-        <filter val="Gourmet (Pak Arab)"/>
-        <filter val="Gourmet A  Block"/>
-        <filter val="Gourmet Awan Market"/>
-        <filter val="GOURMET BAKERS (25 NO STOP) BEGIUM KOT"/>
-        <filter val="GOURMET BAKERS (AL REHMAN GARDEN)"/>
-        <filter val="GOURMET BAKERS (KOT ABDUL MALIK)"/>
-        <filter val="GOURMET BAKERS (MACHIS FACTORY)"/>
-        <filter val="GOURMET BAKERS (MANAWWAN)"/>
-        <filter val="GOURMET BAKERS (SHAHDARA MORE)"/>
-        <filter val="Gourmet Barkat Market"/>
-        <filter val="Gourmet Bhatta Chowk"/>
-        <filter val="Gourmet C block"/>
-        <filter val="Gourmet FF Block"/>
-        <filter val="Gourmet Ghalib Market"/>
-        <filter val="Gourmet Girja Chowk"/>
-        <filter val="Gourmet H Block"/>
-        <filter val="Gourmet -Kareem Block"/>
-        <filter val="Gourmet -Kareem Park"/>
-        <filter val="Gourmet -Karishn nagar"/>
-        <filter val="Gourmet -Kot Khaja Saeed"/>
-        <filter val="Gourmet -Liaqat Chowk"/>
-        <filter val="Gourmet Link Rd"/>
-        <filter val="Gourmet -Rustam Park"/>
-        <filter val="Gourmet Shalimar Link Road"/>
-        <filter val="Gourmet Umer Chowk"/>
-        <filter val="Gourmet XX Block"/>
-        <filter val="Gourmet -Yateem Khana"/>
-        <filter val="Hafiz Sweet Bakers"/>
-        <filter val="HAJVERY FOODS (O G BAKERS MARGZAR ROAD)"/>
-        <filter val="HAJVERY FOODS (O G BAKERS) SHADBAGH"/>
-        <filter val="HAJVERY FOODS (OG BAKERS BADAMIBAGH)"/>
-        <filter val="HAJVERY FOODS (OG BAKERS KRISHAN NAGAR)"/>
-        <filter val="HAJVERY FOODS (OG BAKERS WALTON ROAD)"/>
-        <filter val="HASHMAT SUPER MARKET (AUDIT ACCOUNT)"/>
-        <filter val="HIKMA MART (PLAZA NO 60 PARAGON)"/>
-        <filter val="HIKMA MART 1 (81 BRADE WAY PARAGON)"/>
-        <filter val="HIKMA SUPER STORE ASKARI 11"/>
-        <filter val="HIKMAH SUPER STORE"/>
-        <filter val="HIMALAYA SUPER MARKET"/>
-        <filter val="HKB (Phase V)"/>
-        <filter val="HKB Y Block"/>
-        <filter val="Jalal sons (Askari 10 F sector ) 01"/>
-        <filter val="JALAL SONS (ASKARI 11 B BLOCK) 02"/>
-        <filter val="JALAL SONS (C BLOCK MODEL TOWN) 02"/>
-        <filter val="JALAL SONS (DHA C BLOCK,PHASE 6) 02"/>
-        <filter val="JALAL SONS (DHA Y BLOCK) 02"/>
-        <filter val="Jalal Sons (H Block) 01"/>
-        <filter val="JALAL SONS (HUSSAIN CHOWK GULBERG III) 02"/>
-        <filter val="Jalal Sons (Lake City) 01"/>
-        <filter val="Jalal sons (Main Market) 01"/>
-        <filter val="JALAL SONS (MODEL TOWN LINK ROAD) 02"/>
-        <filter val="Jalal Sons (PAF Market) 01 main Market"/>
-        <filter val="JALAL SONS (PHASE 8 EX PARK VIEW) 02"/>
-        <filter val="JALAL SONS (SHAUKAT KHANUM) 02"/>
-        <filter val="JALAL SONS (TALWAR CHOWK) 02"/>
-        <filter val="Jalal Sons Askari X (01)"/>
-        <filter val="K-mart"/>
-        <filter val="KRRAVE TECHNOLOGIES (PRIVATE) LIMITED"/>
-        <filter val="Lake City Management Pvt Ltd"/>
-        <filter val="LARAIB BAKERS &amp; SWEET (SHADMAN)"/>
-        <filter val="LARAIB BAKERS &amp; SWEETS (YATEEM kHANA)"/>
-        <filter val="LARAIB BAKERS (ISLAMPURA)"/>
-        <filter val="LARAIB BAKERS ALI TOWN (RAIWIND ROAD)"/>
-        <filter val="LARAIB BAKERS SWEETS (Ghulshan Ravi)"/>
-        <filter val="LARAIB BAKERS SWEETS (YOUHANABAD)"/>
-        <filter val="LARAIB FOODS (BEGUM KOT)"/>
-        <filter val="LARAIB FOODS (SHALIMAR LINK ROAD)"/>
-        <filter val="LARAIB FOODS LIAQAT CHOWK SABZAZAR"/>
-        <filter val="LUTF MART (Barki Road)"/>
-        <filter val="M/S AL KHAN FOODS (ALI TOWN) THOKAR"/>
-        <filter val="M/S AL KHAN FOODS (FAZAIA HOUSING SOCIETY)"/>
-        <filter val="M/S AL KHAN FOODS (REHMAN GARDEN)"/>
-        <filter val="M/S AL KHAN FOODS (WAHADAT ROAD)"/>
-        <filter val="M/S BUTT SWEETS &amp; BAKERS (KUTCHEHRI BAZAR)"/>
-        <filter val="M/S J.K.S Cash Carry"/>
-        <filter val="Malmo Bakers (Ali View garden)"/>
-        <filter val="Malmo Bakers (Chung )"/>
-        <filter val="Malmo Bakers (College Road)"/>
-        <filter val="Malmo Bakers (Punjab Soc)"/>
-        <filter val="Malmo Bakers (Usmania Tower)"/>
-        <filter val="Malmo Bakery G.T Road"/>
-        <filter val="Malmo Bakery Gulshan Ravi"/>
-        <filter val="Malmo Bakery Neelam Block"/>
-        <filter val="Malmo Bakery Samnabad"/>
-        <filter val="Malmo Bakery Shalimar Link Road"/>
-        <filter val="Malmo Bakery Shama"/>
-        <filter val="Malmo Bakery Wahdat Road"/>
-        <filter val="Malmo DHA Q- BLOCK"/>
-        <filter val="Malmo Liaqat chowk"/>
-        <filter val="MALMO SWEETS &amp; BAKERS (AL-KABIR TOWN)"/>
-        <filter val="MALMO SWEETS &amp; BAKERS (BEHRIA ORCHARD)"/>
-        <filter val="MARKET SECURE 1D HBFC"/>
-        <filter val="MM CASH &amp; CARRY ASKARI XI"/>
-        <filter val="MS RUBAIKA CASH AND CARRY"/>
-        <filter val="NEMAT KHANA STORES (PRIVATE) LIMITED"/>
-        <filter val="NEW RAHAT BAKERS GS (ALLAMA IQBAL ROAD)"/>
-        <filter val="OG BAKERS (GREENWOOD SOCIETY)"/>
-        <filter val="ORGANICS (PAK HEIGHTS BUILDING)"/>
-        <filter val="PAK MADINA SUPER STORE (BEGAM KOT)"/>
-        <filter val="PREMIER MART FP ROAD OPP AWAN MARKET"/>
-        <filter val="PRIME STORE MAIN MARKET"/>
-        <filter val="PRMIE PICK CASH &amp; CARRY REHMAN GARDEN"/>
-        <filter val="PUNJAB CASH &amp; CARRY (ASKARI 11)"/>
-        <filter val="Quick Check Departmental Store"/>
-        <filter val="QUICK MART PARK VIEW MULTAN RD"/>
-        <filter val="RAHIM STORE THOKAR NIAZ BAIG"/>
-        <filter val="RAINBOW CASH &amp; CARRY (MAIN BARKI ROAD)"/>
-        <filter val="REHMAN KHALIS (PVT.) LIMITED"/>
-        <filter val="SAFIA MANZOOR (LIAQAT CHOWK)"/>
-        <filter val="Servaid (T Block) DHA"/>
-        <filter val="SHEZAN BAKERS ABID MARKET"/>
-        <filter val="SHEZAN BAKERS AIRLINE SOCIETY"/>
-        <filter val="SHEZAN BAKERS C BLOCK MODEL TOWN"/>
-        <filter val="SHEZAN BAKERS CAVALRY GROUND"/>
-        <filter val="SHEZAN BAKERS DHA FF"/>
-        <filter val="SHEZAN BAKERS GARHI SHAHU"/>
-        <filter val="SHEZAN BAKERS GIRJA CHOWK"/>
-        <filter val="SHEZAN BAKERS H BLOCK"/>
-        <filter val="SHEZAN BAKERS IQBAL TOWN"/>
-        <filter val="SHEZAN BAKERS LIBERTY MARKET"/>
-        <filter val="SHEZAN BAKERS LOWER MALL"/>
-        <filter val="SHEZAN BAKERS MAIN MARKET"/>
-        <filter val="SHEZAN BAKERS MOCHI PURA"/>
-        <filter val="SHEZAN BAKERS SHER PAO"/>
-        <filter val="TARIQ MART (DHA M BLOCK)"/>
-        <filter val="Umer Super Market (Joher Town)"/>
-        <filter val="Victoria (Link Road)"/>
-        <filter val="ZOHRA MART MAIN MARKET"/>
+        <filter val="EURO Stores (Nishat Colony)"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38FA433E-5B73-46B9-8890-9811C350940E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD437FF-0F6C-472A-9DBA-EFC96092BE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="F75" s="3"/>
     </row>
-    <row r="76" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B76" s="2">
         <f t="shared" si="1"/>
         <v>72</v>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="F76" s="3"/>
     </row>
-    <row r="77" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B77" s="2">
         <f t="shared" si="1"/>
         <v>73</v>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="F245" s="3"/>
     </row>
-    <row r="246" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B246" s="2">
         <f t="shared" si="3"/>
         <v>242</v>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="F246" s="3"/>
     </row>
-    <row r="247" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B247" s="2">
         <f t="shared" si="3"/>
         <v>243</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="F247" s="3"/>
     </row>
-    <row r="248" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B248" s="2">
         <f t="shared" si="3"/>
         <v>244</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="F248" s="3"/>
     </row>
-    <row r="249" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B249" s="2">
         <f t="shared" si="3"/>
         <v>245</v>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="F249" s="3"/>
     </row>
-    <row r="250" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B250" s="2">
         <f t="shared" si="3"/>
         <v>246</v>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="F250" s="3"/>
     </row>
-    <row r="251" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B251" s="2">
         <f t="shared" si="3"/>
         <v>247</v>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="F251" s="3"/>
     </row>
-    <row r="252" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B252" s="2">
         <f t="shared" si="3"/>
         <v>248</v>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="F252" s="3"/>
     </row>
-    <row r="253" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B253" s="2">
         <f t="shared" si="3"/>
         <v>249</v>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="F253" s="3"/>
     </row>
-    <row r="254" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B254" s="2">
         <f t="shared" si="3"/>
         <v>250</v>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F254" s="3"/>
     </row>
-    <row r="255" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B255" s="2">
         <f t="shared" si="3"/>
         <v>251</v>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="F255" s="3"/>
     </row>
-    <row r="256" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B256" s="2">
         <f t="shared" si="3"/>
         <v>252</v>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="F256" s="3"/>
     </row>
-    <row r="257" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B257" s="2">
         <f t="shared" si="3"/>
         <v>253</v>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="F257" s="3"/>
     </row>
-    <row r="258" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B258" s="2">
         <f t="shared" si="3"/>
         <v>254</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="F258" s="3"/>
     </row>
-    <row r="259" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B259" s="2">
         <f t="shared" si="3"/>
         <v>255</v>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="F259" s="3"/>
     </row>
-    <row r="260" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B260" s="2">
         <f t="shared" si="3"/>
         <v>256</v>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="F260" s="3"/>
     </row>
-    <row r="261" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B261" s="2">
         <f t="shared" si="3"/>
         <v>257</v>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="F261" s="3"/>
     </row>
-    <row r="262" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B262" s="2">
         <f t="shared" si="3"/>
         <v>258</v>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="F262" s="3"/>
     </row>
-    <row r="263" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B263" s="2">
         <f t="shared" si="3"/>
         <v>259</v>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="F263" s="3"/>
     </row>
-    <row r="264" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B264" s="2">
         <f t="shared" si="3"/>
         <v>260</v>
@@ -12440,25 +12440,8 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="EURO RANJERS MART"/>
-        <filter val="Euro store  (Academy Road)"/>
-        <filter val="EURO STORE (N F C )"/>
-        <filter val="EURO STORE (Rahamt chowk)"/>
-        <filter val="Euro Store (Scheme Mor)"/>
-        <filter val="Euro Store Airport Road"/>
-        <filter val="Euro Store Bedian Road"/>
-        <filter val="Euro Store College Road (Model Town)"/>
-        <filter val="EURO STORE CROWN BEHRIA TOWN"/>
-        <filter val="Euro Store E-2 (Wapda Town)"/>
-        <filter val="EURO STORE FATAH GARH"/>
-        <filter val="Euro Store G.T Road"/>
-        <filter val="Euro Store Garhi Shahu"/>
-        <filter val="EURO Store Hypermarket (Raiwind Road)"/>
-        <filter val="Euro Store Iqbal Town (Ranchna)"/>
-        <filter val="EURO STORE MARIYA STOP"/>
-        <filter val="EURO STORE PH VIII PARK VIEW"/>
-        <filter val="Euro Stores (G-1 Market)"/>
-        <filter val="EURO Stores (Nishat Colony)"/>
+        <filter val="Al Buraq Departmental Store (Islampura)"/>
+        <filter val="Al Buraq Departmental Store (Samnabad)"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD437FF-0F6C-472A-9DBA-EFC96092BE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80764EC1-032E-4F38-A2EA-F7DA628CEB28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <f>B7+1</f>
         <v>4</v>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="F53" s="3"/>
     </row>
-    <row r="54" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B54" s="2">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="F75" s="3"/>
     </row>
-    <row r="76" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B76" s="2">
         <f t="shared" si="1"/>
         <v>72</v>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="F76" s="3"/>
     </row>
-    <row r="77" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B77" s="2">
         <f t="shared" si="1"/>
         <v>73</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="F86" s="3"/>
     </row>
-    <row r="87" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B87" s="2">
         <f t="shared" si="1"/>
         <v>83</v>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="F108" s="3"/>
     </row>
-    <row r="109" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B109" s="2">
         <f t="shared" si="1"/>
         <v>105</v>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="F133" s="3"/>
     </row>
-    <row r="134" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B134" s="2">
         <f t="shared" si="1"/>
         <v>130</v>
@@ -5730,7 +5730,7 @@
       </c>
       <c r="F183" s="3"/>
     </row>
-    <row r="184" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B184" s="2">
         <f t="shared" si="2"/>
         <v>180</v>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F254" s="3"/>
     </row>
-    <row r="255" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B255" s="2">
         <f t="shared" si="3"/>
         <v>251</v>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="F383" s="3"/>
     </row>
-    <row r="384" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B384" s="2">
         <f t="shared" si="5"/>
         <v>380</v>
@@ -9826,7 +9826,7 @@
       </c>
       <c r="F439" s="3"/>
     </row>
-    <row r="440" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B440" s="2">
         <f t="shared" si="6"/>
         <v>436</v>
@@ -11378,7 +11378,7 @@
       </c>
       <c r="F536" s="3"/>
     </row>
-    <row r="537" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B537" s="2">
         <f t="shared" si="8"/>
         <v>533</v>
@@ -12440,8 +12440,16 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Al Buraq Departmental Store (Islampura)"/>
-        <filter val="Al Buraq Departmental Store (Samnabad)"/>
+        <filter val="AHMAD CASH &amp; CARRY (WAPDA TOWN)"/>
+        <filter val="Ajmair Foods Pvt LTD Wapda Town E-2"/>
+        <filter val="AL FATAH WAPDA TOWN"/>
+        <filter val="AL-KHAN FOODS (WAPDA TOWN)"/>
+        <filter val="BASHIR SONS PHARMACY (WAPDA TOWN)"/>
+        <filter val="BUNDU KHAN WAPDA TOWN"/>
+        <filter val="Euro Store E-2 (Wapda Town)"/>
+        <filter val="GRAIN MART WAPDA TOWN"/>
+        <filter val="JALAL SONS (WAPDA TOWN) 02"/>
+        <filter val="RAHIM STORE WAPDA TOWN"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80764EC1-032E-4F38-A2EA-F7DA628CEB28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1207B9E-637D-4BB0-9E3C-81353CB4554A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <f>B7+1</f>
         <v>4</v>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="F53" s="3"/>
     </row>
-    <row r="54" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B54" s="2">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="F86" s="3"/>
     </row>
-    <row r="87" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B87" s="2">
         <f t="shared" si="1"/>
         <v>83</v>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="F108" s="3"/>
     </row>
-    <row r="109" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B109" s="2">
         <f t="shared" si="1"/>
         <v>105</v>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="F133" s="3"/>
     </row>
-    <row r="134" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B134" s="2">
         <f t="shared" si="1"/>
         <v>130</v>
@@ -5730,7 +5730,7 @@
       </c>
       <c r="F183" s="3"/>
     </row>
-    <row r="184" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B184" s="2">
         <f t="shared" si="2"/>
         <v>180</v>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F254" s="3"/>
     </row>
-    <row r="255" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B255" s="2">
         <f t="shared" si="3"/>
         <v>251</v>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="F383" s="3"/>
     </row>
-    <row r="384" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="384" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B384" s="2">
         <f t="shared" si="5"/>
         <v>380</v>
@@ -9826,7 +9826,7 @@
       </c>
       <c r="F439" s="3"/>
     </row>
-    <row r="440" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="440" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B440" s="2">
         <f t="shared" si="6"/>
         <v>436</v>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="F466" s="3"/>
     </row>
-    <row r="467" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B467" s="2">
         <f t="shared" si="7"/>
         <v>463</v>
@@ -11378,7 +11378,7 @@
       </c>
       <c r="F536" s="3"/>
     </row>
-    <row r="537" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="537" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B537" s="2">
         <f t="shared" si="8"/>
         <v>533</v>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="F548" s="3"/>
     </row>
-    <row r="549" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B549" s="2">
         <f t="shared" si="8"/>
         <v>545</v>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="F549" s="3"/>
     </row>
-    <row r="550" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B550" s="2">
         <f t="shared" si="8"/>
         <v>546</v>
@@ -11602,7 +11602,7 @@
       </c>
       <c r="F550" s="3"/>
     </row>
-    <row r="551" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B551" s="2">
         <f t="shared" si="8"/>
         <v>547</v>
@@ -11618,7 +11618,7 @@
       </c>
       <c r="F551" s="3"/>
     </row>
-    <row r="552" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B552" s="2">
         <f t="shared" si="8"/>
         <v>548</v>
@@ -11634,7 +11634,7 @@
       </c>
       <c r="F552" s="3"/>
     </row>
-    <row r="553" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B553" s="2">
         <f t="shared" si="8"/>
         <v>549</v>
@@ -12440,16 +12440,12 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="AHMAD CASH &amp; CARRY (WAPDA TOWN)"/>
-        <filter val="Ajmair Foods Pvt LTD Wapda Town E-2"/>
-        <filter val="AL FATAH WAPDA TOWN"/>
-        <filter val="AL-KHAN FOODS (WAPDA TOWN)"/>
-        <filter val="BASHIR SONS PHARMACY (WAPDA TOWN)"/>
-        <filter val="BUNDU KHAN WAPDA TOWN"/>
-        <filter val="Euro Store E-2 (Wapda Town)"/>
-        <filter val="GRAIN MART WAPDA TOWN"/>
-        <filter val="JALAL SONS (WAPDA TOWN) 02"/>
-        <filter val="RAHIM STORE WAPDA TOWN"/>
+        <filter val="M.S Traders Harbanspura (Risen)"/>
+        <filter val="Risen / Gajjumata _Rafaqat Sons"/>
+        <filter val="Risen / Manawa _CB TRADERS"/>
+        <filter val="Risen / Sabzazar _Rafaqat Sons"/>
+        <filter val="Risen / Shadbagh _SB Traders"/>
+        <filter val="Risen / TN Traders (Raiwind Road )"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">

--- a/all reports/Client Name & NTN List.xlsx
+++ b/all reports/Client Name & NTN List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1207B9E-637D-4BB0-9E3C-81353CB4554A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9563C28-2E97-4BC5-B0A5-C494E47B2C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="806">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="806">
   <si>
     <t>Sr#</t>
   </si>
@@ -981,9 +981,6 @@
     <t>8062267-4</t>
   </si>
   <si>
-    <t>EURO STORE (N F C )</t>
-  </si>
-  <si>
     <t>E757686-3</t>
   </si>
   <si>
@@ -2446,6 +2443,9 @@
   </si>
   <si>
     <t xml:space="preserve">Risen / Gajjumata _Rafaqat Sons </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EURO STORE (N F C ) Kamla Chowk </t>
   </si>
 </sst>
 </file>
@@ -4472,7 +4472,7 @@
         <v>101</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>90</v>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="F245" s="3"/>
     </row>
-    <row r="246" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B246" s="2">
         <f t="shared" si="3"/>
         <v>242</v>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="F246" s="3"/>
     </row>
-    <row r="247" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B247" s="2">
         <f t="shared" si="3"/>
         <v>243</v>
@@ -6754,272 +6754,272 @@
       </c>
       <c r="F247" s="3"/>
     </row>
-    <row r="248" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B248" s="2">
         <f t="shared" si="3"/>
         <v>244</v>
       </c>
       <c r="C248" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="D248" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="D248" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="E248" s="1" t="s">
-        <v>5</v>
+      <c r="E248" s="9">
+        <v>3277876353369</v>
       </c>
       <c r="F248" s="3"/>
     </row>
-    <row r="249" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B249" s="2">
         <f t="shared" si="3"/>
         <v>245</v>
       </c>
       <c r="C249" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D249" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="D249" s="2" t="s">
-        <v>320</v>
-      </c>
       <c r="E249" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F249" s="3"/>
     </row>
-    <row r="250" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B250" s="2">
         <f t="shared" si="3"/>
         <v>246</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F250" s="3"/>
     </row>
-    <row r="251" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B251" s="2">
         <f t="shared" si="3"/>
         <v>247</v>
       </c>
       <c r="C251" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D251" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="D251" s="2" t="s">
-        <v>323</v>
-      </c>
       <c r="E251" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F251" s="3"/>
     </row>
-    <row r="252" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B252" s="2">
         <f t="shared" si="3"/>
         <v>248</v>
       </c>
       <c r="C252" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D252" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="D252" s="2" t="s">
-        <v>325</v>
-      </c>
       <c r="E252" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F252" s="3"/>
     </row>
-    <row r="253" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B253" s="2">
         <f t="shared" si="3"/>
         <v>249</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E253" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F253" s="3"/>
     </row>
-    <row r="254" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B254" s="2">
         <f t="shared" si="3"/>
         <v>250</v>
       </c>
       <c r="C254" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D254" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="D254" s="2" t="s">
-        <v>327</v>
-      </c>
       <c r="E254" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F254" s="3"/>
     </row>
-    <row r="255" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B255" s="2">
         <f t="shared" si="3"/>
         <v>251</v>
       </c>
       <c r="C255" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D255" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="D255" s="2" t="s">
-        <v>329</v>
-      </c>
       <c r="E255" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F255" s="3"/>
     </row>
-    <row r="256" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B256" s="2">
         <f t="shared" si="3"/>
         <v>252</v>
       </c>
       <c r="C256" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D256" s="2" t="s">
         <v>330</v>
-      </c>
-      <c r="D256" s="2" t="s">
-        <v>331</v>
       </c>
       <c r="E256" s="2">
         <v>5440099376763</v>
       </c>
       <c r="F256" s="3"/>
     </row>
-    <row r="257" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B257" s="2">
         <f t="shared" si="3"/>
         <v>253</v>
       </c>
       <c r="C257" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D257" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="D257" s="2" t="s">
-        <v>333</v>
-      </c>
       <c r="E257" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F257" s="3"/>
     </row>
-    <row r="258" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B258" s="2">
         <f t="shared" si="3"/>
         <v>254</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E258" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F258" s="3"/>
     </row>
-    <row r="259" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B259" s="2">
         <f t="shared" si="3"/>
         <v>255</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E259" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F259" s="3"/>
     </row>
-    <row r="260" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B260" s="2">
         <f t="shared" si="3"/>
         <v>256</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E260" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F260" s="3"/>
     </row>
-    <row r="261" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B261" s="2">
         <f t="shared" si="3"/>
         <v>257</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E261" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F261" s="3"/>
     </row>
-    <row r="262" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B262" s="2">
         <f t="shared" si="3"/>
         <v>258</v>
       </c>
       <c r="C262" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="D262" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="D262" s="2" t="s">
-        <v>338</v>
-      </c>
       <c r="E262" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F262" s="3"/>
     </row>
-    <row r="263" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B263" s="2">
         <f t="shared" si="3"/>
         <v>259</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E263" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F263" s="3"/>
     </row>
-    <row r="264" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:6" ht="13" x14ac:dyDescent="0.3">
       <c r="B264" s="2">
         <f t="shared" si="3"/>
         <v>260</v>
       </c>
       <c r="C264" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D264" s="2" t="s">
         <v>340</v>
-      </c>
-      <c r="D264" s="2" t="s">
-        <v>341</v>
       </c>
       <c r="E264" s="1" t="s">
         <v>5</v>
@@ -7032,10 +7032,10 @@
         <v>261</v>
       </c>
       <c r="C265" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="D265" s="2" t="s">
         <v>342</v>
-      </c>
-      <c r="D265" s="2" t="s">
-        <v>343</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>5</v>
@@ -7048,10 +7048,10 @@
         <v>262</v>
       </c>
       <c r="C266" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D266" s="2" t="s">
         <v>344</v>
-      </c>
-      <c r="D266" s="2" t="s">
-        <v>345</v>
       </c>
       <c r="E266" s="2" t="s">
         <v>5</v>
@@ -7064,13 +7064,13 @@
         <v>263</v>
       </c>
       <c r="C267" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D267" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E267" s="2" t="s">
         <v>346</v>
-      </c>
-      <c r="D267" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E267" s="2" t="s">
-        <v>347</v>
       </c>
       <c r="F267" s="3"/>
     </row>
@@ -7080,10 +7080,10 @@
         <v>264</v>
       </c>
       <c r="C268" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D268" s="2" t="s">
         <v>348</v>
-      </c>
-      <c r="D268" s="2" t="s">
-        <v>349</v>
       </c>
       <c r="E268" s="2" t="s">
         <v>5</v>
@@ -7096,10 +7096,10 @@
         <v>265</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E269" s="2" t="s">
         <v>5</v>
@@ -7112,10 +7112,10 @@
         <v>266</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E270" s="2" t="s">
         <v>5</v>
@@ -7128,10 +7128,10 @@
         <v>267</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E271" s="2" t="s">
         <v>5</v>
@@ -7144,10 +7144,10 @@
         <v>268</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>5</v>
@@ -7160,10 +7160,10 @@
         <v>269</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E273" s="2" t="s">
         <v>5</v>
@@ -7176,10 +7176,10 @@
         <v>270</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E274" s="2" t="s">
         <v>5</v>
@@ -7192,10 +7192,10 @@
         <v>271</v>
       </c>
       <c r="C275" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="D275" s="2" t="s">
         <v>356</v>
-      </c>
-      <c r="D275" s="2" t="s">
-        <v>357</v>
       </c>
       <c r="E275" s="2" t="s">
         <v>5</v>
@@ -7208,10 +7208,10 @@
         <v>272</v>
       </c>
       <c r="C276" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="D276" s="2" t="s">
         <v>358</v>
-      </c>
-      <c r="D276" s="2" t="s">
-        <v>359</v>
       </c>
       <c r="E276" s="2" t="s">
         <v>5</v>
@@ -7224,10 +7224,10 @@
         <v>273</v>
       </c>
       <c r="C277" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D277" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="D277" s="2" t="s">
-        <v>361</v>
       </c>
       <c r="E277" s="2" t="s">
         <v>5</v>
@@ -7240,13 +7240,13 @@
         <v>274</v>
       </c>
       <c r="C278" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E278" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="D278" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E278" s="2" t="s">
-        <v>363</v>
       </c>
       <c r="F278" s="3"/>
     </row>
@@ -7256,10 +7256,10 @@
         <v>275</v>
       </c>
       <c r="C279" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="D279" s="2" t="s">
         <v>364</v>
-      </c>
-      <c r="D279" s="2" t="s">
-        <v>365</v>
       </c>
       <c r="E279" s="2" t="s">
         <v>5</v>
@@ -7272,10 +7272,10 @@
         <v>276</v>
       </c>
       <c r="C280" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="D280" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="D280" s="2" t="s">
-        <v>367</v>
       </c>
       <c r="E280" s="2" t="s">
         <v>5</v>
@@ -7288,10 +7288,10 @@
         <v>277</v>
       </c>
       <c r="C281" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="D281" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="D281" s="2" t="s">
-        <v>369</v>
       </c>
       <c r="E281" s="2" t="s">
         <v>5</v>
@@ -7304,10 +7304,10 @@
         <v>278</v>
       </c>
       <c r="C282" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D282" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="D282" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="E282" s="2" t="s">
         <v>5</v>
@@ -7320,10 +7320,10 @@
         <v>279</v>
       </c>
       <c r="C283" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D283" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="D283" s="2" t="s">
-        <v>373</v>
       </c>
       <c r="E283" s="2" t="s">
         <v>5</v>
@@ -7336,10 +7336,10 @@
         <v>280</v>
       </c>
       <c r="C284" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D284" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="D284" s="2" t="s">
-        <v>375</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>5</v>
@@ -7352,10 +7352,10 @@
         <v>281</v>
       </c>
       <c r="C285" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="D285" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="D285" s="2" t="s">
-        <v>377</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>5</v>
@@ -7368,10 +7368,10 @@
         <v>282</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E286" s="1" t="s">
         <v>5</v>
@@ -7384,10 +7384,10 @@
         <v>283</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E287" s="1" t="s">
         <v>5</v>
@@ -7400,10 +7400,10 @@
         <v>284</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E288" s="1" t="s">
         <v>5</v>
@@ -7416,10 +7416,10 @@
         <v>285</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E289" s="1" t="s">
         <v>5</v>
@@ -7432,10 +7432,10 @@
         <v>286</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E290" s="1" t="s">
         <v>5</v>
@@ -7448,10 +7448,10 @@
         <v>287</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>5</v>
@@ -7464,10 +7464,10 @@
         <v>288</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>5</v>
@@ -7480,10 +7480,10 @@
         <v>289</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>5</v>
@@ -7496,10 +7496,10 @@
         <v>290</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>5</v>
@@ -7512,10 +7512,10 @@
         <v>291</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>5</v>
@@ -7528,10 +7528,10 @@
         <v>292</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E296" s="1" t="s">
         <v>5</v>
@@ -7544,10 +7544,10 @@
         <v>293</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>5</v>
@@ -7560,10 +7560,10 @@
         <v>294</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>5</v>
@@ -7576,10 +7576,10 @@
         <v>295</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E299" s="1" t="s">
         <v>5</v>
@@ -7592,10 +7592,10 @@
         <v>296</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E300" s="1" t="s">
         <v>5</v>
@@ -7608,10 +7608,10 @@
         <v>297</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E301" s="1" t="s">
         <v>5</v>
@@ -7624,10 +7624,10 @@
         <v>298</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E302" s="1" t="s">
         <v>5</v>
@@ -7640,10 +7640,10 @@
         <v>299</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E303" s="1" t="s">
         <v>5</v>
@@ -7656,10 +7656,10 @@
         <v>300</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E304" s="1" t="s">
         <v>5</v>
@@ -7672,10 +7672,10 @@
         <v>301</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E305" s="1" t="s">
         <v>5</v>
@@ -7688,10 +7688,10 @@
         <v>302</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E306" s="1" t="s">
         <v>5</v>
@@ -7704,10 +7704,10 @@
         <v>303</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E307" s="1" t="s">
         <v>5</v>
@@ -7720,10 +7720,10 @@
         <v>304</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E308" s="1" t="s">
         <v>5</v>
@@ -7736,10 +7736,10 @@
         <v>305</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E309" s="1" t="s">
         <v>5</v>
@@ -7752,10 +7752,10 @@
         <v>306</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E310" s="1" t="s">
         <v>5</v>
@@ -7768,10 +7768,10 @@
         <v>307</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E311" s="1" t="s">
         <v>5</v>
@@ -7784,10 +7784,10 @@
         <v>308</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E312" s="1" t="s">
         <v>5</v>
@@ -7800,10 +7800,10 @@
         <v>309</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E313" s="1" t="s">
         <v>5</v>
@@ -7816,10 +7816,10 @@
         <v>310</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E314" s="1" t="s">
         <v>5</v>
@@ -7832,10 +7832,10 @@
         <v>311</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E315" s="1" t="s">
         <v>5</v>
@@ -7848,10 +7848,10 @@
         <v>312</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E316" s="1" t="s">
         <v>5</v>
@@ -7864,10 +7864,10 @@
         <v>313</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E317" s="1" t="s">
         <v>5</v>
@@ -7880,10 +7880,10 @@
         <v>314</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E318" s="1" t="s">
         <v>5</v>
@@ -7896,10 +7896,10 @@
         <v>315</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E319" s="1" t="s">
         <v>5</v>
@@ -7912,10 +7912,10 @@
         <v>316</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>5</v>
@@ -7928,10 +7928,10 @@
         <v>317</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E321" s="1" t="s">
         <v>5</v>
@@ -7944,10 +7944,10 @@
         <v>318</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E322" s="1" t="s">
         <v>5</v>
@@ -7960,10 +7960,10 @@
         <v>319</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E323" s="1" t="s">
         <v>5</v>
@@ -7976,10 +7976,10 @@
         <v>320</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E324" s="1" t="s">
         <v>5</v>
@@ -7992,10 +7992,10 @@
         <v>321</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E325" s="1" t="s">
         <v>5</v>
@@ -8008,10 +8008,10 @@
         <v>322</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E326" s="1" t="s">
         <v>5</v>
@@ -8024,10 +8024,10 @@
         <v>323</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E327" s="1" t="s">
         <v>5</v>
@@ -8040,10 +8040,10 @@
         <v>324</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>5</v>
@@ -8056,10 +8056,10 @@
         <v>325</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>5</v>
@@ -8072,10 +8072,10 @@
         <v>326</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>5</v>
@@ -8088,10 +8088,10 @@
         <v>327</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E331" s="1" t="s">
         <v>5</v>
@@ -8104,10 +8104,10 @@
         <v>328</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>5</v>
@@ -8120,10 +8120,10 @@
         <v>329</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>5</v>
@@ -8136,10 +8136,10 @@
         <v>330</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E334" s="1" t="s">
         <v>5</v>
@@ -8152,10 +8152,10 @@
         <v>331</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E335" s="1" t="s">
         <v>5</v>
@@ -8168,10 +8168,10 @@
         <v>332</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E336" s="1" t="s">
         <v>5</v>
@@ -8184,10 +8184,10 @@
         <v>333</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E337" s="1" t="s">
         <v>5</v>
@@ -8200,10 +8200,10 @@
         <v>334</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E338" s="1" t="s">
         <v>5</v>
@@ -8216,10 +8216,10 @@
         <v>335</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E339" s="1" t="s">
         <v>5</v>
@@ -8232,10 +8232,10 @@
         <v>336</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E340" s="1" t="s">
         <v>5</v>
@@ -8248,10 +8248,10 @@
         <v>337</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>5</v>
@@ -8264,10 +8264,10 @@
         <v>338</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E342" s="1" t="s">
         <v>5</v>
@@ -8280,10 +8280,10 @@
         <v>339</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E343" s="1" t="s">
         <v>5</v>
@@ -8296,10 +8296,10 @@
         <v>340</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E344" s="1" t="s">
         <v>5</v>
@@ -8312,10 +8312,10 @@
         <v>341</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E345" s="1" t="s">
         <v>5</v>
@@ -8328,10 +8328,10 @@
         <v>342</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E346" s="1" t="s">
         <v>5</v>
@@ -8344,10 +8344,10 @@
         <v>343</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E347" s="1" t="s">
         <v>5</v>
@@ -8360,10 +8360,10 @@
         <v>344</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>5</v>
@@ -8376,10 +8376,10 @@
         <v>345</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E349" s="1" t="s">
         <v>5</v>
@@ -8392,10 +8392,10 @@
         <v>346</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>5</v>
@@ -8408,10 +8408,10 @@
         <v>347</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E351" s="1" t="s">
         <v>5</v>
@@ -8424,10 +8424,10 @@
         <v>348</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E352" s="1" t="s">
         <v>5</v>
@@ -8440,10 +8440,10 @@
         <v>349</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E353" s="1" t="s">
         <v>5</v>
@@ -8456,10 +8456,10 @@
         <v>350</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E354" s="1" t="s">
         <v>5</v>
@@ -8472,10 +8472,10 @@
         <v>351</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E355" s="1" t="s">
         <v>5</v>
@@ -8488,10 +8488,10 @@
         <v>352</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E356" s="1" t="s">
         <v>5</v>
@@ -8504,10 +8504,10 @@
         <v>353</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E357" s="1" t="s">
         <v>5</v>
@@ -8520,10 +8520,10 @@
         <v>354</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E358" s="1" t="s">
         <v>5</v>
@@ -8536,10 +8536,10 @@
         <v>355</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E359" s="1" t="s">
         <v>5</v>
@@ -8552,10 +8552,10 @@
         <v>356</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E360" s="1" t="s">
         <v>5</v>
@@ -8568,10 +8568,10 @@
         <v>357</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E361" s="1" t="s">
         <v>5</v>
@@ -8584,10 +8584,10 @@
         <v>358</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E362" s="1" t="s">
         <v>5</v>
@@ -8600,10 +8600,10 @@
         <v>359</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E363" s="1" t="s">
         <v>5</v>
@@ -8616,10 +8616,10 @@
         <v>360</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E364" s="1" t="s">
         <v>5</v>
@@ -8632,10 +8632,10 @@
         <v>361</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E365" s="1" t="s">
         <v>5</v>
@@ -8648,10 +8648,10 @@
         <v>362</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>5</v>
@@ -8664,10 +8664,10 @@
         <v>363</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E367" s="1" t="s">
         <v>5</v>
@@ -8680,10 +8680,10 @@
         <v>364</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E368" s="1" t="s">
         <v>5</v>
@@ -8696,10 +8696,10 @@
         <v>365</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D369" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E369" s="1" t="s">
         <v>5</v>
@@ -8712,10 +8712,10 @@
         <v>366</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D370" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E370" s="1" t="s">
         <v>5</v>
@@ -8728,10 +8728,10 @@
         <v>367</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E371" s="1" t="s">
         <v>5</v>
@@ -8744,10 +8744,10 @@
         <v>368</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D372" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E372" s="1" t="s">
         <v>5</v>
@@ -8760,10 +8760,10 @@
         <v>369</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E373" s="1" t="s">
         <v>5</v>
@@ -8776,10 +8776,10 @@
         <v>370</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D374" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E374" s="1" t="s">
         <v>5</v>
@@ -8792,10 +8792,10 @@
         <v>371</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E375" s="1" t="s">
         <v>5</v>
@@ -8808,10 +8808,10 @@
         <v>372</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E376" s="1" t="s">
         <v>5</v>
@@ -8824,10 +8824,10 @@
         <v>373</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E377" s="1" t="s">
         <v>5</v>
@@ -8840,10 +8840,10 @@
         <v>374</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D378" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E378" s="1" t="s">
         <v>5</v>
@@ -8856,10 +8856,10 @@
         <v>375</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E379" s="1" t="s">
         <v>5</v>
@@ -8872,10 +8872,10 @@
         <v>376</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D380" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E380" s="1" t="s">
         <v>5</v>
@@ -8888,10 +8888,10 @@
         <v>377</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E381" s="1" t="s">
         <v>5</v>
@@ -8904,10 +8904,10 @@
         <v>378</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D382" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E382" s="1" t="s">
         <v>5</v>
@@ -8920,10 +8920,10 @@
         <v>379</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D383" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E383" s="1" t="s">
         <v>5</v>
@@ -8936,10 +8936,10 @@
         <v>380</v>
       </c>
       <c r="C384" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="D384" s="2" t="s">
         <v>476</v>
-      </c>
-      <c r="D384" s="2" t="s">
-        <v>477</v>
       </c>
       <c r="E384" s="1" t="s">
         <v>5</v>
@@ -8952,10 +8952,10 @@
         <v>381</v>
       </c>
       <c r="C385" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="D385" s="2" t="s">
         <v>478</v>
-      </c>
-      <c r="D385" s="2" t="s">
-        <v>479</v>
       </c>
       <c r="E385" s="1" t="s">
         <v>5</v>
@@ -8968,10 +8968,10 @@
         <v>382</v>
       </c>
       <c r="C386" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="D386" s="2" t="s">
         <v>480</v>
-      </c>
-      <c r="D386" s="2" t="s">
-        <v>481</v>
       </c>
       <c r="E386" s="1" t="s">
         <v>5</v>
@@ -8984,10 +8984,10 @@
         <v>383</v>
       </c>
       <c r="C387" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D387" s="2" t="s">
         <v>482</v>
-      </c>
-      <c r="D387" s="2" t="s">
-        <v>483</v>
       </c>
       <c r="E387" s="1" t="s">
         <v>5</v>
@@ -9000,10 +9000,10 @@
         <v>384</v>
       </c>
       <c r="C388" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="D388" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="D388" s="2" t="s">
-        <v>485</v>
       </c>
       <c r="E388" s="1" t="s">
         <v>5</v>
@@ -9016,10 +9016,10 @@
         <v>385</v>
       </c>
       <c r="C389" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="D389" s="2" t="s">
         <v>486</v>
-      </c>
-      <c r="D389" s="2" t="s">
-        <v>487</v>
       </c>
       <c r="E389" s="1" t="s">
         <v>5</v>
@@ -9032,10 +9032,10 @@
         <v>386</v>
       </c>
       <c r="C390" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D390" s="2" t="s">
         <v>488</v>
-      </c>
-      <c r="D390" s="2" t="s">
-        <v>489</v>
       </c>
       <c r="E390" s="1" t="s">
         <v>5</v>
@@ -9048,10 +9048,10 @@
         <v>387</v>
       </c>
       <c r="C391" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="D391" s="2" t="s">
         <v>490</v>
-      </c>
-      <c r="D391" s="2" t="s">
-        <v>491</v>
       </c>
       <c r="E391" s="1" t="s">
         <v>5</v>
@@ -9064,10 +9064,10 @@
         <v>388</v>
       </c>
       <c r="C392" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="D392" s="2" t="s">
         <v>492</v>
-      </c>
-      <c r="D392" s="2" t="s">
-        <v>493</v>
       </c>
       <c r="E392" s="1" t="s">
         <v>5</v>
@@ -9080,10 +9080,10 @@
         <v>389</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E393" s="1" t="s">
         <v>5</v>
@@ -9096,10 +9096,10 @@
         <v>390</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E394" s="1" t="s">
         <v>5</v>
@@ -9112,10 +9112,10 @@
         <v>391</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D395" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E395" s="1" t="s">
         <v>5</v>
@@ -9128,10 +9128,10 @@
         <v>392</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E396" s="1" t="s">
         <v>5</v>
@@ -9144,10 +9144,10 @@
         <v>393</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E397" s="2" t="s">
         <v>5</v>
@@ -9160,10 +9160,10 @@
         <v>394</v>
       </c>
       <c r="C398" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="D398" s="2" t="s">
         <v>499</v>
-      </c>
-      <c r="D398" s="2" t="s">
-        <v>500</v>
       </c>
       <c r="E398" s="2" t="s">
         <v>5</v>
@@ -9176,13 +9176,13 @@
         <v>395</v>
       </c>
       <c r="C399" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="D399" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E399" s="2" t="s">
         <v>501</v>
-      </c>
-      <c r="D399" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E399" s="2" t="s">
-        <v>502</v>
       </c>
       <c r="F399" s="3"/>
     </row>
@@ -9192,10 +9192,10 @@
         <v>396</v>
       </c>
       <c r="C400" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="D400" s="2" t="s">
         <v>503</v>
-      </c>
-      <c r="D400" s="2" t="s">
-        <v>504</v>
       </c>
       <c r="E400" s="2" t="s">
         <v>5</v>
@@ -9208,10 +9208,10 @@
         <v>397</v>
       </c>
       <c r="C401" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="D401" s="2" t="s">
         <v>505</v>
-      </c>
-      <c r="D401" s="2" t="s">
-        <v>506</v>
       </c>
       <c r="E401" s="2" t="s">
         <v>5</v>
@@ -9224,10 +9224,10 @@
         <v>398</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E402" s="2" t="s">
         <v>5</v>
@@ -9240,10 +9240,10 @@
         <v>399</v>
       </c>
       <c r="C403" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="D403" s="2" t="s">
         <v>508</v>
-      </c>
-      <c r="D403" s="2" t="s">
-        <v>509</v>
       </c>
       <c r="E403" s="2" t="s">
         <v>5</v>
@@ -9256,10 +9256,10 @@
         <v>400</v>
       </c>
       <c r="C404" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D404" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="D404" s="2" t="s">
-        <v>511</v>
       </c>
       <c r="E404" s="1" t="s">
         <v>5</v>
@@ -9272,10 +9272,10 @@
         <v>401</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D405" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E405" s="1" t="s">
         <v>5</v>
@@ -9288,10 +9288,10 @@
         <v>402</v>
       </c>
       <c r="C406" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="D406" s="2" t="s">
         <v>513</v>
-      </c>
-      <c r="D406" s="2" t="s">
-        <v>514</v>
       </c>
       <c r="E406" s="1" t="s">
         <v>5</v>
@@ -9304,10 +9304,10 @@
         <v>403</v>
       </c>
       <c r="C407" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="D407" s="2" t="s">
         <v>515</v>
-      </c>
-      <c r="D407" s="2" t="s">
-        <v>516</v>
       </c>
       <c r="E407" s="1" t="s">
         <v>5</v>
@@ -9320,10 +9320,10 @@
         <v>404</v>
       </c>
       <c r="C408" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="D408" s="2" t="s">
         <v>517</v>
-      </c>
-      <c r="D408" s="2" t="s">
-        <v>518</v>
       </c>
       <c r="E408" s="1" t="s">
         <v>5</v>
@@ -9336,10 +9336,10 @@
         <v>405</v>
       </c>
       <c r="C409" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="D409" s="2" t="s">
         <v>519</v>
-      </c>
-      <c r="D409" s="2" t="s">
-        <v>520</v>
       </c>
       <c r="E409" s="1" t="s">
         <v>5</v>
@@ -9352,10 +9352,10 @@
         <v>406</v>
       </c>
       <c r="C410" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D410" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E410" s="1" t="s">
         <v>5</v>
@@ -9368,10 +9368,10 @@
         <v>407</v>
       </c>
       <c r="C411" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D411" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E411" s="1" t="s">
         <v>5</v>
@@ -9384,10 +9384,10 @@
         <v>408</v>
       </c>
       <c r="C412" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D412" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E412" s="1" t="s">
         <v>5</v>
@@ -9400,10 +9400,10 @@
         <v>409</v>
       </c>
       <c r="C413" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D413" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E413" s="1" t="s">
         <v>5</v>
@@ -9416,10 +9416,10 @@
         <v>410</v>
       </c>
       <c r="C414" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D414" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E414" s="1" t="s">
         <v>5</v>
@@ -9432,10 +9432,10 @@
         <v>411</v>
       </c>
       <c r="C415" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D415" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E415" s="1" t="s">
         <v>5</v>
@@ -9448,10 +9448,10 @@
         <v>412</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D416" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E416" s="1" t="s">
         <v>5</v>
@@ -9464,10 +9464,10 @@
         <v>413</v>
       </c>
       <c r="C417" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D417" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E417" s="1" t="s">
         <v>5</v>
@@ -9480,10 +9480,10 @@
         <v>414</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D418" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E418" s="1" t="s">
         <v>5</v>
@@ -9496,10 +9496,10 @@
         <v>415</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D419" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E419" s="7">
         <v>3277876126916</v>
@@ -9512,10 +9512,10 @@
         <v>416</v>
       </c>
       <c r="C420" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D420" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E420" s="1" t="s">
         <v>5</v>
@@ -9528,10 +9528,10 @@
         <v>417</v>
       </c>
       <c r="C421" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D421" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E421" s="1" t="s">
         <v>5</v>
@@ -9544,10 +9544,10 @@
         <v>418</v>
       </c>
       <c r="C422" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D422" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E422" s="1" t="s">
         <v>5</v>
@@ -9560,10 +9560,10 @@
         <v>419</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D423" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E423" s="1" t="s">
         <v>5</v>
@@ -9576,10 +9576,10 @@
         <v>420</v>
       </c>
       <c r="C424" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D424" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E424" s="1" t="s">
         <v>5</v>
@@ -9592,10 +9592,10 @@
         <v>421</v>
       </c>
       <c r="C425" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D425" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E425" s="1" t="s">
         <v>5</v>
@@ -9608,10 +9608,10 @@
         <v>422</v>
       </c>
       <c r="C426" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D426" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E426" s="1" t="s">
         <v>5</v>
@@ -9624,10 +9624,10 @@
         <v>423</v>
       </c>
       <c r="C427" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D427" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E427" s="1" t="s">
         <v>5</v>
@@ -9640,10 +9640,10 @@
         <v>424</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D428" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E428" s="1" t="s">
         <v>5</v>
@@ -9656,10 +9656,10 @@
         <v>425</v>
       </c>
       <c r="C429" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E429" s="1" t="s">
         <v>5</v>
@@ -9672,10 +9672,10 @@
         <v>426</v>
       </c>
       <c r="C430" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D430" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E430" s="7">
         <v>3520255124113</v>
@@ -9688,10 +9688,10 @@
         <v>427</v>
       </c>
       <c r="C431" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E431" s="1" t="s">
         <v>5</v>
@@ -9704,10 +9704,10 @@
         <v>428</v>
       </c>
       <c r="C432" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E432" s="1" t="s">
         <v>5</v>
@@ -9720,10 +9720,10 @@
         <v>429</v>
       </c>
       <c r="C433" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E433" s="1" t="s">
         <v>5</v>
@@ -9736,10 +9736,10 @@
         <v>430</v>
       </c>
       <c r="C434" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>5</v>
@@ -9752,10 +9752,10 @@
         <v>431</v>
       </c>
       <c r="C435" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>5</v>
@@ -9768,10 +9768,10 @@
         <v>432</v>
       </c>
       <c r="C436" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>5</v>
@@ -9784,10 +9784,10 @@
         <v>433</v>
       </c>
       <c r="C437" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E437" s="1" t="s">
         <v>5</v>
@@ -9800,10 +9800,10 @@
         <v>434</v>
       </c>
       <c r="C438" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E438" s="1" t="s">
         <v>5</v>
@@ -9816,10 +9816,10 @@
         <v>435</v>
       </c>
       <c r="C439" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>5</v>
@@ -9832,10 +9832,10 @@
         <v>436</v>
       </c>
       <c r="C440" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>5</v>
@@ -9848,10 +9848,10 @@
         <v>437</v>
       </c>
       <c r="C441" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>5</v>
@@ -9864,10 +9864,10 @@
         <v>438</v>
       </c>
       <c r="C442" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E442" s="1" t="s">
         <v>5</v>
@@ -9880,10 +9880,10 @@
         <v>439</v>
       </c>
       <c r="C443" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="D443" s="2" t="s">
         <v>553</v>
-      </c>
-      <c r="D443" s="2" t="s">
-        <v>554</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>5</v>
@@ -9896,10 +9896,10 @@
         <v>440</v>
       </c>
       <c r="C444" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="D444" s="2" t="s">
         <v>555</v>
-      </c>
-      <c r="D444" s="2" t="s">
-        <v>556</v>
       </c>
       <c r="E444" s="1" t="s">
         <v>5</v>
@@ -9912,10 +9912,10 @@
         <v>441</v>
       </c>
       <c r="C445" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="D445" s="2" t="s">
         <v>557</v>
-      </c>
-      <c r="D445" s="2" t="s">
-        <v>558</v>
       </c>
       <c r="E445" s="1" t="s">
         <v>5</v>
@@ -9928,10 +9928,10 @@
         <v>442</v>
       </c>
       <c r="C446" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D446" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E446" s="1" t="s">
         <v>5</v>
@@ -9944,10 +9944,10 @@
         <v>443</v>
       </c>
       <c r="C447" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E447" s="1" t="s">
         <v>5</v>
@@ -9960,10 +9960,10 @@
         <v>444</v>
       </c>
       <c r="C448" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E448" s="1" t="s">
         <v>5</v>
@@ -9976,10 +9976,10 @@
         <v>445</v>
       </c>
       <c r="C449" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E449" s="1" t="s">
         <v>5</v>
@@ -9992,10 +9992,10 @@
         <v>446</v>
       </c>
       <c r="C450" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E450" s="1" t="s">
         <v>5</v>
@@ -10008,10 +10008,10 @@
         <v>447</v>
       </c>
       <c r="C451" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E451" s="1" t="s">
         <v>5</v>
@@ -10024,10 +10024,10 @@
         <v>448</v>
       </c>
       <c r="C452" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E452" s="1" t="s">
         <v>5</v>
@@ -10040,10 +10040,10 @@
         <v>449</v>
       </c>
       <c r="C453" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>5</v>
@@ -10056,10 +10056,10 @@
         <v>450</v>
       </c>
       <c r="C454" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E454" s="1" t="s">
         <v>5</v>
@@ -10072,10 +10072,10 @@
         <v>451</v>
       </c>
       <c r="C455" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E455" s="1" t="s">
         <v>5</v>
@@ -10088,10 +10088,10 @@
         <v>452</v>
       </c>
       <c r="C456" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E456" s="1" t="s">
         <v>5</v>
@@ -10104,10 +10104,10 @@
         <v>453</v>
       </c>
       <c r="C457" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E457" s="1" t="s">
         <v>5</v>
@@ -10120,10 +10120,10 @@
         <v>454</v>
       </c>
       <c r="C458" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E458" s="1" t="s">
         <v>5</v>
@@ -10136,10 +10136,10 @@
         <v>455</v>
       </c>
       <c r="C459" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E459" s="1" t="s">
         <v>5</v>
@@ -10152,10 +10152,10 @@
         <v>456</v>
       </c>
       <c r="C460" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E460" s="1" t="s">
         <v>5</v>
@@ -10168,10 +10168,10 @@
         <v>457</v>
       </c>
       <c r="C461" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D461" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E461" s="1" t="s">
         <v>5</v>
@@ -10184,10 +10184,10 @@
         <v>458</v>
       </c>
       <c r="C462" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D462" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E462" s="1" t="s">
         <v>5</v>
@@ -10200,10 +10200,10 @@
         <v>459</v>
       </c>
       <c r="C463" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E463" s="1" t="s">
         <v>5</v>
@@ -10216,10 +10216,10 @@
         <v>460</v>
       </c>
       <c r="C464" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="D464" s="2" t="s">
         <v>577</v>
-      </c>
-      <c r="D464" s="2" t="s">
-        <v>578</v>
       </c>
       <c r="E464" s="1" t="s">
         <v>5</v>
@@ -10232,10 +10232,10 @@
         <v>461</v>
       </c>
       <c r="C465" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D465" s="2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E465" s="1" t="s">
         <v>5</v>
@@ -10248,26 +10248,26 @@
         <v>462</v>
       </c>
       <c r="C466" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="D466" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="D466" s="2" t="s">
-        <v>581</v>
-      </c>
       <c r="E466" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F466" s="3"/>
     </row>
-    <row r="467" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="467" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B467" s="2">
         <f t="shared" si="7"/>
         <v>463</v>
       </c>
       <c r="C467" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D467" s="2" t="s">
         <v>582</v>
-      </c>
-      <c r="D467" s="2" t="s">
-        <v>583</v>
       </c>
       <c r="E467" s="1" t="s">
         <v>5</v>
@@ -10280,10 +10280,10 @@
         <v>464</v>
       </c>
       <c r="C468" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="D468" s="2" t="s">
         <v>584</v>
-      </c>
-      <c r="D468" s="2" t="s">
-        <v>585</v>
       </c>
       <c r="E468" s="1" t="s">
         <v>5</v>
@@ -10296,7 +10296,7 @@
         <v>465</v>
       </c>
       <c r="C469" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D469" s="2" t="s">
         <v>114</v>
@@ -10312,10 +10312,10 @@
         <v>466</v>
       </c>
       <c r="C470" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="D470" s="2" t="s">
         <v>587</v>
-      </c>
-      <c r="D470" s="2" t="s">
-        <v>588</v>
       </c>
       <c r="E470" s="1" t="s">
         <v>5</v>
@@ -10328,7 +10328,7 @@
         <v>467</v>
       </c>
       <c r="C471" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D471" s="2" t="s">
         <v>114</v>
@@ -10344,7 +10344,7 @@
         <v>468</v>
       </c>
       <c r="C472" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D472" s="2" t="s">
         <v>114</v>
@@ -10360,7 +10360,7 @@
         <v>469</v>
       </c>
       <c r="C473" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D473" s="2" t="s">
         <v>176</v>
@@ -10376,7 +10376,7 @@
         <v>470</v>
       </c>
       <c r="C474" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D474" s="2" t="s">
         <v>234</v>
@@ -10392,10 +10392,10 @@
         <v>471</v>
       </c>
       <c r="C475" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="D475" s="2" t="s">
         <v>593</v>
-      </c>
-      <c r="D475" s="2" t="s">
-        <v>594</v>
       </c>
       <c r="E475" s="1" t="s">
         <v>5</v>
@@ -10408,13 +10408,13 @@
         <v>472</v>
       </c>
       <c r="C476" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="D476" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E476" s="2" t="s">
         <v>595</v>
-      </c>
-      <c r="D476" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E476" s="2" t="s">
-        <v>596</v>
       </c>
       <c r="F476" s="3"/>
     </row>
@@ -10424,10 +10424,10 @@
         <v>473</v>
       </c>
       <c r="C477" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="D477" s="2" t="s">
         <v>597</v>
-      </c>
-      <c r="D477" s="2" t="s">
-        <v>598</v>
       </c>
       <c r="E477" s="1" t="s">
         <v>5</v>
@@ -10440,10 +10440,10 @@
         <v>474</v>
       </c>
       <c r="C478" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D478" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E478" s="1" t="s">
         <v>5</v>
@@ -10456,10 +10456,10 @@
         <v>475</v>
       </c>
       <c r="C479" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D479" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E479" s="1" t="s">
         <v>5</v>
@@ -10472,10 +10472,10 @@
         <v>476</v>
       </c>
       <c r="C480" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D480" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E480" s="1" t="s">
         <v>5</v>
@@ -10488,10 +10488,10 @@
         <v>477</v>
       </c>
       <c r="C481" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D481" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E481" s="1" t="s">
         <v>5</v>
@@ -10504,10 +10504,10 @@
         <v>478</v>
       </c>
       <c r="C482" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D482" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E482" s="1" t="s">
         <v>5</v>
@@ -10520,10 +10520,10 @@
         <v>479</v>
       </c>
       <c r="C483" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D483" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E483" s="1" t="s">
         <v>5</v>
@@ -10536,10 +10536,10 @@
         <v>480</v>
       </c>
       <c r="C484" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D484" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E484" s="1" t="s">
         <v>5</v>
@@ -10552,10 +10552,10 @@
         <v>481</v>
       </c>
       <c r="C485" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D485" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E485" s="1" t="s">
         <v>5</v>
@@ -10568,10 +10568,10 @@
         <v>482</v>
       </c>
       <c r="C486" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D486" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E486" s="1" t="s">
         <v>5</v>
@@ -10584,10 +10584,10 @@
         <v>483</v>
       </c>
       <c r="C487" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D487" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E487" s="1" t="s">
         <v>5</v>
@@ -10600,10 +10600,10 @@
         <v>484</v>
       </c>
       <c r="C488" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D488" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E488" s="1" t="s">
         <v>5</v>
@@ -10616,10 +10616,10 @@
         <v>485</v>
       </c>
       <c r="C489" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D489" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E489" s="1" t="s">
         <v>5</v>
@@ -10632,10 +10632,10 @@
         <v>486</v>
       </c>
       <c r="C490" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D490" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E490" s="1" t="s">
         <v>5</v>
@@ -10648,10 +10648,10 @@
         <v>487</v>
       </c>
       <c r="C491" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D491" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E491" s="1" t="s">
         <v>5</v>
@@ -10664,10 +10664,10 @@
         <v>488</v>
       </c>
       <c r="C492" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D492" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E492" s="1" t="s">
         <v>5</v>
@@ -10680,10 +10680,10 @@
         <v>489</v>
       </c>
       <c r="C493" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D493" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E493" s="1" t="s">
         <v>5</v>
@@ -10696,10 +10696,10 @@
         <v>490</v>
       </c>
       <c r="C494" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D494" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E494" s="1" t="s">
         <v>5</v>
@@ -10712,10 +10712,10 @@
         <v>491</v>
       </c>
       <c r="C495" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D495" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E495" s="1" t="s">
         <v>5</v>
@@ -10728,10 +10728,10 @@
         <v>492</v>
       </c>
       <c r="C496" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="D496" s="2" t="s">
         <v>617</v>
-      </c>
-      <c r="D496" s="2" t="s">
-        <v>618</v>
       </c>
       <c r="E496" s="2" t="s">
         <v>5</v>
@@ -10744,13 +10744,13 @@
         <v>493</v>
       </c>
       <c r="C497" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="D497" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E497" s="2" t="s">
         <v>619</v>
-      </c>
-      <c r="D497" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E497" s="2" t="s">
-        <v>620</v>
       </c>
       <c r="F497" s="3"/>
     </row>
@@ -10760,10 +10760,10 @@
         <v>494</v>
       </c>
       <c r="C498" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="D498" s="2" t="s">
         <v>621</v>
-      </c>
-      <c r="D498" s="2" t="s">
-        <v>622</v>
       </c>
       <c r="E498" s="2" t="s">
         <v>5</v>
@@ -10776,10 +10776,10 @@
         <v>495</v>
       </c>
       <c r="C499" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="D499" s="2" t="s">
         <v>623</v>
-      </c>
-      <c r="D499" s="2" t="s">
-        <v>624</v>
       </c>
       <c r="E499" s="2" t="s">
         <v>5</v>
@@ -10792,13 +10792,13 @@
         <v>496</v>
       </c>
       <c r="C500" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="D500" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E500" s="2" t="s">
         <v>625</v>
-      </c>
-      <c r="D500" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E500" s="2" t="s">
-        <v>626</v>
       </c>
       <c r="F500" s="3"/>
     </row>
@@ -10808,10 +10808,10 @@
         <v>497</v>
       </c>
       <c r="C501" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="D501" s="2" t="s">
         <v>627</v>
-      </c>
-      <c r="D501" s="2" t="s">
-        <v>628</v>
       </c>
       <c r="E501" s="1" t="s">
         <v>5</v>
@@ -10824,10 +10824,10 @@
         <v>498</v>
       </c>
       <c r="C502" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="D502" s="2" t="s">
         <v>629</v>
-      </c>
-      <c r="D502" s="2" t="s">
-        <v>630</v>
       </c>
       <c r="E502" s="1" t="s">
         <v>5</v>
@@ -10840,10 +10840,10 @@
         <v>499</v>
       </c>
       <c r="C503" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D503" s="2" t="s">
         <v>631</v>
-      </c>
-      <c r="D503" s="2" t="s">
-        <v>632</v>
       </c>
       <c r="E503" s="1" t="s">
         <v>5</v>
@@ -10856,10 +10856,10 @@
         <v>500</v>
       </c>
       <c r="C504" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="D504" s="2" t="s">
         <v>633</v>
-      </c>
-      <c r="D504" s="2" t="s">
-        <v>634</v>
       </c>
       <c r="E504" s="1" t="s">
         <v>5</v>
@@ -10872,10 +10872,10 @@
         <v>501</v>
       </c>
       <c r="C505" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="D505" s="2" t="s">
         <v>635</v>
-      </c>
-      <c r="D505" s="2" t="s">
-        <v>636</v>
       </c>
       <c r="E505" s="1" t="s">
         <v>5</v>
@@ -10888,10 +10888,10 @@
         <v>502</v>
       </c>
       <c r="C506" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D506" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="E506" s="1" t="s">
         <v>5</v>
@@ -10904,10 +10904,10 @@
         <v>503</v>
       </c>
       <c r="C507" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="D507" s="2" t="s">
         <v>638</v>
-      </c>
-      <c r="D507" s="2" t="s">
-        <v>639</v>
       </c>
       <c r="E507" s="1" t="s">
         <v>5</v>
@@ -10920,10 +10920,10 @@
         <v>504</v>
       </c>
       <c r="C508" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D508" s="2" t="s">
         <v>640</v>
-      </c>
-      <c r="D508" s="2" t="s">
-        <v>641</v>
       </c>
       <c r="E508" s="1" t="s">
         <v>5</v>
@@ -10936,10 +10936,10 @@
         <v>505</v>
       </c>
       <c r="C509" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D509" s="2" t="s">
         <v>642</v>
-      </c>
-      <c r="D509" s="2" t="s">
-        <v>643</v>
       </c>
       <c r="E509" s="1" t="s">
         <v>5</v>
@@ -10952,10 +10952,10 @@
         <v>506</v>
       </c>
       <c r="C510" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="D510" s="2" t="s">
         <v>644</v>
-      </c>
-      <c r="D510" s="2" t="s">
-        <v>645</v>
       </c>
       <c r="E510" s="1" t="s">
         <v>5</v>
@@ -10968,10 +10968,10 @@
         <v>507</v>
       </c>
       <c r="C511" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D511" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E511" s="1" t="s">
         <v>5</v>
@@ -10984,10 +10984,10 @@
         <v>508</v>
       </c>
       <c r="C512" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="D512" s="2" t="s">
         <v>647</v>
-      </c>
-      <c r="D512" s="2" t="s">
-        <v>648</v>
       </c>
       <c r="E512" s="1" t="s">
         <v>5</v>
@@ -11000,10 +11000,10 @@
         <v>509</v>
       </c>
       <c r="C513" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="D513" s="2" t="s">
         <v>649</v>
-      </c>
-      <c r="D513" s="2" t="s">
-        <v>650</v>
       </c>
       <c r="E513" s="1" t="s">
         <v>5</v>
@@ -11016,10 +11016,10 @@
         <v>510</v>
       </c>
       <c r="C514" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="D514" s="2" t="s">
         <v>651</v>
-      </c>
-      <c r="D514" s="2" t="s">
-        <v>652</v>
       </c>
       <c r="E514" s="1" t="s">
         <v>5</v>
@@ -11032,10 +11032,10 @@
         <v>511</v>
       </c>
       <c r="C515" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="D515" s="2" t="s">
         <v>653</v>
-      </c>
-      <c r="D515" s="2" t="s">
-        <v>654</v>
       </c>
       <c r="E515" s="1" t="s">
         <v>5</v>
@@ -11048,13 +11048,13 @@
         <v>512</v>
       </c>
       <c r="C516" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="D516" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E516" s="2" t="s">
         <v>655</v>
-      </c>
-      <c r="D516" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E516" s="2" t="s">
-        <v>656</v>
       </c>
       <c r="F516" s="3"/>
     </row>
@@ -11064,10 +11064,10 @@
         <v>513</v>
       </c>
       <c r="C517" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="D517" s="2" t="s">
         <v>657</v>
-      </c>
-      <c r="D517" s="2" t="s">
-        <v>658</v>
       </c>
       <c r="E517" s="1" t="s">
         <v>5</v>
@@ -11080,10 +11080,10 @@
         <v>514</v>
       </c>
       <c r="C518" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="D518" s="2" t="s">
         <v>659</v>
-      </c>
-      <c r="D518" s="2" t="s">
-        <v>660</v>
       </c>
       <c r="E518" s="1" t="s">
         <v>5</v>
@@ -11096,10 +11096,10 @@
         <v>515</v>
       </c>
       <c r="C519" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="D519" s="2" t="s">
         <v>661</v>
-      </c>
-      <c r="D519" s="2" t="s">
-        <v>662</v>
       </c>
       <c r="E519" s="1" t="s">
         <v>5</v>
@@ -11112,10 +11112,10 @@
         <v>516</v>
       </c>
       <c r="C520" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="D520" s="2" t="s">
         <v>663</v>
-      </c>
-      <c r="D520" s="2" t="s">
-        <v>664</v>
       </c>
       <c r="E520" s="1" t="s">
         <v>5</v>
@@ -11128,10 +11128,10 @@
         <v>517</v>
       </c>
       <c r="C521" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="D521" s="2" t="s">
         <v>665</v>
-      </c>
-      <c r="D521" s="2" t="s">
-        <v>666</v>
       </c>
       <c r="E521" s="1" t="s">
         <v>5</v>
@@ -11144,7 +11144,7 @@
         <v>518</v>
       </c>
       <c r="C522" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D522" s="2" t="s">
         <v>5</v>
@@ -11160,10 +11160,10 @@
         <v>519</v>
       </c>
       <c r="C523" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="D523" s="2" t="s">
         <v>668</v>
-      </c>
-      <c r="D523" s="2" t="s">
-        <v>669</v>
       </c>
       <c r="E523" s="1" t="s">
         <v>5</v>
@@ -11176,10 +11176,10 @@
         <v>520</v>
       </c>
       <c r="C524" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="D524" s="2" t="s">
         <v>670</v>
-      </c>
-      <c r="D524" s="2" t="s">
-        <v>671</v>
       </c>
       <c r="E524" s="1" t="s">
         <v>5</v>
@@ -11192,10 +11192,10 @@
         <v>521</v>
       </c>
       <c r="C525" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="D525" s="2" t="s">
         <v>672</v>
-      </c>
-      <c r="D525" s="2" t="s">
-        <v>673</v>
       </c>
       <c r="E525" s="1" t="s">
         <v>5</v>
@@ -11208,10 +11208,10 @@
         <v>522</v>
       </c>
       <c r="C526" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="D526" s="2" t="s">
         <v>674</v>
-      </c>
-      <c r="D526" s="2" t="s">
-        <v>675</v>
       </c>
       <c r="E526" s="1" t="s">
         <v>5</v>
@@ -11224,10 +11224,10 @@
         <v>523</v>
       </c>
       <c r="C527" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="D527" s="2" t="s">
         <v>676</v>
-      </c>
-      <c r="D527" s="2" t="s">
-        <v>677</v>
       </c>
       <c r="E527" s="1" t="s">
         <v>5</v>
@@ -11240,10 +11240,10 @@
         <v>524</v>
       </c>
       <c r="C528" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="D528" s="2" t="s">
         <v>678</v>
-      </c>
-      <c r="D528" s="2" t="s">
-        <v>679</v>
       </c>
       <c r="E528" s="1" t="s">
         <v>5</v>
@@ -11256,10 +11256,10 @@
         <v>525</v>
       </c>
       <c r="C529" s="1" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D529" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E529" s="1" t="s">
         <v>5</v>
@@ -11272,7 +11272,7 @@
         <v>526</v>
       </c>
       <c r="C530" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D530" s="2" t="s">
         <v>5</v>
@@ -11288,10 +11288,10 @@
         <v>527</v>
       </c>
       <c r="C531" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="D531" s="2" t="s">
         <v>682</v>
-      </c>
-      <c r="D531" s="2" t="s">
-        <v>683</v>
       </c>
       <c r="E531" s="1" t="s">
         <v>5</v>
@@ -11304,13 +11304,13 @@
         <v>528</v>
       </c>
       <c r="C532" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="D532" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="D532" s="2" t="s">
-        <v>685</v>
-      </c>
       <c r="E532" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F532" s="3"/>
     </row>
@@ -11320,10 +11320,10 @@
         <v>529</v>
       </c>
       <c r="C533" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="D533" s="2" t="s">
         <v>686</v>
-      </c>
-      <c r="D533" s="2" t="s">
-        <v>687</v>
       </c>
       <c r="E533" s="1" t="s">
         <v>5</v>
@@ -11336,10 +11336,10 @@
         <v>530</v>
       </c>
       <c r="C534" s="1" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D534" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E534" s="1" t="s">
         <v>5</v>
@@ -11352,10 +11352,10 @@
         <v>531</v>
       </c>
       <c r="C535" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="D535" s="2" t="s">
         <v>689</v>
-      </c>
-      <c r="D535" s="2" t="s">
-        <v>690</v>
       </c>
       <c r="E535" s="1" t="s">
         <v>5</v>
@@ -11368,10 +11368,10 @@
         <v>532</v>
       </c>
       <c r="C536" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="D536" s="2" t="s">
         <v>691</v>
-      </c>
-      <c r="D536" s="2" t="s">
-        <v>692</v>
       </c>
       <c r="E536" s="1" t="s">
         <v>5</v>
@@ -11384,10 +11384,10 @@
         <v>533</v>
       </c>
       <c r="C537" s="1" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D537" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E537" s="1" t="s">
         <v>5</v>
@@ -11400,10 +11400,10 @@
         <v>534</v>
       </c>
       <c r="C538" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="D538" s="2" t="s">
         <v>694</v>
-      </c>
-      <c r="D538" s="2" t="s">
-        <v>695</v>
       </c>
       <c r="E538" s="1" t="s">
         <v>5</v>
@@ -11416,10 +11416,10 @@
         <v>535</v>
       </c>
       <c r="C539" s="1" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D539" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E539" s="1" t="s">
         <v>5</v>
@@ -11432,10 +11432,10 @@
         <v>536</v>
       </c>
       <c r="C540" s="1" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D540" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E540" s="1" t="s">
         <v>5</v>
@@ -11448,10 +11448,10 @@
         <v>537</v>
       </c>
       <c r="C541" s="1" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D541" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E541" s="1" t="s">
         <v>5</v>
@@ -11464,10 +11464,10 @@
         <v>538</v>
       </c>
       <c r="C542" s="1" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D542" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E542" s="1" t="s">
         <v>5</v>
@@ -11480,10 +11480,10 @@
         <v>539</v>
       </c>
       <c r="C543" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D543" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E543" s="1" t="s">
         <v>5</v>
@@ -11496,10 +11496,10 @@
         <v>540</v>
       </c>
       <c r="C544" s="1" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D544" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E544" s="1" t="s">
         <v>5</v>
@@ -11512,10 +11512,10 @@
         <v>541</v>
       </c>
       <c r="C545" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="D545" s="2" t="s">
         <v>702</v>
-      </c>
-      <c r="D545" s="2" t="s">
-        <v>703</v>
       </c>
       <c r="E545" s="1" t="s">
         <v>5</v>
@@ -11528,13 +11528,13 @@
         <v>542</v>
       </c>
       <c r="C546" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="D546" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E546" s="2" t="s">
         <v>704</v>
-      </c>
-      <c r="D546" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E546" s="2" t="s">
-        <v>705</v>
       </c>
       <c r="F546" s="3"/>
     </row>
@@ -11544,13 +11544,13 @@
         <v>543</v>
       </c>
       <c r="C547" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="D547" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E547" s="2" t="s">
         <v>706</v>
-      </c>
-      <c r="D547" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E547" s="2" t="s">
-        <v>707</v>
       </c>
       <c r="F547" s="3"/>
     </row>
@@ -11560,93 +11560,93 @@
         <v>544</v>
       </c>
       <c r="C548" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="D548" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="D548" s="2" t="s">
-        <v>709</v>
-      </c>
       <c r="E548" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F548" s="3"/>
     </row>
-    <row r="549" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="549" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B549" s="2">
         <f t="shared" si="8"/>
         <v>545</v>
       </c>
       <c r="C549" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D549" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E549" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F549" s="3"/>
     </row>
-    <row r="550" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="550" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B550" s="2">
         <f t="shared" si="8"/>
         <v>546</v>
       </c>
       <c r="C550" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="D550" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="D550" s="2" t="s">
-        <v>712</v>
-      </c>
       <c r="E550" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F550" s="3"/>
     </row>
-    <row r="551" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="551" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B551" s="2">
         <f t="shared" si="8"/>
         <v>547</v>
       </c>
       <c r="C551" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D551" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E551" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F551" s="3"/>
     </row>
-    <row r="552" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="552" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B552" s="2">
         <f t="shared" si="8"/>
         <v>548</v>
       </c>
       <c r="C552" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="D552" s="2" t="s">
         <v>713</v>
       </c>
-      <c r="D552" s="2" t="s">
-        <v>714</v>
-      </c>
       <c r="E552" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F552" s="3"/>
     </row>
-    <row r="553" spans="2:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="553" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B553" s="2">
         <f t="shared" si="8"/>
         <v>549</v>
       </c>
       <c r="C553" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D553" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="E553" s="13" t="s">
         <v>798</v>
-      </c>
-      <c r="E553" s="13" t="s">
-        <v>799</v>
       </c>
       <c r="F553" s="3"/>
     </row>
@@ -11656,10 +11656,10 @@
         <v>550</v>
       </c>
       <c r="C554" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="D554" s="2" t="s">
         <v>716</v>
-      </c>
-      <c r="D554" s="2" t="s">
-        <v>717</v>
       </c>
       <c r="E554" s="1" t="s">
         <v>5</v>
@@ -11672,10 +11672,10 @@
         <v>551</v>
       </c>
       <c r="C555" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="D555" s="2" t="s">
         <v>718</v>
-      </c>
-      <c r="D555" s="2" t="s">
-        <v>719</v>
       </c>
       <c r="E555" s="1" t="s">
         <v>5</v>
@@ -11688,10 +11688,10 @@
         <v>552</v>
       </c>
       <c r="C556" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="D556" s="2" t="s">
         <v>720</v>
-      </c>
-      <c r="D556" s="2" t="s">
-        <v>721</v>
       </c>
       <c r="E556" s="1" t="s">
         <v>5</v>
@@ -11704,10 +11704,10 @@
         <v>553</v>
       </c>
       <c r="C557" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="D557" s="2" t="s">
         <v>722</v>
-      </c>
-      <c r="D557" s="2" t="s">
-        <v>723</v>
       </c>
       <c r="E557" s="1" t="s">
         <v>5</v>
@@ -11720,10 +11720,10 @@
         <v>554</v>
       </c>
       <c r="C558" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D558" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E558" s="1" t="s">
         <v>5</v>
@@ -11736,10 +11736,10 @@
         <v>555</v>
       </c>
       <c r="C559" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D559" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E559" s="1" t="s">
         <v>5</v>
@@ -11752,7 +11752,7 @@
         <v>556</v>
       </c>
       <c r="C560" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D560" s="2" t="s">
         <v>160</v>
@@ -11768,10 +11768,10 @@
         <v>557</v>
       </c>
       <c r="C561" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="D561" s="2" t="s">
         <v>727</v>
-      </c>
-      <c r="D561" s="2" t="s">
-        <v>728</v>
       </c>
       <c r="E561" s="1" t="s">
         <v>5</v>
@@ -11784,10 +11784,10 @@
         <v>558</v>
       </c>
       <c r="C562" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="D562" s="2" t="s">
         <v>729</v>
-      </c>
-      <c r="D562" s="2" t="s">
-        <v>730</v>
       </c>
       <c r="E562" s="1" t="s">
         <v>5</v>
@@ -11800,10 +11800,10 @@
         <v>559</v>
       </c>
       <c r="C563" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="D563" s="2" t="s">
         <v>731</v>
-      </c>
-      <c r="D563" s="2" t="s">
-        <v>732</v>
       </c>
       <c r="E563" s="1" t="s">
         <v>5</v>
@@ -11816,10 +11816,10 @@
         <v>560</v>
       </c>
       <c r="C564" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D564" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E564" s="1" t="s">
         <v>5</v>
@@ -11832,10 +11832,10 @@
         <v>561</v>
       </c>
       <c r="C565" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D565" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E565" s="1" t="s">
         <v>5</v>
@@ -11848,10 +11848,10 @@
         <v>562</v>
       </c>
       <c r="C566" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D566" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E566" s="1" t="s">
         <v>5</v>
@@ -11864,10 +11864,10 @@
         <v>563</v>
       </c>
       <c r="C567" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D567" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E567" s="1" t="s">
         <v>5</v>
@@ -11880,10 +11880,10 @@
         <v>564</v>
       </c>
       <c r="C568" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D568" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E568" s="1" t="s">
         <v>5</v>
@@ -11896,10 +11896,10 @@
         <v>565</v>
       </c>
       <c r="C569" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D569" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E569" s="1" t="s">
         <v>5</v>
@@ -11912,10 +11912,10 @@
         <v>566</v>
       </c>
       <c r="C570" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D570" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E570" s="1" t="s">
         <v>5</v>
@@ -11928,10 +11928,10 @@
         <v>567</v>
       </c>
       <c r="C571" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D571" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E571" s="1" t="s">
         <v>5</v>
@@ -11944,10 +11944,10 @@
         <v>568</v>
       </c>
       <c r="C572" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D572" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E572" s="1" t="s">
         <v>5</v>
@@ -11960,10 +11960,10 @@
         <v>569</v>
       </c>
       <c r="C573" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D573" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E573" s="1" t="s">
         <v>5</v>
@@ -11976,10 +11976,10 @@
         <v>570</v>
       </c>
       <c r="C574" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D574" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E574" s="1" t="s">
         <v>5</v>
@@ -11992,10 +11992,10 @@
         <v>571</v>
       </c>
       <c r="C575" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D575" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E575" s="1" t="s">
         <v>5</v>
@@ -12008,10 +12008,10 @@
         <v>572</v>
       </c>
       <c r="C576" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D576" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E576" s="1" t="s">
         <v>5</v>
@@ -12024,10 +12024,10 @@
         <v>573</v>
       </c>
       <c r="C577" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="D577" s="2" t="s">
         <v>746</v>
-      </c>
-      <c r="D577" s="2" t="s">
-        <v>747</v>
       </c>
       <c r="E577" s="2" t="s">
         <v>5</v>
@@ -12040,10 +12040,10 @@
         <v>574</v>
       </c>
       <c r="C578" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="D578" s="2" t="s">
         <v>748</v>
-      </c>
-      <c r="D578" s="2" t="s">
-        <v>749</v>
       </c>
       <c r="E578" s="1" t="s">
         <v>5</v>
@@ -12056,10 +12056,10 @@
         <v>575</v>
       </c>
       <c r="C579" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="D579" s="2" t="s">
         <v>750</v>
-      </c>
-      <c r="D579" s="2" t="s">
-        <v>751</v>
       </c>
       <c r="E579" s="1" t="s">
         <v>5</v>
@@ -12072,10 +12072,10 @@
         <v>576</v>
       </c>
       <c r="C580" s="1" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D580" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="E580" s="1" t="s">
         <v>5</v>
@@ -12088,10 +12088,10 @@
         <v>577</v>
       </c>
       <c r="C581" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="D581" s="2" t="s">
         <v>753</v>
-      </c>
-      <c r="D581" s="2" t="s">
-        <v>754</v>
       </c>
       <c r="E581" s="1" t="s">
         <v>5</v>
@@ -12104,10 +12104,10 @@
         <v>578</v>
       </c>
       <c r="C582" s="1" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D582" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E582" s="7">
         <v>3520268948847</v>
@@ -12120,10 +12120,10 @@
         <v>579</v>
       </c>
       <c r="C583" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="D583" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E583" s="1" t="s">
         <v>5</v>
@@ -12136,10 +12136,10 @@
         <v>580</v>
       </c>
       <c r="C584" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="D584" s="2" t="s">
         <v>757</v>
-      </c>
-      <c r="D584" s="2" t="s">
-        <v>758</v>
       </c>
       <c r="E584" s="1" t="s">
         <v>5</v>
@@ -12152,10 +12152,10 @@
         <v>581</v>
       </c>
       <c r="C585" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="D585" s="2" t="s">
         <v>759</v>
-      </c>
-      <c r="D585" s="2" t="s">
-        <v>760</v>
       </c>
       <c r="E585" s="1" t="s">
         <v>5</v>
@@ -12168,10 +12168,10 @@
         <v>582</v>
       </c>
       <c r="C586" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D586" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="E586" s="1" t="s">
         <v>5</v>
@@ -12184,10 +12184,10 @@
         <v>583</v>
       </c>
       <c r="C587" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="D587" s="2" t="s">
         <v>762</v>
-      </c>
-      <c r="D587" s="2" t="s">
-        <v>763</v>
       </c>
       <c r="E587" s="1" t="s">
         <v>5</v>
@@ -12200,10 +12200,10 @@
         <v>584</v>
       </c>
       <c r="C588" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="D588" s="2" t="s">
         <v>764</v>
-      </c>
-      <c r="D588" s="2" t="s">
-        <v>765</v>
       </c>
       <c r="E588" s="1" t="s">
         <v>5</v>
@@ -12216,10 +12216,10 @@
         <v>585</v>
       </c>
       <c r="C589" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="D589" s="2" t="s">
         <v>766</v>
-      </c>
-      <c r="D589" s="2" t="s">
-        <v>767</v>
       </c>
       <c r="E589" s="1" t="s">
         <v>5</v>
@@ -12232,10 +12232,10 @@
         <v>586</v>
       </c>
       <c r="C590" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="D590" s="2" t="s">
         <v>768</v>
-      </c>
-      <c r="D590" s="2" t="s">
-        <v>769</v>
       </c>
       <c r="E590" s="1" t="s">
         <v>5</v>
@@ -12248,10 +12248,10 @@
         <v>587</v>
       </c>
       <c r="C591" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="D591" s="2" t="s">
         <v>770</v>
-      </c>
-      <c r="D591" s="2" t="s">
-        <v>771</v>
       </c>
       <c r="E591" s="1" t="s">
         <v>5</v>
@@ -12264,10 +12264,10 @@
         <v>588</v>
       </c>
       <c r="C592" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="D592" s="2" t="s">
         <v>772</v>
-      </c>
-      <c r="D592" s="2" t="s">
-        <v>773</v>
       </c>
       <c r="E592" s="1" t="s">
         <v>5</v>
@@ -12280,10 +12280,10 @@
         <v>589</v>
       </c>
       <c r="C593" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="D593" s="2" t="s">
         <v>774</v>
-      </c>
-      <c r="D593" s="2" t="s">
-        <v>775</v>
       </c>
       <c r="E593" s="1" t="s">
         <v>5</v>
@@ -12296,10 +12296,10 @@
         <v>590</v>
       </c>
       <c r="C594" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="D594" s="2" t="s">
         <v>776</v>
-      </c>
-      <c r="D594" s="2" t="s">
-        <v>777</v>
       </c>
       <c r="E594" s="1" t="s">
         <v>5</v>
@@ -12312,10 +12312,10 @@
         <v>591</v>
       </c>
       <c r="C595" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="D595" s="2" t="s">
         <v>778</v>
-      </c>
-      <c r="D595" s="2" t="s">
-        <v>779</v>
       </c>
       <c r="E595" s="1" t="s">
         <v>5</v>
@@ -12328,10 +12328,10 @@
         <v>592</v>
       </c>
       <c r="C596" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="D596" s="2" t="s">
         <v>780</v>
-      </c>
-      <c r="D596" s="2" t="s">
-        <v>781</v>
       </c>
       <c r="E596" s="1" t="s">
         <v>5</v>
@@ -12344,10 +12344,10 @@
         <v>593</v>
       </c>
       <c r="C597" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="D597" s="2" t="s">
         <v>782</v>
-      </c>
-      <c r="D597" s="2" t="s">
-        <v>783</v>
       </c>
       <c r="E597" s="1" t="s">
         <v>5</v>
@@ -12360,10 +12360,10 @@
         <v>594</v>
       </c>
       <c r="C598" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="D598" s="2" t="s">
         <v>784</v>
-      </c>
-      <c r="D598" s="2" t="s">
-        <v>785</v>
       </c>
       <c r="E598" s="1" t="s">
         <v>5</v>
@@ -12375,10 +12375,10 @@
         <v>595</v>
       </c>
       <c r="C599" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="D599" s="2" t="s">
         <v>786</v>
-      </c>
-      <c r="D599" s="2" t="s">
-        <v>787</v>
       </c>
       <c r="E599" s="5"/>
     </row>
@@ -12387,10 +12387,10 @@
         <v>596</v>
       </c>
       <c r="C600" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="D600" s="6" t="s">
         <v>788</v>
-      </c>
-      <c r="D600" s="6" t="s">
-        <v>789</v>
       </c>
       <c r="E600" s="5"/>
     </row>
@@ -12402,10 +12402,10 @@
         <v>509</v>
       </c>
       <c r="C602" s="4" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D602" s="8" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="603" spans="2:6" ht="13" hidden="1" x14ac:dyDescent="0.3">
@@ -12413,10 +12413,10 @@
         <v>334</v>
       </c>
       <c r="C603" s="10" t="s">
+        <v>793</v>
+      </c>
+      <c r="D603" t="s">
         <v>794</v>
-      </c>
-      <c r="D603" t="s">
-        <v>795</v>
       </c>
       <c r="E603" s="11">
         <v>3277876171384</v>
@@ -12427,10 +12427,10 @@
         <v>263</v>
       </c>
       <c r="C604" s="10" t="s">
+        <v>795</v>
+      </c>
+      <c r="D604" s="12" t="s">
         <v>796</v>
-      </c>
-      <c r="D604" s="12" t="s">
-        <v>797</v>
       </c>
       <c r="E604" s="11">
         <v>3520210170957</v>
@@ -12440,12 +12440,25 @@
   <autoFilter ref="B4:F604" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="M.S Traders Harbanspura (Risen)"/>
-        <filter val="Risen / Gajjumata _Rafaqat Sons"/>
-        <filter val="Risen / Manawa _CB TRADERS"/>
-        <filter val="Risen / Sabzazar _Rafaqat Sons"/>
-        <filter val="Risen / Shadbagh _SB Traders"/>
-        <filter val="Risen / TN Traders (Raiwind Road )"/>
+        <filter val="EURO RANJERS MART"/>
+        <filter val="Euro store  (Academy Road)"/>
+        <filter val="EURO STORE (N F C )"/>
+        <filter val="EURO STORE (Rahamt chowk)"/>
+        <filter val="Euro Store (Scheme Mor)"/>
+        <filter val="Euro Store Airport Road"/>
+        <filter val="Euro Store Bedian Road"/>
+        <filter val="Euro Store College Road (Model Town)"/>
+        <filter val="EURO STORE CROWN BEHRIA TOWN"/>
+        <filter val="Euro Store E-2 (Wapda Town)"/>
+        <filter val="EURO STORE FATAH GARH"/>
+        <filter val="Euro Store G.T Road"/>
+        <filter val="Euro Store Garhi Shahu"/>
+        <filter val="EURO Store Hypermarket (Raiwind Road)"/>
+        <filter val="Euro Store Iqbal Town (Ranchna)"/>
+        <filter val="EURO STORE MARIYA STOP"/>
+        <filter val="EURO STORE PH VIII PARK VIEW"/>
+        <filter val="Euro Stores (G-1 Market)"/>
+        <filter val="EURO Stores (Nishat Colony)"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F598">
